--- a/research/traditional_assets/database/data/united_arab_emirates/united_arab_emirates_chemical_specialty.xlsx
+++ b/research/traditional_assets/database/data/united_arab_emirates/united_arab_emirates_chemical_specialty.xlsx
@@ -644,10 +644,10 @@
         <v>0.1328096003958926</v>
       </c>
       <c r="X2">
-        <v>0.1032496678309931</v>
+        <v>0.1032212903145358</v>
       </c>
       <c r="Y2">
-        <v>0.02955993256489953</v>
+        <v>0.02958831008135684</v>
       </c>
       <c r="Z2">
         <v>2.022636976808649</v>
@@ -656,10 +656,10 @@
         <v>0.4047475745567394</v>
       </c>
       <c r="AB2">
-        <v>0.09002464859884148</v>
+        <v>0.09000294498634302</v>
       </c>
       <c r="AC2">
-        <v>0.314722925957898</v>
+        <v>0.3147446295703964</v>
       </c>
       <c r="AD2">
         <v>1702.7</v>
@@ -775,10 +775,10 @@
         <v>0.1328096003958926</v>
       </c>
       <c r="X3">
-        <v>0.1032496678309931</v>
+        <v>0.1032212903145358</v>
       </c>
       <c r="Y3">
-        <v>0.02955993256489953</v>
+        <v>0.02958831008135684</v>
       </c>
       <c r="Z3">
         <v>2.022636976808649</v>
@@ -787,10 +787,10 @@
         <v>0.4047475745567394</v>
       </c>
       <c r="AB3">
-        <v>0.09002464859884148</v>
+        <v>0.09000294498634302</v>
       </c>
       <c r="AC3">
-        <v>0.314722925957898</v>
+        <v>0.3147446295703964</v>
       </c>
       <c r="AD3">
         <v>1702.7</v>
@@ -1127,49 +1127,49 @@
         <v>3.50398262128892</v>
       </c>
       <c r="F2">
-        <v>3.04948472548745</v>
+        <v>3.013781838844</v>
       </c>
       <c r="G2">
         <v>2.29350754310345</v>
       </c>
       <c r="H2">
-        <v>3.51072737068965</v>
+        <v>3.70576778017241</v>
       </c>
       <c r="I2">
         <v>0.235182806392354</v>
       </c>
       <c r="J2">
-        <v>0.36</v>
+        <v>0.38</v>
       </c>
       <c r="K2">
         <v>5537.2</v>
       </c>
       <c r="L2">
-        <v>4829.05706080426</v>
+        <v>4837.13631643512</v>
       </c>
       <c r="M2">
         <v>6571.2</v>
       </c>
       <c r="N2">
-        <v>6766.72106080426</v>
+        <v>6919.59831643512</v>
       </c>
       <c r="O2">
         <v>1702.7</v>
       </c>
       <c r="P2">
-        <v>2606.364</v>
+        <v>2751.162</v>
       </c>
       <c r="Q2">
-        <v>0.0900246485988415</v>
+        <v>0.09000294498634299</v>
       </c>
       <c r="R2">
-        <v>0.08874679923427591</v>
+        <v>0.0877773488013537</v>
       </c>
       <c r="S2">
         <v>0.0470167338209769</v>
       </c>
       <c r="T2">
-        <v>0.0470917338209769</v>
+        <v>0.0451417338209769</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1182,16 +1182,16 @@
         </is>
       </c>
       <c r="W2">
-        <v>0.103249667830993</v>
+        <v>0.103221290314536</v>
       </c>
       <c r="X2">
-        <v>0.112177773529257</v>
+        <v>0.113908854757069</v>
       </c>
       <c r="Y2">
         <v>1.15093281851851</v>
       </c>
       <c r="Z2">
-        <v>1.32979633928878</v>
+        <v>1.3651507261894</v>
       </c>
       <c r="AA2">
         <v>1702.7</v>
@@ -1224,7 +1224,7 @@
         <v>5537.2</v>
       </c>
       <c r="AK2">
-        <v>0.04991574391365663</v>
+        <v>0.04989108781210082</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1412,13 +1412,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.09248326929530136</v>
+        <v>0.09246020988882045</v>
       </c>
       <c r="C2">
-        <v>6893.821232071823</v>
+        <v>6893.84113816388</v>
       </c>
       <c r="D2">
-        <v>6225.121232071823</v>
+        <v>6225.14113816388</v>
       </c>
       <c r="E2">
         <v>-1702.7</v>
@@ -1463,19 +1463,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.09248326929530136</v>
+        <v>0.09246020988882045</v>
       </c>
       <c r="T2">
         <v>0.9352413814778209</v>
       </c>
       <c r="U2">
-        <v>0.05658897842796926</v>
+        <v>0.05518897842796926</v>
       </c>
       <c r="V2">
         <v>0.25</v>
       </c>
       <c r="W2">
-        <v>0.04244173382097694</v>
+        <v>0.04139173382097694</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1494,13 +1494,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.09233297846027289</v>
+        <v>0.09229947670230816</v>
       </c>
       <c r="C3">
-        <v>6841.527944172764</v>
+        <v>6842.96037541269</v>
       </c>
       <c r="D3">
-        <v>6245.226944172765</v>
+        <v>6246.659375412691</v>
       </c>
       <c r="E3">
         <v>-1630.301</v>
@@ -1527,37 +1527,37 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M3">
-        <v>4.096985449206546</v>
+        <v>3.995626849206546</v>
       </c>
       <c r="N3">
-        <v>494.9540349589567</v>
+        <v>495.0553935589567</v>
       </c>
       <c r="O3">
-        <v>123.7385087397392</v>
+        <v>123.7638483897392</v>
       </c>
       <c r="P3">
-        <v>371.2155262192175</v>
+        <v>371.2915451692176</v>
       </c>
       <c r="Q3">
-        <v>629.7155262192175</v>
+        <v>629.7915451692176</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.09283693042632638</v>
+        <v>0.09281369632737212</v>
       </c>
       <c r="T3">
         <v>0.9423265434587135</v>
       </c>
       <c r="U3">
-        <v>0.05658897842796926</v>
+        <v>0.05518897842796926</v>
       </c>
       <c r="V3">
         <v>0.25</v>
       </c>
       <c r="W3">
-        <v>0.04244173382097694</v>
+        <v>0.04139173382097694</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>121.8093221455823</v>
+        <v>124.8993059767994</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1576,13 +1576,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.0921826876252444</v>
+        <v>0.09213874351579589</v>
       </c>
       <c r="C4">
-        <v>6789.36495076138</v>
+        <v>6792.228891410931</v>
       </c>
       <c r="D4">
-        <v>6265.46295076138</v>
+        <v>6268.326891410931</v>
       </c>
       <c r="E4">
         <v>-1557.902</v>
@@ -1609,37 +1609,37 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M4">
-        <v>8.193970898413092</v>
+        <v>7.991253698413092</v>
       </c>
       <c r="N4">
-        <v>490.8570495097501</v>
+        <v>491.0597667097501</v>
       </c>
       <c r="O4">
-        <v>122.7142623774375</v>
+        <v>122.7649416774375</v>
       </c>
       <c r="P4">
-        <v>368.1427871323126</v>
+        <v>368.2948250323126</v>
       </c>
       <c r="Q4">
-        <v>626.6427871323126</v>
+        <v>626.7948250323126</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.09319780913145394</v>
+        <v>0.09317439677487382</v>
       </c>
       <c r="T4">
         <v>0.9495563005820733</v>
       </c>
       <c r="U4">
-        <v>0.05658897842796926</v>
+        <v>0.05518897842796926</v>
       </c>
       <c r="V4">
         <v>0.25</v>
       </c>
       <c r="W4">
-        <v>0.04244173382097694</v>
+        <v>0.04139173382097694</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>60.90466107279114</v>
+        <v>62.44965298839969</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1658,13 +1658,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.0920323967902159</v>
+        <v>0.0919780103292836</v>
       </c>
       <c r="C5">
-        <v>6737.333522509452</v>
+        <v>6741.648244955674</v>
       </c>
       <c r="D5">
-        <v>6285.830522509452</v>
+        <v>6290.145244955675</v>
       </c>
       <c r="E5">
         <v>-1485.503</v>
@@ -1691,37 +1691,37 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M5">
-        <v>12.29095634761964</v>
+        <v>11.98688054761964</v>
       </c>
       <c r="N5">
-        <v>486.7600640605436</v>
+        <v>487.0641398605436</v>
       </c>
       <c r="O5">
-        <v>121.6900160151359</v>
+        <v>121.7660349651359</v>
       </c>
       <c r="P5">
-        <v>365.0700480454077</v>
+        <v>365.2981048954077</v>
       </c>
       <c r="Q5">
-        <v>623.5700480454077</v>
+        <v>623.7981048954077</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.09356612863462535</v>
+        <v>0.09354253434500442</v>
       </c>
       <c r="T5">
         <v>0.9569351248626156</v>
       </c>
       <c r="U5">
-        <v>0.05658897842796926</v>
+        <v>0.05518897842796926</v>
       </c>
       <c r="V5">
         <v>0.25</v>
       </c>
       <c r="W5">
-        <v>0.04244173382097694</v>
+        <v>0.04139173382097694</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>40.60310738186076</v>
+        <v>41.63310199226646</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1740,13 +1740,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.09188210595518742</v>
+        <v>0.09181727714277131</v>
       </c>
       <c r="C6">
-        <v>6685.434946665286</v>
+        <v>6691.220016622803</v>
       </c>
       <c r="D6">
-        <v>6306.330946665285</v>
+        <v>6312.116016622804</v>
       </c>
       <c r="E6">
         <v>-1413.104</v>
@@ -1773,37 +1773,37 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M6">
-        <v>16.38794179682618</v>
+        <v>15.98250739682618</v>
       </c>
       <c r="N6">
-        <v>482.6630786113371</v>
+        <v>483.0685130113371</v>
       </c>
       <c r="O6">
-        <v>120.6657696528343</v>
+        <v>120.7671282528343</v>
       </c>
       <c r="P6">
-        <v>361.9973089585028</v>
+        <v>362.3013847585028</v>
       </c>
       <c r="Q6">
-        <v>620.4973089585028</v>
+        <v>620.8013847585028</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.09394212146077953</v>
+        <v>0.09391834144784608</v>
       </c>
       <c r="T6">
         <v>0.9644676746490027</v>
       </c>
       <c r="U6">
-        <v>0.05658897842796926</v>
+        <v>0.05518897842796926</v>
       </c>
       <c r="V6">
         <v>0.25</v>
       </c>
       <c r="W6">
-        <v>0.04244173382097694</v>
+        <v>0.04139173382097694</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>30.45233053639557</v>
+        <v>31.22482649419985</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1822,13 +1822,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.09173181512015893</v>
+        <v>0.09165654395625904</v>
       </c>
       <c r="C7">
-        <v>6633.67052732492</v>
+        <v>6640.945809148702</v>
       </c>
       <c r="D7">
-        <v>6326.96552732492</v>
+        <v>6334.240809148702</v>
       </c>
       <c r="E7">
         <v>-1340.705</v>
@@ -1855,37 +1855,37 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M7">
-        <v>20.48492724603273</v>
+        <v>19.97813424603273</v>
       </c>
       <c r="N7">
-        <v>478.5660931621305</v>
+        <v>479.0728861621305</v>
       </c>
       <c r="O7">
-        <v>119.6415232905326</v>
+        <v>119.7682215405326</v>
       </c>
       <c r="P7">
-        <v>358.9245698715979</v>
+        <v>359.3046646215979</v>
       </c>
       <c r="Q7">
-        <v>617.4245698715979</v>
+        <v>617.8046646215979</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.09432602992537904</v>
+        <v>0.09430206027916863</v>
       </c>
       <c r="T7">
         <v>0.9721588044308928</v>
       </c>
       <c r="U7">
-        <v>0.05658897842796926</v>
+        <v>0.05518897842796926</v>
       </c>
       <c r="V7">
         <v>0.25</v>
       </c>
       <c r="W7">
-        <v>0.04244173382097694</v>
+        <v>0.04139173382097694</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>24.36186442911645</v>
+        <v>24.97986119535988</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1904,13 +1904,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.09158152428513044</v>
+        <v>0.09149581076974676</v>
       </c>
       <c r="C8">
-        <v>6582.041585708645</v>
+        <v>6590.827247819999</v>
       </c>
       <c r="D8">
-        <v>6347.735585708646</v>
+        <v>6356.521247819999</v>
       </c>
       <c r="E8">
         <v>-1268.306</v>
@@ -1937,37 +1937,37 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M8">
-        <v>24.58191269523928</v>
+        <v>23.97376109523928</v>
       </c>
       <c r="N8">
-        <v>474.469107712924</v>
+        <v>475.077259312924</v>
       </c>
       <c r="O8">
-        <v>118.617276928231</v>
+        <v>118.769314828231</v>
       </c>
       <c r="P8">
-        <v>355.851830784693</v>
+        <v>356.3079444846929</v>
       </c>
       <c r="Q8">
-        <v>614.351830784693</v>
+        <v>614.8079444846929</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.09471810665518281</v>
+        <v>0.09469394334094483</v>
       </c>
       <c r="T8">
         <v>0.9800135752719719</v>
       </c>
       <c r="U8">
-        <v>0.05658897842796926</v>
+        <v>0.05518897842796926</v>
       </c>
       <c r="V8">
         <v>0.25</v>
       </c>
       <c r="W8">
-        <v>0.04244173382097694</v>
+        <v>0.04139173382097694</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>20.30155369093038</v>
+        <v>20.81655099613323</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1986,13 +1986,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.09143123345010197</v>
+        <v>0.09133507758323448</v>
       </c>
       <c r="C9">
-        <v>6530.549460443017</v>
+        <v>6540.86598087157</v>
       </c>
       <c r="D9">
-        <v>6368.642460443017</v>
+        <v>6378.95898087157</v>
       </c>
       <c r="E9">
         <v>-1195.907</v>
@@ -2019,37 +2019,37 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M9">
-        <v>28.67889814444582</v>
+        <v>27.96938794444582</v>
       </c>
       <c r="N9">
-        <v>470.3721222637174</v>
+        <v>471.0816324637174</v>
       </c>
       <c r="O9">
-        <v>117.5930305659294</v>
+        <v>117.7704081159294</v>
       </c>
       <c r="P9">
-        <v>352.7790916977881</v>
+        <v>353.3112243477881</v>
       </c>
       <c r="Q9">
-        <v>611.2790916977881</v>
+        <v>611.8112243477881</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.09511861514261676</v>
+        <v>0.09509425399544741</v>
       </c>
       <c r="T9">
         <v>0.9880372659160849</v>
       </c>
       <c r="U9">
-        <v>0.05658897842796926</v>
+        <v>0.05518897842796926</v>
       </c>
       <c r="V9">
         <v>0.25</v>
       </c>
       <c r="W9">
-        <v>0.04244173382097694</v>
+        <v>0.04139173382097694</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>17.40133173508318</v>
+        <v>17.84275799668562</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2068,13 +2068,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.09128094261507348</v>
+        <v>0.09117434439672219</v>
       </c>
       <c r="C10">
-        <v>6479.195507848447</v>
+        <v>6491.063679892983</v>
       </c>
       <c r="D10">
-        <v>6389.687507848447</v>
+        <v>6401.555679892983</v>
       </c>
       <c r="E10">
         <v>-1123.508</v>
@@ -2101,37 +2101,37 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M10">
-        <v>32.77588359365237</v>
+        <v>31.96501479365237</v>
       </c>
       <c r="N10">
-        <v>466.2751368145109</v>
+        <v>467.0860056145109</v>
       </c>
       <c r="O10">
-        <v>116.5687842036277</v>
+        <v>116.7715014036277</v>
       </c>
       <c r="P10">
-        <v>349.7063526108832</v>
+        <v>350.3145042108832</v>
       </c>
       <c r="Q10">
-        <v>608.2063526108832</v>
+        <v>608.8145042108831</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.09552783033629927</v>
+        <v>0.09550326705548265</v>
       </c>
       <c r="T10">
         <v>0.9962353846176788</v>
       </c>
       <c r="U10">
-        <v>0.05658897842796926</v>
+        <v>0.05518897842796926</v>
       </c>
       <c r="V10">
         <v>0.25</v>
       </c>
       <c r="W10">
-        <v>0.04244173382097694</v>
+        <v>0.04139173382097694</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>15.22616526819779</v>
+        <v>15.61241324709992</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2150,13 +2150,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.09113065178004501</v>
+        <v>0.09101361121020993</v>
       </c>
       <c r="C11">
-        <v>6427.981102232512</v>
+        <v>6441.422040243631</v>
       </c>
       <c r="D11">
-        <v>6410.872102232512</v>
+        <v>6424.313040243631</v>
       </c>
       <c r="E11">
         <v>-1051.109</v>
@@ -2183,37 +2183,37 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M11">
-        <v>36.87286904285891</v>
+        <v>35.96064164285891</v>
       </c>
       <c r="N11">
-        <v>462.1781513653044</v>
+        <v>463.0903787653044</v>
       </c>
       <c r="O11">
-        <v>115.5445378413261</v>
+        <v>115.7725946913261</v>
       </c>
       <c r="P11">
-        <v>346.6336135239783</v>
+        <v>347.3177840739783</v>
       </c>
       <c r="Q11">
-        <v>605.1336135239783</v>
+        <v>605.8177840739783</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.09594603927050228</v>
+        <v>0.09592126941354065</v>
       </c>
       <c r="T11">
         <v>1.004613681752275</v>
       </c>
       <c r="U11">
-        <v>0.05658897842796926</v>
+        <v>0.05518897842796926</v>
       </c>
       <c r="V11">
         <v>0.25</v>
       </c>
       <c r="W11">
-        <v>0.04244173382097694</v>
+        <v>0.04139173382097694</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>13.53436912728692</v>
+        <v>13.87770066408882</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2232,13 +2232,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.09098036094501652</v>
+        <v>0.09085287802369764</v>
       </c>
       <c r="C12">
-        <v>6376.907636189133</v>
+        <v>6391.942781476759</v>
       </c>
       <c r="D12">
-        <v>6432.197636189133</v>
+        <v>6447.232781476759</v>
       </c>
       <c r="E12">
         <v>-978.71</v>
@@ -2265,37 +2265,37 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M12">
-        <v>40.96985449206546</v>
+        <v>39.95626849206546</v>
       </c>
       <c r="N12">
-        <v>458.0811659160978</v>
+        <v>459.0947519160978</v>
       </c>
       <c r="O12">
-        <v>114.5202914790245</v>
+        <v>114.7736879790244</v>
       </c>
       <c r="P12">
-        <v>343.5608744370734</v>
+        <v>344.3210639370733</v>
       </c>
       <c r="Q12">
-        <v>602.0608744370734</v>
+        <v>602.8210639370734</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.09637354173657647</v>
+        <v>0.09634856071288882</v>
       </c>
       <c r="T12">
         <v>1.013178163267639</v>
       </c>
       <c r="U12">
-        <v>0.05658897842796926</v>
+        <v>0.05518897842796926</v>
       </c>
       <c r="V12">
         <v>0.25</v>
       </c>
       <c r="W12">
-        <v>0.04244173382097694</v>
+        <v>0.04139173382097694</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>12.18093221455823</v>
+        <v>12.48993059767994</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2314,13 +2314,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.09083007010998803</v>
+        <v>0.09069214483718535</v>
       </c>
       <c r="C13">
-        <v>6325.976520903723</v>
+        <v>6342.627647772558</v>
       </c>
       <c r="D13">
-        <v>6453.665520903724</v>
+        <v>6470.316647772558</v>
       </c>
       <c r="E13">
         <v>-906.311</v>
@@ -2347,37 +2347,37 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M13">
-        <v>45.06683994127201</v>
+        <v>43.95189534127201</v>
       </c>
       <c r="N13">
-        <v>453.9841804668912</v>
+        <v>455.0991250668912</v>
       </c>
       <c r="O13">
-        <v>113.4960451167228</v>
+        <v>113.7747812667228</v>
       </c>
       <c r="P13">
-        <v>340.4881353501684</v>
+        <v>341.3243438001684</v>
       </c>
       <c r="Q13">
-        <v>598.9881353501685</v>
+        <v>599.8243438001684</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.09681065099964109</v>
+        <v>0.09678545406390773</v>
       </c>
       <c r="T13">
         <v>1.021935105041776</v>
       </c>
       <c r="U13">
-        <v>0.05658897842796926</v>
+        <v>0.05518897842796926</v>
       </c>
       <c r="V13">
         <v>0.25</v>
       </c>
       <c r="W13">
-        <v>0.04244173382097694</v>
+        <v>0.04139173382097694</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>11.07357474050748</v>
+        <v>11.35448236152722</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2396,13 +2396,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.09067977927495956</v>
+        <v>0.09053141165067306</v>
       </c>
       <c r="C14">
-        <v>6275.189186464482</v>
+        <v>6293.478408380646</v>
       </c>
       <c r="D14">
-        <v>6475.277186464482</v>
+        <v>6493.566408380646</v>
       </c>
       <c r="E14">
         <v>-833.9120000000001</v>
@@ -2429,37 +2429,37 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M14">
-        <v>49.16382539047855</v>
+        <v>47.94752219047855</v>
       </c>
       <c r="N14">
-        <v>449.8871950176847</v>
+        <v>451.1034982176847</v>
       </c>
       <c r="O14">
-        <v>112.4717987544212</v>
+        <v>112.7758745544212</v>
       </c>
       <c r="P14">
-        <v>337.4153962632635</v>
+        <v>338.3276236632635</v>
       </c>
       <c r="Q14">
-        <v>595.9153962632636</v>
+        <v>596.8276236632635</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.09725769456413901</v>
+        <v>0.09723227680926799</v>
       </c>
       <c r="T14">
         <v>1.030891068219871</v>
       </c>
       <c r="U14">
-        <v>0.05658897842796926</v>
+        <v>0.05518897842796926</v>
       </c>
       <c r="V14">
         <v>0.25</v>
       </c>
       <c r="W14">
-        <v>0.04244173382097694</v>
+        <v>0.04139173382097694</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>10.15077684546519</v>
+        <v>10.40827549806662</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2478,13 +2478,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.09052948843993107</v>
+        <v>0.09037067846416079</v>
       </c>
       <c r="C15">
-        <v>6224.547082179969</v>
+        <v>6244.496858072092</v>
       </c>
       <c r="D15">
-        <v>6497.034082179969</v>
+        <v>6516.983858072092</v>
       </c>
       <c r="E15">
         <v>-761.513</v>
@@ -2511,37 +2511,37 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M15">
-        <v>53.2608108396851</v>
+        <v>51.9431490396851</v>
       </c>
       <c r="N15">
-        <v>445.7902095684781</v>
+        <v>447.1078713684781</v>
       </c>
       <c r="O15">
-        <v>111.4475523921195</v>
+        <v>111.7769678421195</v>
       </c>
       <c r="P15">
-        <v>334.3426571763586</v>
+        <v>335.3309035263586</v>
       </c>
       <c r="Q15">
-        <v>592.8426571763587</v>
+        <v>593.8309035263586</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.09771501499218858</v>
+        <v>0.09768937134187791</v>
       </c>
       <c r="T15">
         <v>1.040052915608956</v>
       </c>
       <c r="U15">
-        <v>0.05658897842796926</v>
+        <v>0.05518897842796926</v>
       </c>
       <c r="V15">
         <v>0.25</v>
       </c>
       <c r="W15">
-        <v>0.04244173382097694</v>
+        <v>0.04139173382097694</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>9.369947857352482</v>
+        <v>9.60763892129226</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2560,13 +2560,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.09037919760490258</v>
+        <v>0.0902099452776485</v>
       </c>
       <c r="C16">
-        <v>6174.051676903082</v>
+        <v>6195.684817601273</v>
       </c>
       <c r="D16">
-        <v>6518.937676903082</v>
+        <v>6540.570817601273</v>
       </c>
       <c r="E16">
         <v>-689.114</v>
@@ -2593,37 +2593,37 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M16">
-        <v>57.35779628889165</v>
+        <v>55.93877588889165</v>
       </c>
       <c r="N16">
-        <v>441.6932241192716</v>
+        <v>443.1122445192716</v>
       </c>
       <c r="O16">
-        <v>110.4233060298179</v>
+        <v>110.7780611298179</v>
       </c>
       <c r="P16">
-        <v>331.2699180894537</v>
+        <v>332.3341833894537</v>
       </c>
       <c r="Q16">
-        <v>589.7699180894537</v>
+        <v>590.8341833894538</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.09818297077903002</v>
+        <v>0.09815709597989736</v>
       </c>
       <c r="T16">
         <v>1.049427829216392</v>
       </c>
       <c r="U16">
-        <v>0.05658897842796926</v>
+        <v>0.05518897842796926</v>
       </c>
       <c r="V16">
         <v>0.25</v>
       </c>
       <c r="W16">
-        <v>0.04244173382097694</v>
+        <v>0.04139173382097694</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>8.70066586754159</v>
+        <v>8.921378998342814</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2642,13 +2642,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.0903526567698741</v>
+        <v>0.09021796209113622</v>
       </c>
       <c r="C17">
-        <v>6105.536127677687</v>
+        <v>6122.105337140681</v>
       </c>
       <c r="D17">
-        <v>6522.821127677686</v>
+        <v>6539.39033714068</v>
       </c>
       <c r="E17">
         <v>-616.7150000000001</v>
@@ -2675,37 +2675,37 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M17">
-        <v>62.64936523809818</v>
+        <v>61.56338023809818</v>
       </c>
       <c r="N17">
-        <v>436.4016551700651</v>
+        <v>437.487640170065</v>
       </c>
       <c r="O17">
-        <v>109.1004137925163</v>
+        <v>109.3719100425163</v>
       </c>
       <c r="P17">
-        <v>327.3012413775488</v>
+        <v>328.1157301275488</v>
       </c>
       <c r="Q17">
-        <v>585.8012413775488</v>
+        <v>586.6157301275488</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.09866193729026772</v>
+        <v>0.09863582590351727</v>
       </c>
       <c r="T17">
         <v>1.059023329026356</v>
       </c>
       <c r="U17">
-        <v>0.05768897842796925</v>
+        <v>0.05668897842796925</v>
       </c>
       <c r="V17">
         <v>0.25</v>
       </c>
       <c r="W17">
-        <v>0.04326673382097694</v>
+        <v>0.04251673382097694</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>7.965779358043384</v>
+        <v>8.106296608114576</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2724,13 +2724,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.0902106159348456</v>
+        <v>0.09006847890462394</v>
       </c>
       <c r="C18">
-        <v>6053.999413422071</v>
+        <v>6071.788164427981</v>
       </c>
       <c r="D18">
-        <v>6543.683413422072</v>
+        <v>6561.472164427982</v>
       </c>
       <c r="E18">
         <v>-544.316</v>
@@ -2757,37 +2757,37 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M18">
-        <v>66.82598958730473</v>
+        <v>65.66760558730473</v>
       </c>
       <c r="N18">
-        <v>432.2250308208585</v>
+        <v>433.3834148208585</v>
       </c>
       <c r="O18">
-        <v>108.0562577052146</v>
+        <v>108.3458537052146</v>
       </c>
       <c r="P18">
-        <v>324.1687731156439</v>
+        <v>325.0375611156439</v>
       </c>
       <c r="Q18">
-        <v>582.6687731156439</v>
+        <v>583.5375611156439</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.09915230776605868</v>
+        <v>0.09912595415865194</v>
       </c>
       <c r="T18">
         <v>1.068847293117509</v>
       </c>
       <c r="U18">
-        <v>0.05768897842796925</v>
+        <v>0.05668897842796925</v>
       </c>
       <c r="V18">
         <v>0.25</v>
       </c>
       <c r="W18">
-        <v>0.04326673382097694</v>
+        <v>0.04251673382097694</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>7.467918148165673</v>
+        <v>7.599653070107415</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2806,13 +2806,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.09006857509981712</v>
+        <v>0.08991899571811166</v>
       </c>
       <c r="C19">
-        <v>6002.596577272131</v>
+        <v>6021.620626214127</v>
       </c>
       <c r="D19">
-        <v>6564.679577272132</v>
+        <v>6583.703626214127</v>
       </c>
       <c r="E19">
         <v>-471.9169999999999</v>
@@ -2839,37 +2839,37 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M19">
-        <v>71.00261393651128</v>
+        <v>69.77183093651129</v>
       </c>
       <c r="N19">
-        <v>428.048406471652</v>
+        <v>429.279189471652</v>
       </c>
       <c r="O19">
-        <v>107.012101617913</v>
+        <v>107.319797367913</v>
       </c>
       <c r="P19">
-        <v>321.036304853739</v>
+        <v>321.959392103739</v>
       </c>
       <c r="Q19">
-        <v>579.536304853739</v>
+        <v>580.459392103739</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.09965449439789284</v>
+        <v>0.09962789273318745</v>
       </c>
       <c r="T19">
         <v>1.078907979234956</v>
       </c>
       <c r="U19">
-        <v>0.05768897842796925</v>
+        <v>0.05668897842796925</v>
       </c>
       <c r="V19">
         <v>0.25</v>
       </c>
       <c r="W19">
-        <v>0.04326673382097694</v>
+        <v>0.04251673382097694</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>7.028628845332397</v>
+        <v>7.152614654218742</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2888,13 +2888,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.09022353426478864</v>
+        <v>0.08976951253159937</v>
       </c>
       <c r="C20">
-        <v>5907.298515267379</v>
+        <v>5971.604248636691</v>
       </c>
       <c r="D20">
-        <v>6541.780515267379</v>
+        <v>6606.086248636691</v>
       </c>
       <c r="E20">
         <v>-399.5180000000003</v>
@@ -2921,45 +2921,45 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M20">
-        <v>78.04623868571781</v>
+        <v>73.87605628571781</v>
       </c>
       <c r="N20">
-        <v>421.0047817224454</v>
+        <v>425.1749641224454</v>
       </c>
       <c r="O20">
-        <v>105.2511954306114</v>
+        <v>106.2937410306114</v>
       </c>
       <c r="P20">
-        <v>315.7535862918341</v>
+        <v>318.881223091834</v>
       </c>
       <c r="Q20">
-        <v>574.2535862918342</v>
+        <v>577.381223091834</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.100168929484162</v>
+        <v>0.1001420737119799</v>
       </c>
       <c r="T20">
         <v>1.089214047940633</v>
       </c>
       <c r="U20">
-        <v>0.05988897842796925</v>
+        <v>0.05668897842796925</v>
       </c>
       <c r="V20">
         <v>0.25</v>
       </c>
       <c r="W20">
-        <v>0.04491673382097694</v>
+        <v>0.04251673382097694</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y20">
-        <v>6.394299441101546</v>
+        <v>6.755247173428814</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2970,13 +2970,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.09009799342976019</v>
+        <v>0.08986227934508711</v>
       </c>
       <c r="C21">
-        <v>5853.43896874763</v>
+        <v>5885.297080924537</v>
       </c>
       <c r="D21">
-        <v>6560.319968747631</v>
+        <v>6592.178080924537</v>
       </c>
       <c r="E21">
         <v>-327.1190000000001</v>
@@ -3003,37 +3003,37 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M21">
-        <v>82.38214083492437</v>
+        <v>80.31876933492437</v>
       </c>
       <c r="N21">
-        <v>416.6688795732389</v>
+        <v>418.7322510732389</v>
       </c>
       <c r="O21">
-        <v>104.1672198933097</v>
+        <v>104.6830627683097</v>
       </c>
       <c r="P21">
-        <v>312.5016596799292</v>
+        <v>314.0491883049292</v>
       </c>
       <c r="Q21">
-        <v>571.0016596799292</v>
+        <v>572.5491883049292</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.1006960666713266</v>
+        <v>0.1006689505174092</v>
       </c>
       <c r="T21">
         <v>1.099774587478549</v>
       </c>
       <c r="U21">
-        <v>0.05988897842796925</v>
+        <v>0.05838897842796925</v>
       </c>
       <c r="V21">
         <v>0.25</v>
       </c>
       <c r="W21">
-        <v>0.04491673382097694</v>
+        <v>0.04379173382097694</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>6.057757365254095</v>
+        <v>6.213379818198545</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3052,13 +3052,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.08997245259473169</v>
+        <v>0.08972554615857481</v>
       </c>
       <c r="C22">
-        <v>5799.684802768663</v>
+        <v>5833.418474952363</v>
       </c>
       <c r="D22">
-        <v>6578.964802768664</v>
+        <v>6612.698474952363</v>
       </c>
       <c r="E22">
         <v>-254.72</v>
@@ -3085,37 +3085,37 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M22">
-        <v>86.71804298413092</v>
+        <v>84.54607298413092</v>
       </c>
       <c r="N22">
-        <v>412.3329774240323</v>
+        <v>414.5049474240324</v>
       </c>
       <c r="O22">
-        <v>103.0832443560081</v>
+        <v>103.6262368560081</v>
       </c>
       <c r="P22">
-        <v>309.2497330680242</v>
+        <v>310.8787105680243</v>
       </c>
       <c r="Q22">
-        <v>567.7497330680242</v>
+        <v>569.3787105680243</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.1012363822881704</v>
+        <v>0.1012089992429743</v>
       </c>
       <c r="T22">
         <v>1.110599140504912</v>
       </c>
       <c r="U22">
-        <v>0.05988897842796925</v>
+        <v>0.05838897842796925</v>
       </c>
       <c r="V22">
         <v>0.25</v>
       </c>
       <c r="W22">
-        <v>0.04491673382097694</v>
+        <v>0.04379173382097694</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>5.75486949699139</v>
+        <v>5.902710827288618</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3134,13 +3134,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.09008316175970318</v>
+        <v>0.08958881297206253</v>
       </c>
       <c r="C23">
-        <v>5710.838203483777</v>
+        <v>5781.668021294599</v>
       </c>
       <c r="D23">
-        <v>6562.517203483777</v>
+        <v>6633.347021294599</v>
       </c>
       <c r="E23">
         <v>-182.3210000000001</v>
@@ -3167,45 +3167,45 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M23">
-        <v>93.33451363333747</v>
+        <v>88.77337663333746</v>
       </c>
       <c r="N23">
-        <v>405.7165067748258</v>
+        <v>410.2776437748258</v>
       </c>
       <c r="O23">
-        <v>101.4291266937065</v>
+        <v>102.5694109437064</v>
       </c>
       <c r="P23">
-        <v>304.2873800811194</v>
+        <v>307.7082328311193</v>
       </c>
       <c r="Q23">
-        <v>562.7873800811194</v>
+        <v>566.2082328311194</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.1017903767813899</v>
+        <v>0.1017627200881739</v>
       </c>
       <c r="T23">
         <v>1.121697732848399</v>
       </c>
       <c r="U23">
-        <v>0.06138897842796925</v>
+        <v>0.05838897842796925</v>
       </c>
       <c r="V23">
         <v>0.25</v>
       </c>
       <c r="W23">
-        <v>0.04604173382097694</v>
+        <v>0.04379173382097694</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y23">
-        <v>5.346907601283208</v>
+        <v>5.621629359322493</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3216,13 +3216,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.0899688709246747</v>
+        <v>0.08958407978555026</v>
       </c>
       <c r="C24">
-        <v>5655.42029345445</v>
+        <v>5709.98610542212</v>
       </c>
       <c r="D24">
-        <v>6579.498293454451</v>
+        <v>6634.064105422121</v>
       </c>
       <c r="E24">
         <v>-109.922</v>
@@ -3249,37 +3249,37 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M24">
-        <v>97.77901428254401</v>
+        <v>94.27490268254401</v>
       </c>
       <c r="N24">
-        <v>401.2720061256192</v>
+        <v>404.7761177256193</v>
       </c>
       <c r="O24">
-        <v>100.3180015314048</v>
+        <v>101.1940294314048</v>
       </c>
       <c r="P24">
-        <v>300.9540045942144</v>
+        <v>303.5820882942144</v>
       </c>
       <c r="Q24">
-        <v>559.4540045942144</v>
+        <v>562.0820882942144</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.1023585762616151</v>
+        <v>0.1023306389037632</v>
       </c>
       <c r="T24">
         <v>1.133080904482744</v>
       </c>
       <c r="U24">
-        <v>0.06138897842796925</v>
+        <v>0.05918897842796925</v>
       </c>
       <c r="V24">
         <v>0.25</v>
       </c>
       <c r="W24">
-        <v>0.04604173382097694</v>
+        <v>0.04439173382097694</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>5.103866346679425</v>
+        <v>5.29357237406693</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3298,13 +3298,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.08985458008964622</v>
+        <v>0.08945334659903798</v>
       </c>
       <c r="C25">
-        <v>5600.090491537763</v>
+        <v>5657.454822506788</v>
       </c>
       <c r="D25">
-        <v>6596.567491537763</v>
+        <v>6653.931822506788</v>
       </c>
       <c r="E25">
         <v>-37.52300000000014</v>
@@ -3331,37 +3331,37 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M25">
-        <v>102.2235149317506</v>
+        <v>98.56012553175056</v>
       </c>
       <c r="N25">
-        <v>396.8275054764127</v>
+        <v>400.4908948764127</v>
       </c>
       <c r="O25">
-        <v>99.20687636910317</v>
+        <v>100.1227237191032</v>
       </c>
       <c r="P25">
-        <v>297.6206291073095</v>
+        <v>300.3681711573095</v>
       </c>
       <c r="Q25">
-        <v>556.1206291073095</v>
+        <v>558.8681711573095</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.1029415341698981</v>
+        <v>0.1029133088574198</v>
       </c>
       <c r="T25">
         <v>1.144759742912787</v>
       </c>
       <c r="U25">
-        <v>0.06138897842796925</v>
+        <v>0.05918897842796925</v>
       </c>
       <c r="V25">
         <v>0.25</v>
       </c>
       <c r="W25">
-        <v>0.04604173382097694</v>
+        <v>0.04439173382097694</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>4.881959114215102</v>
+        <v>5.063417053455324</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3380,13 +3380,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.08974028925461774</v>
+        <v>0.08932261341252569</v>
       </c>
       <c r="C26">
-        <v>5544.84948525421</v>
+        <v>5605.042896852407</v>
       </c>
       <c r="D26">
-        <v>6613.72548525421</v>
+        <v>6673.918896852408</v>
       </c>
       <c r="E26">
         <v>34.87599999999975</v>
@@ -3413,37 +3413,37 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M26">
-        <v>106.6680155809571</v>
+        <v>102.8453483809571</v>
       </c>
       <c r="N26">
-        <v>392.3830048272062</v>
+        <v>396.2056720272062</v>
       </c>
       <c r="O26">
-        <v>98.09575120680154</v>
+        <v>99.05141800680154</v>
       </c>
       <c r="P26">
-        <v>294.2872536204046</v>
+        <v>297.1542540204046</v>
       </c>
       <c r="Q26">
-        <v>552.7872536204046</v>
+        <v>555.6542540204046</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.1035398330757675</v>
+        <v>0.1035113122309095</v>
       </c>
       <c r="T26">
         <v>1.156745919196252</v>
       </c>
       <c r="U26">
-        <v>0.06138897842796925</v>
+        <v>0.05918897842796925</v>
       </c>
       <c r="V26">
         <v>0.25</v>
       </c>
       <c r="W26">
-        <v>0.04604173382097694</v>
+        <v>0.04439173382097694</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>4.678544151122807</v>
+        <v>4.852441342894686</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3462,13 +3462,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.08962599841958925</v>
+        <v>0.0891918802260134</v>
       </c>
       <c r="C27">
-        <v>5489.697969296036</v>
+        <v>5552.751407275222</v>
       </c>
       <c r="D27">
-        <v>6630.972969296035</v>
+        <v>6694.026407275222</v>
       </c>
       <c r="E27">
         <v>107.2749999999999</v>
@@ -3495,37 +3495,37 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M27">
-        <v>111.1125162301636</v>
+        <v>107.1305712301636</v>
       </c>
       <c r="N27">
-        <v>387.9385041779996</v>
+        <v>391.9204491779996</v>
       </c>
       <c r="O27">
-        <v>96.9846260444999</v>
+        <v>97.9801122944999</v>
       </c>
       <c r="P27">
-        <v>290.9538781334997</v>
+        <v>293.9403368834997</v>
       </c>
       <c r="Q27">
-        <v>549.4538781334998</v>
+        <v>552.4403368834996</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.1041540866191267</v>
+        <v>0.1041252623610256</v>
       </c>
       <c r="T27">
         <v>1.169051726847276</v>
       </c>
       <c r="U27">
-        <v>0.06138897842796925</v>
+        <v>0.05918897842796925</v>
       </c>
       <c r="V27">
         <v>0.25</v>
       </c>
       <c r="W27">
-        <v>0.04604173382097694</v>
+        <v>0.04439173382097694</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>4.491402385077894</v>
+        <v>4.658343689178898</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3544,13 +3544,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.08951170758456077</v>
+        <v>0.08906114703950113</v>
       </c>
       <c r="C28">
-        <v>5434.636645620988</v>
+        <v>5500.581445632003</v>
       </c>
       <c r="D28">
-        <v>6648.310645620988</v>
+        <v>6714.255445632003</v>
       </c>
       <c r="E28">
         <v>179.674</v>
@@ -3577,37 +3577,37 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M28">
-        <v>115.5570168793702</v>
+        <v>111.4157940793702</v>
       </c>
       <c r="N28">
-        <v>383.4940035287931</v>
+        <v>387.6352263287931</v>
       </c>
       <c r="O28">
-        <v>95.87350088219827</v>
+        <v>96.90880658219827</v>
       </c>
       <c r="P28">
-        <v>287.6205026465948</v>
+        <v>290.7264197465948</v>
       </c>
       <c r="Q28">
-        <v>546.1205026465948</v>
+        <v>549.2264197465947</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.1047849416096037</v>
+        <v>0.1047558057379015</v>
       </c>
       <c r="T28">
         <v>1.181690123894274</v>
       </c>
       <c r="U28">
-        <v>0.06138897842796925</v>
+        <v>0.05918897842796925</v>
       </c>
       <c r="V28">
         <v>0.25</v>
       </c>
       <c r="W28">
-        <v>0.04604173382097694</v>
+        <v>0.04439173382097694</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>4.318656139497976</v>
+        <v>4.479176624210479</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3626,13 +3626,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.0896809167495323</v>
+        <v>0.08893041385298883</v>
       </c>
       <c r="C29">
-        <v>5336.601100713826</v>
+        <v>5448.534117017697</v>
       </c>
       <c r="D29">
-        <v>6622.674100713826</v>
+        <v>6734.607117017697</v>
       </c>
       <c r="E29">
         <v>252.0730000000001</v>
@@ -3659,45 +3659,45 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M29">
-        <v>122.7381997285767</v>
+        <v>115.7010169285767</v>
       </c>
       <c r="N29">
-        <v>376.3128206795865</v>
+        <v>383.3500034795865</v>
       </c>
       <c r="O29">
-        <v>94.07820516989662</v>
+        <v>95.83750086989663</v>
       </c>
       <c r="P29">
-        <v>282.2346155096899</v>
+        <v>287.5125026096899</v>
       </c>
       <c r="Q29">
-        <v>540.7346155096899</v>
+        <v>546.0125026096898</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.10543308029845</v>
+        <v>0.1054036242757878</v>
       </c>
       <c r="T29">
         <v>1.194674778394614</v>
       </c>
       <c r="U29">
-        <v>0.06278897842796925</v>
+        <v>0.05918897842796925</v>
       </c>
       <c r="V29">
         <v>0.25</v>
       </c>
       <c r="W29">
-        <v>0.04709173382097694</v>
+        <v>0.04439173382097694</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y29">
-        <v>4.065979633983265</v>
+        <v>4.313281193684165</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3708,13 +3708,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.08957712591450381</v>
+        <v>0.08900968066647655</v>
       </c>
       <c r="C30">
-        <v>5279.903745366721</v>
+        <v>5363.780689999867</v>
       </c>
       <c r="D30">
-        <v>6638.375745366721</v>
+        <v>6722.252689999867</v>
       </c>
       <c r="E30">
         <v>324.472</v>
@@ -3741,37 +3741,37 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M30">
-        <v>127.2840589777833</v>
+        <v>122.0134117777833</v>
       </c>
       <c r="N30">
-        <v>371.76696143038</v>
+        <v>377.03760863038</v>
       </c>
       <c r="O30">
-        <v>92.94174035759499</v>
+        <v>94.25940215759499</v>
       </c>
       <c r="P30">
-        <v>278.825221072785</v>
+        <v>282.778206472785</v>
       </c>
       <c r="Q30">
-        <v>537.325221072785</v>
+        <v>541.278206472785</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.1060992228397643</v>
+        <v>0.1060694377730597</v>
       </c>
       <c r="T30">
         <v>1.208020117742185</v>
       </c>
       <c r="U30">
-        <v>0.06278897842796925</v>
+        <v>0.06018897842796925</v>
       </c>
       <c r="V30">
         <v>0.25</v>
       </c>
       <c r="W30">
-        <v>0.04709173382097694</v>
+        <v>0.04514173382097694</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>3.920766075626719</v>
+        <v>4.090132495574004</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3790,13 +3790,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.0894733350794753</v>
+        <v>0.08888644747996427</v>
       </c>
       <c r="C31">
-        <v>5223.281020766592</v>
+        <v>5310.608260487366</v>
       </c>
       <c r="D31">
-        <v>6654.152020766592</v>
+        <v>6741.479260487366</v>
       </c>
       <c r="E31">
         <v>396.8709999999999</v>
@@ -3823,37 +3823,37 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M31">
-        <v>131.8299182269898</v>
+        <v>126.3710336269898</v>
       </c>
       <c r="N31">
-        <v>367.2211021811734</v>
+        <v>372.6799867811734</v>
       </c>
       <c r="O31">
-        <v>91.80527554529336</v>
+        <v>93.16999669529335</v>
       </c>
       <c r="P31">
-        <v>275.4158266358801</v>
+        <v>279.5099900858801</v>
       </c>
       <c r="Q31">
-        <v>533.9158266358801</v>
+        <v>538.0099900858801</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.106784129959707</v>
+        <v>0.106754006580114</v>
       </c>
       <c r="T31">
         <v>1.221741382141801</v>
       </c>
       <c r="U31">
-        <v>0.06278897842796925</v>
+        <v>0.06018897842796925</v>
       </c>
       <c r="V31">
         <v>0.25</v>
       </c>
       <c r="W31">
-        <v>0.04709173382097694</v>
+        <v>0.04514173382097694</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>3.785567245432695</v>
+        <v>3.949093444002486</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3872,13 +3872,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.08936954424444683</v>
+        <v>0.08876321429345198</v>
       </c>
       <c r="C32">
-        <v>5166.733460266783</v>
+        <v>5257.546127729234</v>
       </c>
       <c r="D32">
-        <v>6670.003460266783</v>
+        <v>6760.816127729234</v>
       </c>
       <c r="E32">
         <v>469.2699999999998</v>
@@ -3905,37 +3905,37 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M32">
-        <v>136.3757774761964</v>
+        <v>130.7286554761964</v>
       </c>
       <c r="N32">
-        <v>362.6752429319669</v>
+        <v>368.3223649319669</v>
       </c>
       <c r="O32">
-        <v>90.66881073299172</v>
+        <v>92.08059123299172</v>
       </c>
       <c r="P32">
-        <v>272.0064321989752</v>
+        <v>276.2417736989752</v>
       </c>
       <c r="Q32">
-        <v>530.5064321989752</v>
+        <v>534.7417736989752</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.1074886058545054</v>
+        <v>0.1074581344959413</v>
       </c>
       <c r="T32">
         <v>1.23585468266712</v>
       </c>
       <c r="U32">
-        <v>0.06278897842796925</v>
+        <v>0.06018897842796925</v>
       </c>
       <c r="V32">
         <v>0.25</v>
       </c>
       <c r="W32">
-        <v>0.04709173382097694</v>
+        <v>0.04514173382097694</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>3.659381670584938</v>
+        <v>3.81745699586907</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3954,13 +3954,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.08926575340941835</v>
+        <v>0.0886399811069397</v>
       </c>
       <c r="C33">
-        <v>5110.261602314986</v>
+        <v>5204.595243562057</v>
       </c>
       <c r="D33">
-        <v>6685.930602314986</v>
+        <v>6780.264243562056</v>
       </c>
       <c r="E33">
         <v>541.6689999999996</v>
@@ -3987,37 +3987,37 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M33">
-        <v>140.9216367254029</v>
+        <v>135.0862773254029</v>
       </c>
       <c r="N33">
-        <v>358.1293836827604</v>
+        <v>363.9647430827604</v>
       </c>
       <c r="O33">
-        <v>89.53234592069009</v>
+        <v>90.99118577069009</v>
       </c>
       <c r="P33">
-        <v>268.5970377620703</v>
+        <v>272.9735573120703</v>
       </c>
       <c r="Q33">
-        <v>527.0970377620703</v>
+        <v>531.4735573120703</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.1082135013404573</v>
+        <v>0.1081826719165752</v>
       </c>
       <c r="T33">
         <v>1.250377064367087</v>
       </c>
       <c r="U33">
-        <v>0.06278897842796925</v>
+        <v>0.06018897842796925</v>
       </c>
       <c r="V33">
         <v>0.25</v>
       </c>
       <c r="W33">
-        <v>0.04709173382097694</v>
+        <v>0.04514173382097694</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>3.54133710056607</v>
+        <v>3.694313221808778</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4036,13 +4036,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.08916196257438985</v>
+        <v>0.08851674792042744</v>
       </c>
       <c r="C34">
-        <v>5053.865990514179</v>
+        <v>5151.756570806203</v>
       </c>
       <c r="D34">
-        <v>6701.93399051418</v>
+        <v>6799.824570806203</v>
       </c>
       <c r="E34">
         <v>614.068</v>
@@ -4069,37 +4069,37 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M34">
-        <v>145.4674959746095</v>
+        <v>139.4438991746095</v>
       </c>
       <c r="N34">
-        <v>353.5835244335537</v>
+        <v>359.6071212335538</v>
       </c>
       <c r="O34">
-        <v>88.39588110838844</v>
+        <v>89.90178030838845</v>
       </c>
       <c r="P34">
-        <v>265.1876433251653</v>
+        <v>269.7053409251654</v>
       </c>
       <c r="Q34">
-        <v>523.6876433251653</v>
+        <v>528.2053409251654</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.1089597172818783</v>
+        <v>0.1089285192613453</v>
       </c>
       <c r="T34">
         <v>1.265326574940581</v>
       </c>
       <c r="U34">
-        <v>0.06278897842796925</v>
+        <v>0.06018897842796925</v>
       </c>
       <c r="V34">
         <v>0.25</v>
       </c>
       <c r="W34">
-        <v>0.04709173382097694</v>
+        <v>0.04514173382097694</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>3.430670316173379</v>
+        <v>3.578865933627253</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4118,13 +4118,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.0890581717393614</v>
+        <v>0.08839351473391513</v>
       </c>
       <c r="C35">
-        <v>4997.547173684476</v>
+        <v>5099.03108342473</v>
       </c>
       <c r="D35">
-        <v>6718.014173684476</v>
+        <v>6819.498083424731</v>
       </c>
       <c r="E35">
         <v>686.4669999999999</v>
@@ -4151,37 +4151,37 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M35">
-        <v>150.013355223816</v>
+        <v>143.801521023816</v>
       </c>
       <c r="N35">
-        <v>349.0376651843472</v>
+        <v>355.2494993843472</v>
       </c>
       <c r="O35">
-        <v>87.25941629608681</v>
+        <v>88.81237484608681</v>
       </c>
       <c r="P35">
-        <v>261.7782488882605</v>
+        <v>266.4371245382604</v>
       </c>
       <c r="Q35">
-        <v>520.2782488882605</v>
+        <v>524.9371245382604</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.1097282083260284</v>
+        <v>0.1096966307059593</v>
       </c>
       <c r="T35">
         <v>1.280722339561046</v>
       </c>
       <c r="U35">
-        <v>0.06278897842796925</v>
+        <v>0.06018897842796925</v>
       </c>
       <c r="V35">
         <v>0.25</v>
       </c>
       <c r="W35">
-        <v>0.04709173382097694</v>
+        <v>0.04514173382097694</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.326710609622671</v>
+        <v>3.470415450790064</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4200,13 +4200,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.0889543809043329</v>
+        <v>0.08827028154740288</v>
       </c>
       <c r="C36">
-        <v>4941.305705925888</v>
+        <v>5046.419766685003</v>
       </c>
       <c r="D36">
-        <v>6734.171705925888</v>
+        <v>6839.285766685003</v>
       </c>
       <c r="E36">
         <v>758.8660000000002</v>
@@ -4233,37 +4233,37 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M36">
-        <v>154.5592144730226</v>
+        <v>148.1591428730226</v>
       </c>
       <c r="N36">
-        <v>344.4918059351407</v>
+        <v>350.8918775351407</v>
       </c>
       <c r="O36">
-        <v>86.12295148378517</v>
+        <v>87.72296938378517</v>
       </c>
       <c r="P36">
-        <v>258.3688544513555</v>
+        <v>263.1689081513555</v>
       </c>
       <c r="Q36">
-        <v>516.8688544513554</v>
+        <v>521.6689081513555</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.1105199869775769</v>
+        <v>0.1104880182549556</v>
       </c>
       <c r="T36">
         <v>1.296584642503343</v>
       </c>
       <c r="U36">
-        <v>0.06278897842796925</v>
+        <v>0.06018897842796925</v>
       </c>
       <c r="V36">
         <v>0.25</v>
       </c>
       <c r="W36">
-        <v>0.04709173382097694</v>
+        <v>0.04514173382097694</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.228866179927886</v>
+        <v>3.368344408119767</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4282,13 +4282,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.0888505900693044</v>
+        <v>0.0881470483608906</v>
       </c>
       <c r="C37">
-        <v>4885.142146681941</v>
+        <v>4993.923617323233</v>
       </c>
       <c r="D37">
-        <v>6750.407146681941</v>
+        <v>6859.188617323233</v>
       </c>
       <c r="E37">
         <v>831.2650000000001</v>
@@ -4315,37 +4315,37 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M37">
-        <v>159.1050737222291</v>
+        <v>152.5167647222291</v>
       </c>
       <c r="N37">
-        <v>339.9459466859341</v>
+        <v>346.5342556859341</v>
       </c>
       <c r="O37">
-        <v>84.98648667148353</v>
+        <v>86.63356392148353</v>
       </c>
       <c r="P37">
-        <v>254.9594600144506</v>
+        <v>259.9006917644506</v>
       </c>
       <c r="Q37">
-        <v>513.4594600144505</v>
+        <v>518.4006917644506</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.1113361280491731</v>
+        <v>0.1113037561900749</v>
       </c>
       <c r="T37">
         <v>1.312935016305403</v>
       </c>
       <c r="U37">
-        <v>0.06278897842796925</v>
+        <v>0.06018897842796925</v>
       </c>
       <c r="V37">
         <v>0.25</v>
       </c>
       <c r="W37">
-        <v>0.04709173382097694</v>
+        <v>0.04514173382097694</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.136612860501375</v>
+        <v>3.272105996459203</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4364,13 +4364,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.08874679923427593</v>
+        <v>0.08802381517437831</v>
       </c>
       <c r="C38">
-        <v>4829.057060804258</v>
+        <v>4941.543643711793</v>
       </c>
       <c r="D38">
-        <v>6766.721060804258</v>
+        <v>6879.207643711793</v>
       </c>
       <c r="E38">
         <v>903.6639999999995</v>
@@ -4397,37 +4397,37 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M38">
-        <v>163.6509329714356</v>
+        <v>156.8743865714356</v>
       </c>
       <c r="N38">
-        <v>335.4000874367276</v>
+        <v>342.1766338367277</v>
       </c>
       <c r="O38">
-        <v>83.85002185918191</v>
+        <v>85.54415845918192</v>
       </c>
       <c r="P38">
-        <v>251.5500655775457</v>
+        <v>256.6324753775457</v>
       </c>
       <c r="Q38">
-        <v>510.0500655775458</v>
+        <v>515.1324753775457</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.1121777735292566</v>
+        <v>0.1121449859356666</v>
       </c>
       <c r="T38">
         <v>1.329796339288777</v>
       </c>
       <c r="U38">
-        <v>0.06278897842796925</v>
+        <v>0.06018897842796925</v>
       </c>
       <c r="V38">
         <v>0.25</v>
       </c>
       <c r="W38">
-        <v>0.04709173382097694</v>
+        <v>0.04514173382097694</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>3.049484725487449</v>
+        <v>3.181214163224226</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4446,13 +4446,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.08936450839924745</v>
+        <v>0.08790058198786602</v>
       </c>
       <c r="C39">
-        <v>4660.711480212593</v>
+        <v>4889.280866029542</v>
       </c>
       <c r="D39">
-        <v>6670.774480212594</v>
+        <v>6899.343866029542</v>
       </c>
       <c r="E39">
         <v>976.0629999999999</v>
@@ -4479,45 +4479,45 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M39">
-        <v>175.1615760206422</v>
+        <v>161.2320084206422</v>
       </c>
       <c r="N39">
-        <v>323.8894443875211</v>
+        <v>337.8190119875211</v>
       </c>
       <c r="O39">
-        <v>80.97236109688026</v>
+        <v>84.45475299688027</v>
       </c>
       <c r="P39">
-        <v>242.9170832906408</v>
+        <v>253.3642589906408</v>
       </c>
       <c r="Q39">
-        <v>501.4170832906408</v>
+        <v>511.8642589906408</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.1130461379134698</v>
+        <v>0.1130129213874675</v>
       </c>
       <c r="T39">
         <v>1.347192942366861</v>
       </c>
       <c r="U39">
-        <v>0.06538897842796926</v>
+        <v>0.06018897842796925</v>
       </c>
       <c r="V39">
         <v>0.25</v>
       </c>
       <c r="W39">
-        <v>0.04904173382097694</v>
+        <v>0.04514173382097694</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y39">
-        <v>2.849089576296983</v>
+        <v>3.095235402056003</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4528,13 +4528,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.08928021756421897</v>
+        <v>0.08777734880135374</v>
       </c>
       <c r="C40">
-        <v>4601.244456700368</v>
+        <v>4837.136316435122</v>
       </c>
       <c r="D40">
-        <v>6683.706456700367</v>
+        <v>6919.598316435123</v>
       </c>
       <c r="E40">
         <v>1048.462</v>
@@ -4561,45 +4561,45 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M40">
-        <v>179.8956726698488</v>
+        <v>165.5896302698487</v>
       </c>
       <c r="N40">
-        <v>319.1553477383145</v>
+        <v>333.4613901383145</v>
       </c>
       <c r="O40">
-        <v>79.78883693457863</v>
+        <v>83.36534753457863</v>
       </c>
       <c r="P40">
-        <v>239.3665108037359</v>
+        <v>250.0960426037359</v>
       </c>
       <c r="Q40">
-        <v>497.8665108037359</v>
+        <v>508.5960426037359</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.1139425140520125</v>
+        <v>0.1139088547570686</v>
       </c>
       <c r="T40">
         <v>1.3651507261894</v>
       </c>
       <c r="U40">
-        <v>0.06538897842796926</v>
+        <v>0.06018897842796925</v>
       </c>
       <c r="V40">
         <v>0.25</v>
       </c>
       <c r="W40">
-        <v>0.04904173382097694</v>
+        <v>0.04514173382097694</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y40">
-        <v>2.774113534815483</v>
+        <v>3.013781838844003</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4610,13 +4610,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.08919592672919048</v>
+        <v>0.08838536561484145</v>
       </c>
       <c r="C41">
-        <v>4541.827670488226</v>
+        <v>4665.942059937253</v>
       </c>
       <c r="D41">
-        <v>6696.688670488226</v>
+        <v>6820.803059937253</v>
       </c>
       <c r="E41">
         <v>1120.861</v>
@@ -4643,37 +4643,37 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M41">
-        <v>184.6297693190553</v>
+        <v>177.0061546190553</v>
       </c>
       <c r="N41">
-        <v>314.421251089108</v>
+        <v>322.044865789108</v>
       </c>
       <c r="O41">
-        <v>78.60531277227699</v>
+        <v>80.51121644727699</v>
       </c>
       <c r="P41">
-        <v>235.815938316831</v>
+        <v>241.533649341831</v>
       </c>
       <c r="Q41">
-        <v>494.315938316831</v>
+        <v>500.033649341831</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.1148682795721467</v>
+        <v>0.1148341629912466</v>
       </c>
       <c r="T41">
         <v>1.383697289809399</v>
       </c>
       <c r="U41">
-        <v>0.06538897842796926</v>
+        <v>0.06268897842796925</v>
       </c>
       <c r="V41">
         <v>0.25</v>
       </c>
       <c r="W41">
-        <v>0.04904173382097694</v>
+        <v>0.04701673382097694</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.702982418538163</v>
+        <v>2.819399254688056</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4692,13 +4692,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.08911163589416199</v>
+        <v>0.08828088242832918</v>
       </c>
       <c r="C42">
-        <v>4482.461414883765</v>
+        <v>4610.319058869884</v>
       </c>
       <c r="D42">
-        <v>6709.721414883766</v>
+        <v>6837.579058869884</v>
       </c>
       <c r="E42">
         <v>1193.26</v>
@@ -4725,37 +4725,37 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M42">
-        <v>189.3638659682618</v>
+        <v>181.5447739682618</v>
       </c>
       <c r="N42">
-        <v>309.6871544399014</v>
+        <v>317.5062464399014</v>
       </c>
       <c r="O42">
-        <v>77.42178860997535</v>
+        <v>79.37656160997535</v>
       </c>
       <c r="P42">
-        <v>232.2653658299261</v>
+        <v>238.1296848299261</v>
       </c>
       <c r="Q42">
-        <v>490.7653658299261</v>
+        <v>496.6296848299261</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.115824903942952</v>
+        <v>0.1157903148332307</v>
       </c>
       <c r="T42">
         <v>1.402862072216731</v>
       </c>
       <c r="U42">
-        <v>0.06538897842796926</v>
+        <v>0.06268897842796925</v>
       </c>
       <c r="V42">
         <v>0.25</v>
       </c>
       <c r="W42">
-        <v>0.04904173382097694</v>
+        <v>0.04701673382097694</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.635407858074709</v>
+        <v>2.748914273320854</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4774,13 +4774,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.08902734505913353</v>
+        <v>0.0881763992418169</v>
       </c>
       <c r="C43">
-        <v>4423.145985482313</v>
+        <v>4554.778783558209</v>
       </c>
       <c r="D43">
-        <v>6722.804985482313</v>
+        <v>6854.43778355821</v>
       </c>
       <c r="E43">
         <v>1265.659</v>
@@ -4807,37 +4807,37 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M43">
-        <v>194.0979626174684</v>
+        <v>186.0833933174684</v>
       </c>
       <c r="N43">
-        <v>304.9530577906949</v>
+        <v>312.9676270906949</v>
       </c>
       <c r="O43">
-        <v>76.23826444767371</v>
+        <v>78.24190677267373</v>
       </c>
       <c r="P43">
-        <v>228.7147933430211</v>
+        <v>234.7257203180212</v>
       </c>
       <c r="Q43">
-        <v>487.2147933430211</v>
+        <v>493.2257203180212</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.1168139562585305</v>
+        <v>0.1167788786020616</v>
       </c>
       <c r="T43">
         <v>1.42267650826499</v>
       </c>
       <c r="U43">
-        <v>0.06538897842796926</v>
+        <v>0.06268897842796925</v>
       </c>
       <c r="V43">
         <v>0.25</v>
       </c>
       <c r="W43">
-        <v>0.04904173382097694</v>
+        <v>0.04701673382097694</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.571129617633862</v>
+        <v>2.681867583727663</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4856,13 +4856,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.08894305422410503</v>
+        <v>0.08807191605530462</v>
       </c>
       <c r="C44">
-        <v>4363.881680189286</v>
+        <v>4499.321847420169</v>
       </c>
       <c r="D44">
-        <v>6735.939680189286</v>
+        <v>6871.379847420169</v>
       </c>
       <c r="E44">
         <v>1338.058</v>
@@ -4889,37 +4889,37 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M44">
-        <v>198.8320592666749</v>
+        <v>190.6220126666749</v>
       </c>
       <c r="N44">
-        <v>300.2189611414883</v>
+        <v>308.4290077414884</v>
       </c>
       <c r="O44">
-        <v>75.05474028537208</v>
+        <v>77.10725193537209</v>
       </c>
       <c r="P44">
-        <v>225.1642208561162</v>
+        <v>231.3217558061163</v>
       </c>
       <c r="Q44">
-        <v>483.6642208561162</v>
+        <v>489.8217558061162</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.1178371138263702</v>
+        <v>0.1178015307767143</v>
       </c>
       <c r="T44">
         <v>1.443174200728706</v>
       </c>
       <c r="U44">
-        <v>0.06538897842796926</v>
+        <v>0.06268897842796925</v>
       </c>
       <c r="V44">
         <v>0.25</v>
       </c>
       <c r="W44">
-        <v>0.04904173382097694</v>
+        <v>0.04701673382097694</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.509912245785437</v>
+        <v>2.618013593638909</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4938,13 +4938,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.08972951338907655</v>
+        <v>0.08796743286879233</v>
       </c>
       <c r="C45">
-        <v>4170.890825477383</v>
+        <v>4443.948869953454</v>
       </c>
       <c r="D45">
-        <v>6615.347825477383</v>
+        <v>6888.405869953453</v>
       </c>
       <c r="E45">
         <v>1410.457</v>
@@ -4971,45 +4971,45 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M45">
-        <v>211.9716798158815</v>
+        <v>195.1606320158814</v>
       </c>
       <c r="N45">
-        <v>287.0793405922818</v>
+        <v>303.8903883922818</v>
       </c>
       <c r="O45">
-        <v>71.76983514807046</v>
+        <v>75.97259709807045</v>
       </c>
       <c r="P45">
-        <v>215.3095054442114</v>
+        <v>227.9177912942114</v>
       </c>
       <c r="Q45">
-        <v>473.8095054442114</v>
+        <v>486.4177912942114</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.1188961716597482</v>
+        <v>0.118860065483811</v>
       </c>
       <c r="T45">
         <v>1.464391110471851</v>
       </c>
       <c r="U45">
-        <v>0.06808897842796925</v>
+        <v>0.06268897842796925</v>
       </c>
       <c r="V45">
         <v>0.25</v>
       </c>
       <c r="W45">
-        <v>0.05106673382097694</v>
+        <v>0.04701673382097694</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y45">
-        <v>2.354328752037248</v>
+        <v>2.557129556577539</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5020,13 +5020,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.08966547255404808</v>
+        <v>0.08901794968228006</v>
       </c>
       <c r="C46">
-        <v>4108.1498178363</v>
+        <v>4204.110501873465</v>
       </c>
       <c r="D46">
-        <v>6625.0058178363</v>
+        <v>6720.966501873465</v>
       </c>
       <c r="E46">
         <v>1482.856</v>
@@ -5053,37 +5053,37 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M46">
-        <v>216.901253765088</v>
+        <v>210.848697365088</v>
       </c>
       <c r="N46">
-        <v>282.1497666430752</v>
+        <v>288.2023230430752</v>
       </c>
       <c r="O46">
-        <v>70.53744166076881</v>
+        <v>72.05058076076881</v>
       </c>
       <c r="P46">
-        <v>211.6123249823064</v>
+        <v>216.1517422823064</v>
       </c>
       <c r="Q46">
-        <v>470.1123249823064</v>
+        <v>474.6517422823064</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.1199930529871754</v>
+        <v>0.1199564050018753</v>
       </c>
       <c r="T46">
         <v>1.486365766991537</v>
       </c>
       <c r="U46">
-        <v>0.06808897842796925</v>
+        <v>0.06618897842796925</v>
       </c>
       <c r="V46">
         <v>0.25</v>
       </c>
       <c r="W46">
-        <v>0.05106673382097694</v>
+        <v>0.04964173382097694</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.300821280400037</v>
+        <v>2.366867932525322</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5102,13 +5102,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.09118768171901959</v>
+        <v>0.08893971649576776</v>
       </c>
       <c r="C47">
-        <v>3813.561796675653</v>
+        <v>4143.899867226667</v>
       </c>
       <c r="D47">
-        <v>6402.816796675653</v>
+        <v>6733.154867226667</v>
       </c>
       <c r="E47">
         <v>1555.255</v>
@@ -5135,45 +5135,45 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M47">
-        <v>237.1432162142945</v>
+        <v>215.6407132142945</v>
       </c>
       <c r="N47">
-        <v>261.9078041938687</v>
+        <v>283.4103071938687</v>
       </c>
       <c r="O47">
-        <v>65.47695104846719</v>
+        <v>70.85257679846717</v>
       </c>
       <c r="P47">
-        <v>196.4308531454016</v>
+        <v>212.5577303954015</v>
       </c>
       <c r="Q47">
-        <v>454.9308531454016</v>
+        <v>471.0577303954015</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.1211298209083272</v>
+        <v>0.1210926114115057</v>
       </c>
       <c r="T47">
         <v>1.50913950193012</v>
       </c>
       <c r="U47">
-        <v>0.07278897842796925</v>
+        <v>0.06618897842796925</v>
       </c>
       <c r="V47">
         <v>0.25</v>
       </c>
       <c r="W47">
-        <v>0.05459173382097694</v>
+        <v>0.04964173382097694</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y47">
-        <v>2.104428827334431</v>
+        <v>2.314270867358093</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5184,13 +5184,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.09115889088399111</v>
+        <v>0.0888614833092555</v>
       </c>
       <c r="C48">
-        <v>3745.226882867314</v>
+        <v>4083.733519705466</v>
       </c>
       <c r="D48">
-        <v>6406.880882867314</v>
+        <v>6745.387519705466</v>
       </c>
       <c r="E48">
         <v>1627.654</v>
@@ -5217,45 +5217,45 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M48">
-        <v>242.4130654635011</v>
+        <v>220.4327290635011</v>
       </c>
       <c r="N48">
-        <v>256.6379549446622</v>
+        <v>278.6182913446621</v>
       </c>
       <c r="O48">
-        <v>64.15948873616554</v>
+        <v>69.65457283616553</v>
       </c>
       <c r="P48">
-        <v>192.4784662084966</v>
+        <v>208.9637185084966</v>
       </c>
       <c r="Q48">
-        <v>450.9784662084966</v>
+        <v>467.4637185084966</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.1223086913450772</v>
+        <v>0.1222708995400113</v>
       </c>
       <c r="T48">
         <v>1.532756708533095</v>
       </c>
       <c r="U48">
-        <v>0.07278897842796925</v>
+        <v>0.06618897842796925</v>
       </c>
       <c r="V48">
         <v>0.25</v>
       </c>
       <c r="W48">
-        <v>0.05459173382097694</v>
+        <v>0.04964173382097694</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y48">
-        <v>2.058680374566291</v>
+        <v>2.263960631111178</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5266,13 +5266,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.09113010004896262</v>
+        <v>0.08977025012274321</v>
       </c>
       <c r="C49">
-        <v>3676.89713156402</v>
+        <v>3871.922433012517</v>
       </c>
       <c r="D49">
-        <v>6410.95013156402</v>
+        <v>6605.975433012517</v>
       </c>
       <c r="E49">
         <v>1700.053</v>
@@ -5299,37 +5299,37 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M49">
-        <v>247.6829147127077</v>
+        <v>234.7524533127077</v>
       </c>
       <c r="N49">
-        <v>251.3681056954556</v>
+        <v>264.2985670954556</v>
       </c>
       <c r="O49">
-        <v>62.8420264238639</v>
+        <v>66.0746417738639</v>
       </c>
       <c r="P49">
-        <v>188.5260792715917</v>
+        <v>198.2239253215917</v>
       </c>
       <c r="Q49">
-        <v>447.0260792715917</v>
+        <v>456.7239253215917</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.1235320474586858</v>
+        <v>0.1234936513714793</v>
       </c>
       <c r="T49">
         <v>1.557265130479579</v>
       </c>
       <c r="U49">
-        <v>0.07278897842796925</v>
+        <v>0.06898897842796925</v>
       </c>
       <c r="V49">
         <v>0.25</v>
       </c>
       <c r="W49">
-        <v>0.05459173382097694</v>
+        <v>0.05174173382097694</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.014878664469136</v>
+        <v>2.125860724204617</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5348,13 +5348,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.09614130921393413</v>
+        <v>0.08971301693623092</v>
       </c>
       <c r="C50">
-        <v>2966.322196986289</v>
+        <v>3808.133204110738</v>
       </c>
       <c r="D50">
-        <v>5772.774196986289</v>
+        <v>6614.585204110738</v>
       </c>
       <c r="E50">
         <v>1772.452</v>
@@ -5381,45 +5381,45 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M50">
-        <v>301.6048919619142</v>
+        <v>239.7471863619142</v>
       </c>
       <c r="N50">
-        <v>197.4461284462491</v>
+        <v>259.3038340462491</v>
       </c>
       <c r="O50">
-        <v>49.36153211156227</v>
+        <v>64.82595851156228</v>
       </c>
       <c r="P50">
-        <v>148.0845963346868</v>
+        <v>194.4778755346868</v>
       </c>
       <c r="Q50">
-        <v>406.5845963346868</v>
+        <v>452.9778755346869</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.12480245573051</v>
+        <v>0.1247634321195423</v>
       </c>
       <c r="T50">
         <v>1.582716184039389</v>
       </c>
       <c r="U50">
-        <v>0.08678897842796926</v>
+        <v>0.06898897842796925</v>
       </c>
       <c r="V50">
         <v>0.25</v>
       </c>
       <c r="W50">
-        <v>0.06509173382097694</v>
+        <v>0.05174173382097694</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y50">
-        <v>1.654651611125664</v>
+        <v>2.081571959117021</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5430,13 +5430,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.09621751837890564</v>
+        <v>0.08965578374971864</v>
       </c>
       <c r="C51">
-        <v>2885.197295449146</v>
+        <v>3744.36644725679</v>
       </c>
       <c r="D51">
-        <v>5764.048295449146</v>
+        <v>6623.21744725679</v>
       </c>
       <c r="E51">
         <v>1844.851</v>
@@ -5463,45 +5463,45 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M51">
-        <v>307.8883272111208</v>
+        <v>244.7419194111207</v>
       </c>
       <c r="N51">
-        <v>191.1626931970425</v>
+        <v>254.3091009970425</v>
       </c>
       <c r="O51">
-        <v>47.79067329926062</v>
+        <v>63.57727524926063</v>
       </c>
       <c r="P51">
-        <v>143.3720198977819</v>
+        <v>190.7318257477819</v>
       </c>
       <c r="Q51">
-        <v>401.8720198977819</v>
+        <v>449.2318257477819</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.1261226839345626</v>
+        <v>0.1260830081910587</v>
       </c>
       <c r="T51">
         <v>1.609165318130956</v>
       </c>
       <c r="U51">
-        <v>0.08678897842796926</v>
+        <v>0.06898897842796925</v>
       </c>
       <c r="V51">
         <v>0.25</v>
       </c>
       <c r="W51">
-        <v>0.06509173382097694</v>
+        <v>0.05174173382097694</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y51">
-        <v>1.62088321089861</v>
+        <v>2.039090898726878</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5512,13 +5512,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.09629372754387716</v>
+        <v>0.09252355056320635</v>
       </c>
       <c r="C52">
-        <v>2804.098733566535</v>
+        <v>3265.452039827264</v>
       </c>
       <c r="D52">
-        <v>5755.348733566535</v>
+        <v>6216.702039827264</v>
       </c>
       <c r="E52">
         <v>1917.25</v>
@@ -5545,45 +5545,45 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M52">
-        <v>314.1717624603273</v>
+        <v>277.9722624603273</v>
       </c>
       <c r="N52">
-        <v>184.8792579478359</v>
+        <v>221.078757947836</v>
       </c>
       <c r="O52">
-        <v>46.21981448695898</v>
+        <v>55.269689486959</v>
       </c>
       <c r="P52">
-        <v>138.659443460877</v>
+        <v>165.809068460877</v>
       </c>
       <c r="Q52">
-        <v>397.159443460877</v>
+        <v>424.309068460877</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.1274957212667774</v>
+        <v>0.1274553673054358</v>
       </c>
       <c r="T52">
         <v>1.636672417586186</v>
       </c>
       <c r="U52">
-        <v>0.08678897842796926</v>
+        <v>0.07678897842796925</v>
       </c>
       <c r="V52">
         <v>0.25</v>
       </c>
       <c r="W52">
-        <v>0.06509173382097694</v>
+        <v>0.05759173382097694</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y52">
-        <v>1.588465546680637</v>
+        <v>1.795326684724123</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5594,13 +5594,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.09636993670884868</v>
+        <v>0.09252481737669409</v>
       </c>
       <c r="C53">
-        <v>2723.026392256455</v>
+        <v>3192.884491239267</v>
       </c>
       <c r="D53">
-        <v>5746.675392256455</v>
+        <v>6216.533491239267</v>
       </c>
       <c r="E53">
         <v>1989.649</v>
@@ -5627,45 +5627,45 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M53">
-        <v>320.4551977095338</v>
+        <v>283.5317077095338</v>
       </c>
       <c r="N53">
-        <v>178.5958226986294</v>
+        <v>215.5193126986294</v>
       </c>
       <c r="O53">
-        <v>44.64895567465736</v>
+        <v>53.87982817465736</v>
       </c>
       <c r="P53">
-        <v>133.9468670239721</v>
+        <v>161.6394845239721</v>
       </c>
       <c r="Q53">
-        <v>392.4468670239721</v>
+        <v>420.1394845239721</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.1289248009390825</v>
+        <v>0.1288837410775426</v>
       </c>
       <c r="T53">
         <v>1.665302255794691</v>
       </c>
       <c r="U53">
-        <v>0.08678897842796926</v>
+        <v>0.07678897842796925</v>
       </c>
       <c r="V53">
         <v>0.25</v>
       </c>
       <c r="W53">
-        <v>0.06509173382097694</v>
+        <v>0.05759173382097694</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y53">
-        <v>1.55731916341239</v>
+        <v>1.760124200709925</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5676,13 +5676,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.09644614587382019</v>
+        <v>0.0940470841901818</v>
       </c>
       <c r="C54">
-        <v>2641.980153153655</v>
+        <v>2924.34467179936</v>
       </c>
       <c r="D54">
-        <v>5738.028153153655</v>
+        <v>6020.39267179936</v>
       </c>
       <c r="E54">
         <v>2062.048</v>
@@ -5709,37 +5709,37 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M54">
-        <v>326.7386329587404</v>
+        <v>303.7736701587404</v>
       </c>
       <c r="N54">
-        <v>172.3123874494228</v>
+        <v>195.2773502494229</v>
       </c>
       <c r="O54">
-        <v>43.07809686235571</v>
+        <v>48.81933756235571</v>
       </c>
       <c r="P54">
-        <v>129.2342905870671</v>
+        <v>146.4580126870671</v>
       </c>
       <c r="Q54">
-        <v>387.7342905870671</v>
+        <v>404.9580126870671</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.1304134255977337</v>
+        <v>0.1303716304234871</v>
       </c>
       <c r="T54">
         <v>1.69512500392855</v>
       </c>
       <c r="U54">
-        <v>0.08678897842796926</v>
+        <v>0.08068897842796925</v>
       </c>
       <c r="V54">
         <v>0.25</v>
       </c>
       <c r="W54">
-        <v>0.06509173382097694</v>
+        <v>0.06051673382097694</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>1.527370717962151</v>
+        <v>1.642838301777038</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5758,13 +5758,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.1030016050387917</v>
+        <v>0.09407760100366952</v>
       </c>
       <c r="C55">
-        <v>1911.987555562354</v>
+        <v>2848.140114015448</v>
       </c>
       <c r="D55">
-        <v>5080.434555562354</v>
+        <v>6016.587114015448</v>
       </c>
       <c r="E55">
         <v>2134.447</v>
@@ -5791,45 +5791,45 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M55">
-        <v>395.567564307947</v>
+        <v>309.6154715079469</v>
       </c>
       <c r="N55">
-        <v>103.4834561002163</v>
+        <v>189.4355489002163</v>
       </c>
       <c r="O55">
-        <v>25.87086402505408</v>
+        <v>47.35888722505408</v>
       </c>
       <c r="P55">
-        <v>77.61259207516223</v>
+        <v>142.0766616751622</v>
       </c>
       <c r="Q55">
-        <v>336.1125920751622</v>
+        <v>400.5766616751622</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.1319653959865403</v>
+        <v>0.1319228342096846</v>
       </c>
       <c r="T55">
         <v>1.726216805174489</v>
       </c>
       <c r="U55">
-        <v>0.1030889784279693</v>
+        <v>0.08068897842796925</v>
       </c>
       <c r="V55">
         <v>0.25</v>
       </c>
       <c r="W55">
-        <v>0.07731673382097694</v>
+        <v>0.06051673382097694</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y55">
-        <v>1.261607536708078</v>
+        <v>1.611841352686906</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5840,13 +5840,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.1179201899905149</v>
+        <v>0.09410811781715724</v>
       </c>
       <c r="C56">
-        <v>788.6637795905317</v>
+        <v>2771.940364263905</v>
       </c>
       <c r="D56">
-        <v>4029.509779590532</v>
+        <v>6012.786364263906</v>
       </c>
       <c r="E56">
         <v>2206.846</v>
@@ -5873,45 +5873,45 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M56">
-        <v>530.8732574571535</v>
+        <v>315.4572728571535</v>
       </c>
       <c r="N56">
-        <v>-31.82223704899025</v>
+        <v>183.5937475510098</v>
       </c>
       <c r="O56">
-        <v>-7.955559262247561</v>
+        <v>45.89843688775244</v>
       </c>
       <c r="P56">
-        <v>-23.86667778674268</v>
+        <v>137.6953106632573</v>
       </c>
       <c r="Q56">
-        <v>234.6333222132573</v>
+        <v>396.1953106632573</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.1344060965162311</v>
+        <v>0.1335414816387602</v>
       </c>
       <c r="T56">
-        <v>1.775113212166093</v>
+        <v>1.758660423865902</v>
       </c>
       <c r="U56">
-        <v>0.1357889784279692</v>
+        <v>0.08068897842796925</v>
       </c>
       <c r="V56">
-        <v>0.2350142022592094</v>
+        <v>0.25</v>
       </c>
       <c r="W56">
-        <v>0.1038766399871271</v>
+        <v>0.06051673382097694</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y56">
-        <v>0.9400568090368375</v>
+        <v>1.581992438748259</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5922,13 +5922,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.1188200797747946</v>
+        <v>0.09413863463064495</v>
       </c>
       <c r="C57">
-        <v>666.6056351813199</v>
+        <v>2695.745413438612</v>
       </c>
       <c r="D57">
-        <v>3979.85063518132</v>
+        <v>6008.990413438612</v>
       </c>
       <c r="E57">
         <v>2279.245</v>
@@ -5955,45 +5955,45 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M57">
-        <v>540.70424370636</v>
+        <v>321.29907420636</v>
       </c>
       <c r="N57">
-        <v>-41.65322329819674</v>
+        <v>177.7519462018032</v>
       </c>
       <c r="O57">
-        <v>-10.41330582454918</v>
+        <v>44.4379865504508</v>
       </c>
       <c r="P57">
-        <v>-31.23991747364755</v>
+        <v>133.3139596513524</v>
       </c>
       <c r="Q57">
-        <v>227.2600825263524</v>
+        <v>391.8139596513524</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.1363751208832585</v>
+        <v>0.1352320689535725</v>
       </c>
       <c r="T57">
-        <v>1.814560172436451</v>
+        <v>1.792545981165824</v>
       </c>
       <c r="U57">
-        <v>0.1357889784279692</v>
+        <v>0.08068897842796925</v>
       </c>
       <c r="V57">
-        <v>0.2307412167635874</v>
+        <v>0.25</v>
       </c>
       <c r="W57">
-        <v>0.1044568643224151</v>
+        <v>0.06051673382097694</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y57">
-        <v>0.9229648670543498</v>
+        <v>1.553228939861927</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6004,13 +6004,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1197199695590743</v>
+        <v>0.09416915144413267</v>
       </c>
       <c r="C58">
-        <v>545.7565755976702</v>
+        <v>2619.555252456428</v>
       </c>
       <c r="D58">
-        <v>3931.40057559767</v>
+        <v>6005.199252456428</v>
       </c>
       <c r="E58">
         <v>2351.644</v>
@@ -6037,45 +6037,45 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M58">
-        <v>550.5352299555666</v>
+        <v>327.1408755555666</v>
       </c>
       <c r="N58">
-        <v>-51.48420954740334</v>
+        <v>171.9101448525967</v>
       </c>
       <c r="O58">
-        <v>-12.87105238685083</v>
+        <v>42.97753621314916</v>
       </c>
       <c r="P58">
-        <v>-38.6131571605525</v>
+        <v>128.9326086394475</v>
       </c>
       <c r="Q58">
-        <v>219.8868428394475</v>
+        <v>387.4326086394475</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.138433646357878</v>
+        <v>0.1369995011463309</v>
       </c>
       <c r="T58">
-        <v>1.855800176355461</v>
+        <v>1.827971791070286</v>
       </c>
       <c r="U58">
-        <v>0.1357889784279692</v>
+        <v>0.08068897842796925</v>
       </c>
       <c r="V58">
-        <v>0.2266208378928091</v>
+        <v>0.25</v>
       </c>
       <c r="W58">
-        <v>0.1050163663600143</v>
+        <v>0.06051673382097694</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y58">
-        <v>0.9064833515712363</v>
+        <v>1.525492708792964</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6086,13 +6086,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.120619859343354</v>
+        <v>0.1002701682576204</v>
       </c>
       <c r="C59">
-        <v>426.0729743308275</v>
+        <v>1874.534471038395</v>
       </c>
       <c r="D59">
-        <v>3884.115974330828</v>
+        <v>5332.577471038396</v>
       </c>
       <c r="E59">
         <v>2424.043000000001</v>
@@ -6119,45 +6119,45 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M59">
-        <v>560.3662162047732</v>
+        <v>391.5824275047732</v>
       </c>
       <c r="N59">
-        <v>-61.31519579660994</v>
+        <v>107.4685929033901</v>
       </c>
       <c r="O59">
-        <v>-15.32879894915249</v>
+        <v>26.86714822584752</v>
       </c>
       <c r="P59">
-        <v>-45.98639684745746</v>
+        <v>80.60144467754255</v>
       </c>
       <c r="Q59">
-        <v>212.5136031525425</v>
+        <v>339.1014446775425</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.1405879172034101</v>
+        <v>0.1388491394875896</v>
       </c>
       <c r="T59">
-        <v>1.898958319991635</v>
+        <v>1.865045313063329</v>
       </c>
       <c r="U59">
-        <v>0.1357889784279692</v>
+        <v>0.09488897842796926</v>
       </c>
       <c r="V59">
-        <v>0.222645033719251</v>
+        <v>0.25</v>
       </c>
       <c r="W59">
-        <v>0.1055562367471714</v>
+        <v>0.07116673382097694</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y59">
-        <v>0.8905801348770039</v>
+        <v>1.274446924465424</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6168,13 +6168,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.1215197491276337</v>
+        <v>0.1004071850711081</v>
       </c>
       <c r="C60">
-        <v>307.5132787853881</v>
+        <v>1788.755312881432</v>
       </c>
       <c r="D60">
-        <v>3837.955278785388</v>
+        <v>5319.197312881432</v>
       </c>
       <c r="E60">
         <v>2496.442</v>
@@ -6201,45 +6201,45 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M60">
-        <v>570.1972024539796</v>
+        <v>398.4522946539797</v>
       </c>
       <c r="N60">
-        <v>-71.14618204581632</v>
+        <v>100.5987257541836</v>
       </c>
       <c r="O60">
-        <v>-17.78654551145408</v>
+        <v>25.1496814385459</v>
       </c>
       <c r="P60">
-        <v>-53.35963653436224</v>
+        <v>75.44904431563769</v>
       </c>
       <c r="Q60">
-        <v>205.1403634656378</v>
+        <v>333.9490443156377</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.1428447723749198</v>
+        <v>0.1407868558450988</v>
       </c>
       <c r="T60">
-        <v>1.944171613324769</v>
+        <v>1.903884240865564</v>
       </c>
       <c r="U60">
-        <v>0.1357889784279692</v>
+        <v>0.09488897842796926</v>
       </c>
       <c r="V60">
-        <v>0.2188063262413329</v>
+        <v>0.25</v>
       </c>
       <c r="W60">
-        <v>0.1060774909140817</v>
+        <v>0.07116673382097694</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y60">
-        <v>0.8752253049653317</v>
+        <v>1.252473701629814</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6250,13 +6250,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.1224196389119134</v>
+        <v>0.1145526968201056</v>
       </c>
       <c r="C61">
-        <v>190.0378884897909</v>
+        <v>621.9589791815479</v>
       </c>
       <c r="D61">
-        <v>3792.87888848979</v>
+        <v>4224.799979181547</v>
       </c>
       <c r="E61">
         <v>2568.840999999999</v>
@@ -6283,37 +6283,37 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M61">
-        <v>580.0281887031861</v>
+        <v>527.4882344031862</v>
       </c>
       <c r="N61">
-        <v>-80.97716829502281</v>
+        <v>-28.43721399502294</v>
       </c>
       <c r="O61">
-        <v>-20.2442920737557</v>
+        <v>-7.109303498755736</v>
       </c>
       <c r="P61">
-        <v>-60.73287622126711</v>
+        <v>-21.32791049626721</v>
       </c>
       <c r="Q61">
-        <v>197.7671237787329</v>
+        <v>237.1720895037328</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.1452117180426008</v>
+        <v>0.1437240544040451</v>
       </c>
       <c r="T61">
-        <v>1.991590433161958</v>
+        <v>1.962756450066702</v>
       </c>
       <c r="U61">
-        <v>0.1357889784279692</v>
+        <v>0.1234889784279693</v>
       </c>
       <c r="V61">
-        <v>0.2150977444406324</v>
+        <v>0.2365223467840958</v>
       </c>
       <c r="W61">
-        <v>0.1065810754482154</v>
+        <v>0.0942810754482154</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.8603909777625296</v>
+        <v>0.9460893871363831</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6332,13 +6332,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.1233195286961931</v>
+        <v>0.1153295866043853</v>
       </c>
       <c r="C62">
-        <v>73.60904178962846</v>
+        <v>502.3541189895896</v>
       </c>
       <c r="D62">
-        <v>3748.849041789628</v>
+        <v>4177.594118989589</v>
       </c>
       <c r="E62">
         <v>2641.24</v>
@@ -6365,37 +6365,37 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M62">
-        <v>589.8591749523927</v>
+        <v>536.4287129523927</v>
       </c>
       <c r="N62">
-        <v>-90.80815454422941</v>
+        <v>-37.37769254422949</v>
       </c>
       <c r="O62">
-        <v>-22.70203863605735</v>
+        <v>-9.344423136057372</v>
       </c>
       <c r="P62">
-        <v>-68.10611590817206</v>
+        <v>-28.03326940817212</v>
       </c>
       <c r="Q62">
-        <v>190.3938840918279</v>
+        <v>230.4667305918279</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.1476970109936658</v>
+        <v>0.1461721557641463</v>
       </c>
       <c r="T62">
-        <v>2.041380193991007</v>
+        <v>2.01182536131837</v>
       </c>
       <c r="U62">
-        <v>0.1357889784279692</v>
+        <v>0.1234889784279693</v>
       </c>
       <c r="V62">
-        <v>0.2115127820332885</v>
+        <v>0.2325803076710275</v>
       </c>
       <c r="W62">
-        <v>0.1070678738312113</v>
+        <v>0.0947678738312113</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.846051128133154</v>
+        <v>0.9303212306841101</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6414,13 +6414,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.1242194184804728</v>
+        <v>0.116106476388665</v>
       </c>
       <c r="C63">
-        <v>-41.80928965763724</v>
+        <v>383.7925126321297</v>
       </c>
       <c r="D63">
-        <v>3705.829710342363</v>
+        <v>4131.43151263213</v>
       </c>
       <c r="E63">
         <v>2713.639</v>
@@ -6447,37 +6447,37 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M63">
-        <v>599.6901612015993</v>
+        <v>545.3691915015994</v>
       </c>
       <c r="N63">
-        <v>-100.639140793436</v>
+        <v>-46.31817109343615</v>
       </c>
       <c r="O63">
-        <v>-25.159785198359</v>
+        <v>-11.57954277335904</v>
       </c>
       <c r="P63">
-        <v>-75.47935559507701</v>
+        <v>-34.73862832007711</v>
       </c>
       <c r="Q63">
-        <v>183.020644404923</v>
+        <v>223.7613716799229</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.1503097548652983</v>
+        <v>0.1487458007837398</v>
       </c>
       <c r="T63">
-        <v>2.093723275888212</v>
+        <v>2.0634106269932</v>
       </c>
       <c r="U63">
-        <v>0.1357889784279692</v>
+        <v>0.1234889784279693</v>
       </c>
       <c r="V63">
-        <v>0.2080453593770051</v>
+        <v>0.2287675157419942</v>
       </c>
       <c r="W63">
-        <v>0.107538711611486</v>
+        <v>0.09523871161148602</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.8321814375080202</v>
+        <v>0.915070062967977</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6496,13 +6496,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.1251193082647525</v>
+        <v>0.1168833661729447</v>
       </c>
       <c r="C64">
-        <v>-156.2514992061379</v>
+        <v>266.2399540794031</v>
       </c>
       <c r="D64">
-        <v>3663.786500793861</v>
+        <v>4086.277954079402</v>
       </c>
       <c r="E64">
         <v>2786.038</v>
@@ -6529,37 +6529,37 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M64">
-        <v>609.5211474508058</v>
+        <v>554.3096700508058</v>
       </c>
       <c r="N64">
-        <v>-110.4701270426425</v>
+        <v>-55.25864964264258</v>
       </c>
       <c r="O64">
-        <v>-27.61753176066063</v>
+        <v>-13.81466241066065</v>
       </c>
       <c r="P64">
-        <v>-82.85259528198188</v>
+        <v>-41.44398723198194</v>
       </c>
       <c r="Q64">
-        <v>175.6474047180181</v>
+        <v>217.0560127680181</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.1530600115722798</v>
+        <v>0.1514549008043645</v>
       </c>
       <c r="T64">
-        <v>2.148821256832639</v>
+        <v>2.117710906650915</v>
       </c>
       <c r="U64">
-        <v>0.1357889784279692</v>
+        <v>0.1234889784279693</v>
       </c>
       <c r="V64">
-        <v>0.2046897890644727</v>
+        <v>0.2250777171009944</v>
       </c>
       <c r="W64">
-        <v>0.107994361076268</v>
+        <v>0.09569436107626801</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.818759156257891</v>
+        <v>0.9003108684039776</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6578,13 +6578,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.1260191980490322</v>
+        <v>0.1176602559572243</v>
       </c>
       <c r="C65">
-        <v>-269.7504369271692</v>
+        <v>149.6637165234806</v>
       </c>
       <c r="D65">
-        <v>3622.68656307283</v>
+        <v>4042.100716523481</v>
       </c>
       <c r="E65">
         <v>2858.437</v>
@@ -6611,37 +6611,37 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M65">
-        <v>619.3521337000124</v>
+        <v>563.2501486000125</v>
       </c>
       <c r="N65">
-        <v>-120.3011132918491</v>
+        <v>-64.19912819184924</v>
       </c>
       <c r="O65">
-        <v>-30.07527832296228</v>
+        <v>-16.04978204796231</v>
       </c>
       <c r="P65">
-        <v>-90.22583496888683</v>
+        <v>-48.14934614388693</v>
       </c>
       <c r="Q65">
-        <v>168.2741650311132</v>
+        <v>210.3506538561131</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.1559589308039631</v>
+        <v>0.1543104386639419</v>
       </c>
       <c r="T65">
-        <v>2.206897507017305</v>
+        <v>2.174946336560399</v>
       </c>
       <c r="U65">
-        <v>0.1357889784279692</v>
+        <v>0.1234889784279693</v>
       </c>
       <c r="V65">
-        <v>0.2014407447936081</v>
+        <v>0.2215050549247881</v>
       </c>
       <c r="W65">
-        <v>0.1084355454786759</v>
+        <v>0.09613554547867596</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.8057629791744323</v>
+        <v>0.8860202196991523</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6660,13 +6660,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.1835342549825239</v>
+        <v>0.118437145741504</v>
       </c>
       <c r="C66">
-        <v>-1854.910543115071</v>
+        <v>34.03247327328336</v>
       </c>
       <c r="D66">
-        <v>2109.925456884929</v>
+        <v>3998.868473273283</v>
       </c>
       <c r="E66">
         <v>2930.836</v>
@@ -6693,45 +6693,45 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M66">
-        <v>1022.570326349219</v>
+        <v>572.190627149219</v>
       </c>
       <c r="N66">
-        <v>-523.5193059410558</v>
+        <v>-73.13960674105579</v>
       </c>
       <c r="O66">
-        <v>-130.8798264852639</v>
+        <v>-18.28490168526395</v>
       </c>
       <c r="P66">
-        <v>-392.6394794557918</v>
+        <v>-54.85470505579184</v>
       </c>
       <c r="Q66">
-        <v>-134.1394794557918</v>
+        <v>203.6452949442082</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.1653499209629955</v>
+        <v>0.1573246175157181</v>
       </c>
       <c r="T66">
-        <v>2.39503434366902</v>
+        <v>2.235361512575966</v>
       </c>
       <c r="U66">
-        <v>0.2206889784279693</v>
+        <v>0.1234889784279693</v>
       </c>
       <c r="V66">
-        <v>0.122008972769109</v>
+        <v>0.2180440384415883</v>
       </c>
       <c r="W66">
-        <v>0.1937629428685087</v>
+        <v>0.09656294286850868</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y66">
-        <v>0.4880358910764362</v>
+        <v>0.872176153766353</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6742,13 +6742,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.1852831447668036</v>
+        <v>0.1192140355257837</v>
       </c>
       <c r="C67">
-        <v>-1953.764546573066</v>
+        <v>-80.68377632775537</v>
       </c>
       <c r="D67">
-        <v>2083.470453426934</v>
+        <v>3956.551223672244</v>
       </c>
       <c r="E67">
         <v>3003.235</v>
@@ -6775,45 +6775,45 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M67">
-        <v>1038.547987698425</v>
+        <v>581.1311056984255</v>
       </c>
       <c r="N67">
-        <v>-539.4969672902622</v>
+        <v>-82.08008529026222</v>
       </c>
       <c r="O67">
-        <v>-134.8742418225656</v>
+        <v>-20.52002132256555</v>
       </c>
       <c r="P67">
-        <v>-404.6227254676967</v>
+        <v>-61.56006396769666</v>
       </c>
       <c r="Q67">
-        <v>-146.1227254676967</v>
+        <v>196.9399360323033</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.1687656329905097</v>
+        <v>0.1605110351590243</v>
       </c>
       <c r="T67">
-        <v>2.463463896345278</v>
+        <v>2.299228984363851</v>
       </c>
       <c r="U67">
-        <v>0.2206889784279693</v>
+        <v>0.1234889784279693</v>
       </c>
       <c r="V67">
-        <v>0.1201319116495843</v>
+        <v>0.2146895147732562</v>
       </c>
       <c r="W67">
-        <v>0.1941771895694235</v>
+        <v>0.09697718956942346</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y67">
-        <v>0.4805276465983372</v>
+        <v>0.8587580590930247</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6824,13 +6824,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.1870320345510833</v>
+        <v>0.1199909253100634</v>
       </c>
       <c r="C68">
-        <v>-2051.963360357729</v>
+        <v>-194.5137763294952</v>
       </c>
       <c r="D68">
-        <v>2057.670639642271</v>
+        <v>3915.120223670504</v>
       </c>
       <c r="E68">
         <v>3075.634</v>
@@ -6857,45 +6857,45 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M68">
-        <v>1054.525649047632</v>
+        <v>590.0715842476321</v>
       </c>
       <c r="N68">
-        <v>-555.474628639469</v>
+        <v>-91.02056383946888</v>
       </c>
       <c r="O68">
-        <v>-138.8686571598672</v>
+        <v>-22.75514095986722</v>
       </c>
       <c r="P68">
-        <v>-416.6059714796017</v>
+        <v>-68.26542287960166</v>
       </c>
       <c r="Q68">
-        <v>-158.1059714796017</v>
+        <v>190.2345771203983</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.1723822692549364</v>
+        <v>0.1638848891342897</v>
       </c>
       <c r="T68">
-        <v>2.535918716826021</v>
+        <v>2.366853366256906</v>
       </c>
       <c r="U68">
-        <v>0.2206889784279693</v>
+        <v>0.1234889784279693</v>
       </c>
       <c r="V68">
-        <v>0.1183117311700451</v>
+        <v>0.2114366433372977</v>
       </c>
       <c r="W68">
-        <v>0.1945788833400075</v>
+        <v>0.09737888334000748</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y68">
-        <v>0.4732469246801805</v>
+        <v>0.8457465733491909</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6906,13 +6906,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.188780924335363</v>
+        <v>0.1207678150943431</v>
       </c>
       <c r="C69">
-        <v>-2149.531026582336</v>
+        <v>-307.4850792860216</v>
       </c>
       <c r="D69">
-        <v>2032.501973417664</v>
+        <v>3874.547920713979</v>
       </c>
       <c r="E69">
         <v>3148.033</v>
@@ -6939,45 +6939,45 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M69">
-        <v>1070.503310396839</v>
+        <v>599.0120627968387</v>
       </c>
       <c r="N69">
-        <v>-571.4522899886755</v>
+        <v>-99.96104238867542</v>
       </c>
       <c r="O69">
-        <v>-142.8630724971689</v>
+        <v>-24.99026059716886</v>
       </c>
       <c r="P69">
-        <v>-428.5892174915066</v>
+        <v>-74.97078179150657</v>
       </c>
       <c r="Q69">
-        <v>-170.0892174915066</v>
+        <v>183.5292182084934</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.1762180955959951</v>
+        <v>0.1674632191080561</v>
       </c>
       <c r="T69">
-        <v>2.612764738548023</v>
+        <v>2.438576195537418</v>
       </c>
       <c r="U69">
-        <v>0.2206889784279693</v>
+        <v>0.1234889784279693</v>
       </c>
       <c r="V69">
-        <v>0.1165458844361639</v>
+        <v>0.2082808725412186</v>
       </c>
       <c r="W69">
-        <v>0.1949685862517681</v>
+        <v>0.09776858625176811</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y69">
-        <v>0.4661835377446554</v>
+        <v>0.8331234901648745</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6988,13 +6988,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.1905298141196427</v>
+        <v>0.1215447048786228</v>
       </c>
       <c r="C70">
-        <v>-2246.490425277384</v>
+        <v>-419.6241073596457</v>
       </c>
       <c r="D70">
-        <v>2007.941574722617</v>
+        <v>3834.807892640355</v>
       </c>
       <c r="E70">
         <v>3220.432000000001</v>
@@ -7021,45 +7021,45 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M70">
-        <v>1086.480971746045</v>
+        <v>607.9525413460452</v>
       </c>
       <c r="N70">
-        <v>-587.429951337882</v>
+        <v>-108.901520937882</v>
       </c>
       <c r="O70">
-        <v>-146.8574878344705</v>
+        <v>-27.22538023447049</v>
       </c>
       <c r="P70">
-        <v>-440.5724635034115</v>
+        <v>-81.67614070341148</v>
       </c>
       <c r="Q70">
-        <v>-182.0724635034115</v>
+        <v>176.8238592965885</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.18029366108337</v>
+        <v>0.1712651947051828</v>
       </c>
       <c r="T70">
-        <v>2.694413636627648</v>
+        <v>2.514781701647963</v>
       </c>
       <c r="U70">
-        <v>0.2206889784279693</v>
+        <v>0.1234889784279693</v>
       </c>
       <c r="V70">
-        <v>0.1148319743709262</v>
+        <v>0.2052179185332595</v>
       </c>
       <c r="W70">
-        <v>0.1953468273131828</v>
+        <v>0.09814682731318283</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y70">
-        <v>0.4593278974837046</v>
+        <v>0.8208716741330382</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7070,13 +7070,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1922787039039224</v>
+        <v>0.1223215946629025</v>
       </c>
       <c r="C71">
-        <v>-2342.863343764307</v>
+        <v>-530.9562097027374</v>
       </c>
       <c r="D71">
-        <v>1983.967656235693</v>
+        <v>3795.874790297262</v>
       </c>
       <c r="E71">
         <v>3292.831</v>
@@ -7103,45 +7103,45 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M71">
-        <v>1102.458633095252</v>
+        <v>616.8930198952518</v>
       </c>
       <c r="N71">
-        <v>-603.4076126870885</v>
+        <v>-117.8419994870885</v>
       </c>
       <c r="O71">
-        <v>-150.8519031717721</v>
+        <v>-29.46049987177213</v>
       </c>
       <c r="P71">
-        <v>-452.5557095153164</v>
+        <v>-88.38149961531639</v>
       </c>
       <c r="Q71">
-        <v>-194.0557095153164</v>
+        <v>170.1185003846836</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.1846321662796077</v>
+        <v>0.1753124590505113</v>
       </c>
       <c r="T71">
-        <v>2.781330205551121</v>
+        <v>2.595903692023704</v>
       </c>
       <c r="U71">
-        <v>0.2206889784279693</v>
+        <v>0.1234889784279693</v>
       </c>
       <c r="V71">
-        <v>0.113167742858304</v>
+        <v>0.2022437458008935</v>
       </c>
       <c r="W71">
-        <v>0.1957141048655711</v>
+        <v>0.09851410486557104</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y71">
-        <v>0.4526709714332161</v>
+        <v>0.8089749832035739</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7152,13 +7152,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1940275936882021</v>
+        <v>0.1832406305389493</v>
       </c>
       <c r="C72">
-        <v>-2438.670541118105</v>
+        <v>-2285.834630994167</v>
       </c>
       <c r="D72">
-        <v>1960.559458881896</v>
+        <v>2113.395369005833</v>
       </c>
       <c r="E72">
         <v>3365.23</v>
@@ -7185,37 +7185,37 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M72">
-        <v>1118.436294444458</v>
+        <v>1042.417344444458</v>
       </c>
       <c r="N72">
-        <v>-619.3852740362951</v>
+        <v>-543.3663240362952</v>
       </c>
       <c r="O72">
-        <v>-154.8463185090738</v>
+        <v>-135.8415810090738</v>
       </c>
       <c r="P72">
-        <v>-464.5389555272213</v>
+        <v>-407.5247430272213</v>
       </c>
       <c r="Q72">
-        <v>-206.0389555272213</v>
+        <v>-149.0247430272213</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.1892599051555947</v>
+        <v>0.1883033613247521</v>
       </c>
       <c r="T72">
-        <v>2.874041212402825</v>
+        <v>2.856288920006043</v>
       </c>
       <c r="U72">
-        <v>0.2206889784279693</v>
+        <v>0.2056889784279693</v>
       </c>
       <c r="V72">
-        <v>0.1115510608174711</v>
+        <v>0.1196859931072342</v>
       </c>
       <c r="W72">
-        <v>0.1960708887736053</v>
+        <v>0.1810708887736053</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.4462042432698845</v>
+        <v>0.4787439724289367</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7234,13 +7234,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.1957764834724818</v>
+        <v>0.184839520323229</v>
       </c>
       <c r="C73">
-        <v>-2533.93180811972</v>
+        <v>-2382.536694308769</v>
       </c>
       <c r="D73">
-        <v>1937.697191880279</v>
+        <v>2089.092305691231</v>
       </c>
       <c r="E73">
         <v>3437.629</v>
@@ -7267,37 +7267,37 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M73">
-        <v>1134.413955793665</v>
+        <v>1057.309020793665</v>
       </c>
       <c r="N73">
-        <v>-635.3629353855016</v>
+        <v>-558.2580003855015</v>
       </c>
       <c r="O73">
-        <v>-158.8407338463754</v>
+        <v>-139.5645000963754</v>
       </c>
       <c r="P73">
-        <v>-476.5222015391262</v>
+        <v>-418.6935002891262</v>
       </c>
       <c r="Q73">
-        <v>-218.0222015391262</v>
+        <v>-160.1935002891262</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.194206798436822</v>
+        <v>0.1932172703359504</v>
       </c>
       <c r="T73">
-        <v>2.973146081796024</v>
+        <v>2.95478164138556</v>
       </c>
       <c r="U73">
-        <v>0.2206889784279693</v>
+        <v>0.2056889784279693</v>
       </c>
       <c r="V73">
-        <v>0.1099799191158166</v>
+        <v>0.1180002748944563</v>
       </c>
       <c r="W73">
-        <v>0.196417622430709</v>
+        <v>0.181417622430709</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.4399196764632665</v>
+        <v>0.472001099577825</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7316,13 +7316,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.1975253732567614</v>
+        <v>0.1864384101075087</v>
       </c>
       <c r="C74">
-        <v>-2628.666023062127</v>
+        <v>-2478.686164350584</v>
       </c>
       <c r="D74">
-        <v>1915.361976937872</v>
+        <v>2065.341835649415</v>
       </c>
       <c r="E74">
         <v>3510.027999999999</v>
@@ -7349,37 +7349,37 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M74">
-        <v>1150.391617142871</v>
+        <v>1072.200697142871</v>
       </c>
       <c r="N74">
-        <v>-651.3405967347079</v>
+        <v>-573.1496767347079</v>
       </c>
       <c r="O74">
-        <v>-162.835149183677</v>
+        <v>-143.287419183677</v>
       </c>
       <c r="P74">
-        <v>-488.5054475510309</v>
+        <v>-429.8622575510309</v>
       </c>
       <c r="Q74">
-        <v>-230.0054475510309</v>
+        <v>-171.3622575510309</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.1995070412381371</v>
+        <v>0.1984821728479486</v>
       </c>
       <c r="T74">
-        <v>3.079329870431597</v>
+        <v>3.06030955714933</v>
       </c>
       <c r="U74">
-        <v>0.2206889784279693</v>
+        <v>0.2056889784279693</v>
       </c>
       <c r="V74">
-        <v>0.1084524202392081</v>
+        <v>0.1163613821875888</v>
       </c>
       <c r="W74">
-        <v>0.1967547245973376</v>
+        <v>0.1817547245973376</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.4338096809568323</v>
+        <v>0.4654455287503553</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7398,13 +7398,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.1992742630410412</v>
+        <v>0.1880372998917884</v>
       </c>
       <c r="C75">
-        <v>-2722.891203740831</v>
+        <v>-2574.301676226004</v>
       </c>
       <c r="D75">
-        <v>1893.535796259169</v>
+        <v>2042.125323773995</v>
       </c>
       <c r="E75">
         <v>3582.427</v>
@@ -7431,37 +7431,37 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M75">
-        <v>1166.369278492078</v>
+        <v>1087.092373492078</v>
       </c>
       <c r="N75">
-        <v>-667.3182580839147</v>
+        <v>-588.0413530839145</v>
       </c>
       <c r="O75">
-        <v>-166.8295645209787</v>
+        <v>-147.0103382709786</v>
       </c>
       <c r="P75">
-        <v>-500.488693562936</v>
+        <v>-441.0310148129358</v>
       </c>
       <c r="Q75">
-        <v>-241.988693562936</v>
+        <v>-182.5310148129358</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.2051998946173273</v>
+        <v>0.2041370681386134</v>
       </c>
       <c r="T75">
-        <v>3.193379124892027</v>
+        <v>3.173654355562268</v>
       </c>
       <c r="U75">
-        <v>0.2206889784279693</v>
+        <v>0.2056889784279693</v>
       </c>
       <c r="V75">
-        <v>0.1069667706468901</v>
+        <v>0.1147673906507725</v>
       </c>
       <c r="W75">
-        <v>0.1970825910881682</v>
+        <v>0.1820825910881682</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.4278670825875605</v>
+        <v>0.4590695626030902</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7480,13 +7480,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.2010231528253208</v>
+        <v>0.1896361896760681</v>
       </c>
       <c r="C76">
-        <v>-2816.624555929722</v>
+        <v>-2669.401036446576</v>
       </c>
       <c r="D76">
-        <v>1872.201444070278</v>
+        <v>2019.424963553424</v>
       </c>
       <c r="E76">
         <v>3654.826</v>
@@ -7513,37 +7513,37 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M76">
-        <v>1182.346939841284</v>
+        <v>1101.984049841284</v>
       </c>
       <c r="N76">
-        <v>-683.2959194331212</v>
+        <v>-602.9330294331211</v>
       </c>
       <c r="O76">
-        <v>-170.8239798582803</v>
+        <v>-150.7332573582803</v>
       </c>
       <c r="P76">
-        <v>-512.4719395748409</v>
+        <v>-452.1997720748408</v>
       </c>
       <c r="Q76">
-        <v>-253.9719395748409</v>
+        <v>-193.6997720748408</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.2113306597949168</v>
+        <v>0.2102269553747139</v>
       </c>
       <c r="T76">
-        <v>3.316201398926335</v>
+        <v>3.295717984622356</v>
       </c>
       <c r="U76">
-        <v>0.2206889784279693</v>
+        <v>0.2056889784279693</v>
       </c>
       <c r="V76">
-        <v>0.1055212737462565</v>
+        <v>0.1132164799663026</v>
       </c>
       <c r="W76">
-        <v>0.1974015963224898</v>
+        <v>0.1824015963224898</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.4220850949850259</v>
+        <v>0.4528659198652105</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7562,13 +7562,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.2027720426096006</v>
+        <v>0.1912350794603478</v>
       </c>
       <c r="C77">
-        <v>-2909.882518616419</v>
+        <v>-2764.001268476192</v>
       </c>
       <c r="D77">
-        <v>1851.342481383581</v>
+        <v>1997.223731523807</v>
       </c>
       <c r="E77">
         <v>3727.224999999999</v>
@@ -7595,37 +7595,37 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M77">
-        <v>1198.324601190491</v>
+        <v>1116.875726190491</v>
       </c>
       <c r="N77">
-        <v>-699.2735807823277</v>
+        <v>-617.8247057823277</v>
       </c>
       <c r="O77">
-        <v>-174.8183951955819</v>
+        <v>-154.4561764455819</v>
       </c>
       <c r="P77">
-        <v>-524.4551855867458</v>
+        <v>-463.3685293367457</v>
       </c>
       <c r="Q77">
-        <v>-265.9551855867458</v>
+        <v>-204.8685293367457</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.2179518861867135</v>
+        <v>0.2168040335897025</v>
       </c>
       <c r="T77">
-        <v>3.448849454883388</v>
+        <v>3.427546704007251</v>
       </c>
       <c r="U77">
-        <v>0.2206889784279693</v>
+        <v>0.2056889784279693</v>
       </c>
       <c r="V77">
-        <v>0.1041143234296397</v>
+        <v>0.1117069269000853</v>
       </c>
       <c r="W77">
-        <v>0.1977120947505629</v>
+        <v>0.1827120947505629</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.4164572937185589</v>
+        <v>0.4468277076003411</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7644,13 +7644,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.2045209323938803</v>
+        <v>0.1928339692446275</v>
       </c>
       <c r="C78">
-        <v>-3002.680806246987</v>
+        <v>-2858.118655306527</v>
       </c>
       <c r="D78">
-        <v>1830.943193753012</v>
+        <v>1975.505344693472</v>
       </c>
       <c r="E78">
         <v>3799.624</v>
@@ -7677,37 +7677,37 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M78">
-        <v>1214.302262539697</v>
+        <v>1131.767402539698</v>
       </c>
       <c r="N78">
-        <v>-715.2512421315342</v>
+        <v>-632.7163821315343</v>
       </c>
       <c r="O78">
-        <v>-178.8128105328836</v>
+        <v>-158.1790955328836</v>
       </c>
       <c r="P78">
-        <v>-536.4384315986507</v>
+        <v>-474.5372865986507</v>
       </c>
       <c r="Q78">
-        <v>-277.9384315986507</v>
+        <v>-216.0372865986507</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.2251248814444933</v>
+        <v>0.2239292016559401</v>
       </c>
       <c r="T78">
-        <v>3.59255151550353</v>
+        <v>3.570361150007553</v>
       </c>
       <c r="U78">
-        <v>0.2206889784279693</v>
+        <v>0.2056889784279693</v>
       </c>
       <c r="V78">
-        <v>0.102744398121355</v>
+        <v>0.1102370989145578</v>
       </c>
       <c r="W78">
-        <v>0.1980144221673709</v>
+        <v>0.1830144221673709</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.41097759248542</v>
+        <v>0.4409483956582313</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7726,13 +7726,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.20626982217816</v>
+        <v>0.1944328590289072</v>
       </c>
       <c r="C79">
-        <v>-3095.03444820824</v>
+        <v>-2951.768779284476</v>
       </c>
       <c r="D79">
-        <v>1810.98855179176</v>
+        <v>1954.254220715523</v>
       </c>
       <c r="E79">
         <v>3872.023</v>
@@ -7759,37 +7759,37 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M79">
-        <v>1230.279923888904</v>
+        <v>1146.659078888904</v>
       </c>
       <c r="N79">
-        <v>-731.228903480741</v>
+        <v>-647.6080584807409</v>
       </c>
       <c r="O79">
-        <v>-182.8072258701852</v>
+        <v>-161.9020146201852</v>
       </c>
       <c r="P79">
-        <v>-548.4216776105558</v>
+        <v>-485.7060438605556</v>
       </c>
       <c r="Q79">
-        <v>-289.9216776105558</v>
+        <v>-227.2060438605556</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.2329216154203408</v>
+        <v>0.2316739495540245</v>
       </c>
       <c r="T79">
-        <v>3.748749407481945</v>
+        <v>3.725594243486142</v>
       </c>
       <c r="U79">
-        <v>0.2206889784279693</v>
+        <v>0.2056889784279693</v>
       </c>
       <c r="V79">
-        <v>0.1014100552886101</v>
+        <v>0.1088054482793038</v>
       </c>
       <c r="W79">
-        <v>0.198308896924002</v>
+        <v>0.183308896924002</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.4056402211544404</v>
+        <v>0.4352217931172153</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7808,13 +7808,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.2080187119624397</v>
+        <v>0.1960317488131869</v>
       </c>
       <c r="C80">
-        <v>-3186.957825756063</v>
+        <v>-3044.96655939635</v>
       </c>
       <c r="D80">
-        <v>1791.464174243937</v>
+        <v>1933.45544060365</v>
       </c>
       <c r="E80">
         <v>3944.422</v>
@@ -7841,37 +7841,37 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M80">
-        <v>1246.257585238111</v>
+        <v>1161.550755238111</v>
       </c>
       <c r="N80">
-        <v>-747.2065648299475</v>
+        <v>-662.4997348299474</v>
       </c>
       <c r="O80">
-        <v>-186.8016412074869</v>
+        <v>-165.6249337074869</v>
       </c>
       <c r="P80">
-        <v>-560.4049236224606</v>
+        <v>-496.8748011224606</v>
       </c>
       <c r="Q80">
-        <v>-301.9049236224606</v>
+        <v>-238.3748011224606</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.2414271433939927</v>
+        <v>0.2401227654428438</v>
       </c>
       <c r="T80">
-        <v>3.919147107822033</v>
+        <v>3.894939436371876</v>
       </c>
       <c r="U80">
-        <v>0.2206889784279693</v>
+        <v>0.2056889784279693</v>
       </c>
       <c r="V80">
-        <v>0.1001099263746536</v>
+        <v>0.1074105066346974</v>
       </c>
       <c r="W80">
-        <v>0.1985958210458478</v>
+        <v>0.1835958210458478</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.4004397054986143</v>
+        <v>0.4296420265387895</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7890,13 +7890,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.2097676017467194</v>
+        <v>0.1976306385974665</v>
       </c>
       <c r="C81">
-        <v>-3278.464706580457</v>
+        <v>-3137.726286196274</v>
       </c>
       <c r="D81">
-        <v>1772.356293419542</v>
+        <v>1913.094713803726</v>
       </c>
       <c r="E81">
         <v>4016.821</v>
@@ -7923,37 +7923,37 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M81">
-        <v>1262.235246587317</v>
+        <v>1176.442431587317</v>
       </c>
       <c r="N81">
-        <v>-763.1842261791541</v>
+        <v>-677.3914111791538</v>
       </c>
       <c r="O81">
-        <v>-190.7960565447885</v>
+        <v>-169.3478527947885</v>
       </c>
       <c r="P81">
-        <v>-572.3881696343656</v>
+        <v>-508.0435583843654</v>
       </c>
       <c r="Q81">
-        <v>-313.8881696343656</v>
+        <v>-249.5435583843654</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.2507427216508495</v>
+        <v>0.2493762304639316</v>
       </c>
       <c r="T81">
-        <v>4.105773160575464</v>
+        <v>4.080412742865775</v>
       </c>
       <c r="U81">
-        <v>0.2206889784279693</v>
+        <v>0.2056889784279693</v>
       </c>
       <c r="V81">
-        <v>0.09884271211674656</v>
+        <v>0.1060508799684354</v>
       </c>
       <c r="W81">
-        <v>0.1988754812658746</v>
+        <v>0.1838754812658746</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3953708484669862</v>
+        <v>0.4242035198737415</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7972,13 +7972,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.2115164915309991</v>
+        <v>0.1992295283817462</v>
       </c>
       <c r="C82">
-        <v>-3369.568277181903</v>
+        <v>-3230.061654550673</v>
       </c>
       <c r="D82">
-        <v>1753.651722818097</v>
+        <v>1893.158345449327</v>
       </c>
       <c r="E82">
         <v>4089.22</v>
@@ -8005,37 +8005,37 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M82">
-        <v>1278.212907936524</v>
+        <v>1191.334107936524</v>
       </c>
       <c r="N82">
-        <v>-779.1618875283606</v>
+        <v>-692.2830875283604</v>
       </c>
       <c r="O82">
-        <v>-194.7904718820901</v>
+        <v>-173.0707718820901</v>
       </c>
       <c r="P82">
-        <v>-584.3714156462704</v>
+        <v>-519.2123156462703</v>
       </c>
       <c r="Q82">
-        <v>-325.8714156462704</v>
+        <v>-260.7123156462703</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.260989857733392</v>
+        <v>0.2595550419871281</v>
       </c>
       <c r="T82">
-        <v>4.311061818604237</v>
+        <v>4.284433380009063</v>
       </c>
       <c r="U82">
-        <v>0.2206889784279693</v>
+        <v>0.2056889784279693</v>
       </c>
       <c r="V82">
-        <v>0.09760717821528724</v>
+        <v>0.1047252439688299</v>
       </c>
       <c r="W82">
-        <v>0.1991481499804008</v>
+        <v>0.1841481499804008</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3904287128611489</v>
+        <v>0.4189009758753197</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8054,13 +8054,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2132653813152787</v>
+        <v>0.200828418166026</v>
       </c>
       <c r="C83">
-        <v>-3460.281173219001</v>
+        <v>-3321.985794356468</v>
       </c>
       <c r="D83">
-        <v>1735.337826780999</v>
+        <v>1873.633205643533</v>
       </c>
       <c r="E83">
         <v>4161.619000000001</v>
@@ -8087,37 +8087,37 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M83">
-        <v>1294.19056928573</v>
+        <v>1206.22578428573</v>
       </c>
       <c r="N83">
-        <v>-795.1395488775671</v>
+        <v>-707.1747638775672</v>
       </c>
       <c r="O83">
-        <v>-198.7848872193918</v>
+        <v>-176.7936909693918</v>
       </c>
       <c r="P83">
-        <v>-596.3546616581754</v>
+        <v>-530.3810729081754</v>
       </c>
       <c r="Q83">
-        <v>-337.8546616581754</v>
+        <v>-271.8810729081754</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.2723156397193599</v>
+        <v>0.2708053073548717</v>
       </c>
       <c r="T83">
-        <v>4.537959809057091</v>
+        <v>4.509929873693752</v>
       </c>
       <c r="U83">
-        <v>0.2206889784279693</v>
+        <v>0.2056889784279693</v>
       </c>
       <c r="V83">
-        <v>0.09640215132374048</v>
+        <v>0.1034323397223011</v>
       </c>
       <c r="W83">
-        <v>0.1994140861340745</v>
+        <v>0.1844140861340745</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3856086052949619</v>
+        <v>0.4137293588892046</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8136,13 +8136,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2150142710995584</v>
+        <v>0.2024273079503057</v>
       </c>
       <c r="C84">
-        <v>-3550.615507974223</v>
+        <v>-3413.511299377809</v>
       </c>
       <c r="D84">
-        <v>1717.402492025777</v>
+        <v>1854.506700622191</v>
       </c>
       <c r="E84">
         <v>4234.018</v>
@@ -8169,37 +8169,37 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M84">
-        <v>1310.168230634937</v>
+        <v>1221.117460634937</v>
       </c>
       <c r="N84">
-        <v>-811.1172102267736</v>
+        <v>-722.0664402267736</v>
       </c>
       <c r="O84">
-        <v>-202.7793025566934</v>
+        <v>-180.5166100566934</v>
       </c>
       <c r="P84">
-        <v>-608.3379076700802</v>
+        <v>-541.5498301700802</v>
       </c>
       <c r="Q84">
-        <v>-349.8379076700802</v>
+        <v>-283.0498301700802</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.284899841925991</v>
+        <v>0.2833056022079202</v>
       </c>
       <c r="T84">
-        <v>4.790068687338041</v>
+        <v>4.760481533343405</v>
       </c>
       <c r="U84">
-        <v>0.2206889784279693</v>
+        <v>0.2056889784279693</v>
       </c>
       <c r="V84">
-        <v>0.09522651533198755</v>
+        <v>0.1021709697256877</v>
       </c>
       <c r="W84">
-        <v>0.1996735360400976</v>
+        <v>0.1846735360400976</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3809060613279502</v>
+        <v>0.4086838789027509</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8218,13 +8218,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2167631608838381</v>
+        <v>0.2040261977345854</v>
       </c>
       <c r="C85">
-        <v>-3640.582899072474</v>
+        <v>-3504.650254334427</v>
       </c>
       <c r="D85">
-        <v>1699.834100927526</v>
+        <v>1835.766745665573</v>
       </c>
       <c r="E85">
         <v>4306.417</v>
@@ -8251,37 +8251,37 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M85">
-        <v>1326.145891984143</v>
+        <v>1236.009136984143</v>
       </c>
       <c r="N85">
-        <v>-827.0948715759802</v>
+        <v>-736.9581165759802</v>
       </c>
       <c r="O85">
-        <v>-206.773717893995</v>
+        <v>-184.239529143995</v>
       </c>
       <c r="P85">
-        <v>-620.3211536819852</v>
+        <v>-552.7185874319852</v>
       </c>
       <c r="Q85">
-        <v>-361.8211536819852</v>
+        <v>-294.2185874319852</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.2989645385098729</v>
+        <v>0.2972765199848567</v>
       </c>
       <c r="T85">
-        <v>5.071837433652044</v>
+        <v>5.040509858834193</v>
       </c>
       <c r="U85">
-        <v>0.2206889784279693</v>
+        <v>0.2056889784279693</v>
       </c>
       <c r="V85">
-        <v>0.09407920791834914</v>
+        <v>0.100939994186824</v>
       </c>
       <c r="W85">
-        <v>0.1999267341411563</v>
+        <v>0.1849267341411563</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3763168316733966</v>
+        <v>0.4037599767472961</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8300,13 +8300,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.2185120506681178</v>
+        <v>0.205625087518865</v>
       </c>
       <c r="C86">
-        <v>-3730.194493576345</v>
+        <v>-3595.414260364025</v>
       </c>
       <c r="D86">
-        <v>1682.621506423654</v>
+        <v>1817.401739635975</v>
       </c>
       <c r="E86">
         <v>4378.816</v>
@@ -8333,37 +8333,37 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M86">
-        <v>1342.12355333335</v>
+        <v>1250.90081333335</v>
       </c>
       <c r="N86">
-        <v>-843.0725329251867</v>
+        <v>-751.8497929251865</v>
       </c>
       <c r="O86">
-        <v>-210.7681332312967</v>
+        <v>-187.9624482312966</v>
       </c>
       <c r="P86">
-        <v>-632.30439969389</v>
+        <v>-563.8873446938899</v>
       </c>
       <c r="Q86">
-        <v>-373.80439969389</v>
+        <v>-305.3873446938899</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.3147873221667399</v>
+        <v>0.3129938024839101</v>
       </c>
       <c r="T86">
-        <v>5.388827273255295</v>
+        <v>5.355541725011328</v>
       </c>
       <c r="U86">
-        <v>0.2206889784279693</v>
+        <v>0.2056889784279693</v>
       </c>
       <c r="V86">
-        <v>0.09295921734789261</v>
+        <v>0.09973832758936185</v>
       </c>
       <c r="W86">
-        <v>0.2001739037159993</v>
+        <v>0.1851739037159993</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3718368693915705</v>
+        <v>0.3989533103574474</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8382,13 +8382,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.2202609404523975</v>
+        <v>0.2072239773031447</v>
       </c>
       <c r="C87">
-        <v>-3819.460991571957</v>
+        <v>-3685.81445897146</v>
       </c>
       <c r="D87">
-        <v>1665.754008428042</v>
+        <v>1799.40054102854</v>
       </c>
       <c r="E87">
         <v>4451.215</v>
@@ -8415,37 +8415,37 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M87">
-        <v>1358.101214682556</v>
+        <v>1265.792489682556</v>
       </c>
       <c r="N87">
-        <v>-859.0501942743932</v>
+        <v>-766.7414692743931</v>
       </c>
       <c r="O87">
-        <v>-214.7625485685983</v>
+        <v>-191.6853673185983</v>
       </c>
       <c r="P87">
-        <v>-644.2876457057949</v>
+        <v>-575.0561019557948</v>
       </c>
       <c r="Q87">
-        <v>-385.7876457057949</v>
+        <v>-316.5561019557948</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.3327198103111892</v>
+        <v>0.3308067226495041</v>
       </c>
       <c r="T87">
-        <v>5.748082424805648</v>
+        <v>5.712577840012083</v>
       </c>
       <c r="U87">
-        <v>0.2206889784279693</v>
+        <v>0.2056889784279693</v>
       </c>
       <c r="V87">
-        <v>0.09186557949674093</v>
+        <v>0.09856493550007524</v>
       </c>
       <c r="W87">
-        <v>0.2004152575361401</v>
+        <v>0.1854152575361401</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3674623179869637</v>
+        <v>0.3942597420003009</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8464,13 +8464,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.2220098302366772</v>
+        <v>0.2088228670874244</v>
       </c>
       <c r="C88">
-        <v>-3908.39266835026</v>
+        <v>-3775.861554568595</v>
       </c>
       <c r="D88">
-        <v>1649.221331649739</v>
+        <v>1781.752445431404</v>
       </c>
       <c r="E88">
         <v>4523.614</v>
@@ -8497,37 +8497,37 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M88">
-        <v>1374.078876031763</v>
+        <v>1280.684166031763</v>
       </c>
       <c r="N88">
-        <v>-875.0278556235997</v>
+        <v>-781.6331456235997</v>
       </c>
       <c r="O88">
-        <v>-218.7569639058999</v>
+        <v>-195.4082864058999</v>
       </c>
       <c r="P88">
-        <v>-656.2708917176998</v>
+        <v>-586.2248592176998</v>
       </c>
       <c r="Q88">
-        <v>-397.7708917176998</v>
+        <v>-327.7248592176998</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.3532140824762741</v>
+        <v>0.3511643456958973</v>
       </c>
       <c r="T88">
-        <v>6.158659740863194</v>
+        <v>6.120619114298662</v>
       </c>
       <c r="U88">
-        <v>0.2206889784279693</v>
+        <v>0.2056889784279693</v>
       </c>
       <c r="V88">
-        <v>0.09079737508398814</v>
+        <v>0.09741883159891156</v>
       </c>
       <c r="W88">
-        <v>0.2006509984767428</v>
+        <v>0.1856509984767428</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3631895003359525</v>
+        <v>0.3896753263956463</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8546,13 +8546,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.2237587200209569</v>
+        <v>0.2104217568717041</v>
       </c>
       <c r="C89">
-        <v>-3996.99939528041</v>
+        <v>-3865.565835700638</v>
       </c>
       <c r="D89">
-        <v>1633.01360471959</v>
+        <v>1764.447164299362</v>
       </c>
       <c r="E89">
         <v>4596.013</v>
@@ -8579,37 +8579,37 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M89">
-        <v>1390.05653738097</v>
+        <v>1295.57584238097</v>
       </c>
       <c r="N89">
-        <v>-891.0055169728063</v>
+        <v>-796.5248219728063</v>
       </c>
       <c r="O89">
-        <v>-222.7513792432016</v>
+        <v>-199.1312054932016</v>
       </c>
       <c r="P89">
-        <v>-668.2541377296047</v>
+        <v>-597.3936164796047</v>
       </c>
       <c r="Q89">
-        <v>-409.7541377296047</v>
+        <v>-338.8936164796047</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.3768613195898337</v>
+        <v>0.3746539107494278</v>
       </c>
       <c r="T89">
-        <v>6.63240279785267</v>
+        <v>6.591435969244712</v>
       </c>
       <c r="U89">
-        <v>0.2206889784279693</v>
+        <v>0.2056889784279693</v>
       </c>
       <c r="V89">
-        <v>0.08975372709451701</v>
+        <v>0.09629907491386661</v>
       </c>
       <c r="W89">
-        <v>0.2008813200853776</v>
+        <v>0.1858813200853776</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.359014908378068</v>
+        <v>0.3851962996554664</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8628,13 +8628,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.2255076098052366</v>
+        <v>0.2120206466559838</v>
       </c>
       <c r="C90">
-        <v>-4085.29065946432</v>
+        <v>-3954.937195047419</v>
       </c>
       <c r="D90">
-        <v>1617.12134053568</v>
+        <v>1747.474804952581</v>
       </c>
       <c r="E90">
         <v>4668.412</v>
@@ -8661,37 +8661,37 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M90">
-        <v>1406.034198730176</v>
+        <v>1310.467518730176</v>
       </c>
       <c r="N90">
-        <v>-906.983178322013</v>
+        <v>-811.4164983220129</v>
       </c>
       <c r="O90">
-        <v>-226.7457945805033</v>
+        <v>-202.8541245805032</v>
       </c>
       <c r="P90">
-        <v>-680.2373837415098</v>
+        <v>-608.5623737415096</v>
       </c>
       <c r="Q90">
-        <v>-421.7373837415098</v>
+        <v>-350.0623737415096</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.4044497628889865</v>
+        <v>0.4020584033118802</v>
       </c>
       <c r="T90">
-        <v>7.185103031007061</v>
+        <v>7.140722300015105</v>
       </c>
       <c r="U90">
-        <v>0.2206889784279693</v>
+        <v>0.2056889784279693</v>
       </c>
       <c r="V90">
-        <v>0.08873379837753384</v>
+        <v>0.09520476724439084</v>
       </c>
       <c r="W90">
-        <v>0.201106407111998</v>
+        <v>0.1861064071119979</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3549351935101354</v>
+        <v>0.3808190689775633</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8710,13 +8710,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.2272564995895162</v>
+        <v>0.2136195364402635</v>
       </c>
       <c r="C91">
-        <v>-4173.275582254637</v>
+        <v>-4043.985148281295</v>
       </c>
       <c r="D91">
-        <v>1601.535417745363</v>
+        <v>1730.825851718705</v>
       </c>
       <c r="E91">
         <v>4740.811</v>
@@ -8743,37 +8743,37 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M91">
-        <v>1422.011860079383</v>
+        <v>1325.359195079383</v>
       </c>
       <c r="N91">
-        <v>-922.9608396712193</v>
+        <v>-826.3081746712193</v>
       </c>
       <c r="O91">
-        <v>-230.7402099178048</v>
+        <v>-206.5770436678048</v>
       </c>
       <c r="P91">
-        <v>-692.2206297534145</v>
+        <v>-619.7311310034145</v>
       </c>
       <c r="Q91">
-        <v>-433.7206297534145</v>
+        <v>-361.2311310034145</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.4370542867879852</v>
+        <v>0.4344455308856875</v>
       </c>
       <c r="T91">
-        <v>7.838294215644065</v>
+        <v>7.789878872743753</v>
       </c>
       <c r="U91">
-        <v>0.2206889784279693</v>
+        <v>0.2056889784279693</v>
       </c>
       <c r="V91">
-        <v>0.08773678940699978</v>
+        <v>0.09413505075849882</v>
       </c>
       <c r="W91">
-        <v>0.2013264360031886</v>
+        <v>0.1863264360031886</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3509471576279991</v>
+        <v>0.3765402030339953</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8792,13 +8792,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.229005389373796</v>
+        <v>0.2152184262245432</v>
       </c>
       <c r="C92">
-        <v>-4260.962936712061</v>
+        <v>-4132.718851857235</v>
       </c>
       <c r="D92">
-        <v>1586.247063287938</v>
+        <v>1714.491148142765</v>
       </c>
       <c r="E92">
         <v>4813.21</v>
@@ -8825,37 +8825,37 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M92">
-        <v>1437.989521428589</v>
+        <v>1340.250871428589</v>
       </c>
       <c r="N92">
-        <v>-938.9385010204261</v>
+        <v>-841.1998510204259</v>
       </c>
       <c r="O92">
-        <v>-234.7346252551065</v>
+        <v>-210.2999627551065</v>
       </c>
       <c r="P92">
-        <v>-704.2038757653196</v>
+        <v>-630.8998882653194</v>
       </c>
       <c r="Q92">
-        <v>-445.7038757653196</v>
+        <v>-372.3998882653194</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.4761797154667839</v>
+        <v>0.4733100839742562</v>
       </c>
       <c r="T92">
-        <v>8.622123637208475</v>
+        <v>8.568866760018127</v>
       </c>
       <c r="U92">
-        <v>0.2206889784279693</v>
+        <v>0.2056889784279693</v>
       </c>
       <c r="V92">
-        <v>0.08676193619136642</v>
+        <v>0.09308910575007105</v>
       </c>
       <c r="W92">
-        <v>0.201541575363464</v>
+        <v>0.186541575363464</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3470477447654657</v>
+        <v>0.3723564230002843</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8874,13 +8874,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.2307542791580756</v>
+        <v>0.2168173160088229</v>
       </c>
       <c r="C93">
-        <v>-4348.36116407223</v>
+        <v>-4221.147119804946</v>
       </c>
       <c r="D93">
-        <v>1571.24783592777</v>
+        <v>1698.461880195054</v>
       </c>
       <c r="E93">
         <v>4885.609</v>
@@ -8907,37 +8907,37 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M93">
-        <v>1453.967182777796</v>
+        <v>1355.142547777796</v>
       </c>
       <c r="N93">
-        <v>-954.9161623696326</v>
+        <v>-856.0915273696324</v>
       </c>
       <c r="O93">
-        <v>-238.7290405924082</v>
+        <v>-214.0228818424081</v>
       </c>
       <c r="P93">
-        <v>-716.1871217772244</v>
+        <v>-642.0686455272244</v>
       </c>
       <c r="Q93">
-        <v>-457.6871217772244</v>
+        <v>-383.5686455272244</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.5239996838519821</v>
+        <v>0.5208112044158403</v>
       </c>
       <c r="T93">
-        <v>9.580137374676083</v>
+        <v>9.520963066686809</v>
       </c>
       <c r="U93">
-        <v>0.2206889784279693</v>
+        <v>0.2056889784279693</v>
       </c>
       <c r="V93">
-        <v>0.08580850832113163</v>
+        <v>0.09206614854402631</v>
       </c>
       <c r="W93">
-        <v>0.2017519863861508</v>
+        <v>0.1867519863861508</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3432340332845265</v>
+        <v>0.3682645941761052</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8956,13 +8956,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.2325031689423554</v>
+        <v>0.2184162057931026</v>
       </c>
       <c r="C94">
-        <v>-4435.478389287111</v>
+        <v>-4309.278439587753</v>
       </c>
       <c r="D94">
-        <v>1556.529610712889</v>
+        <v>1682.729560412246</v>
       </c>
       <c r="E94">
         <v>4958.008</v>
@@ -8989,37 +8989,37 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M94">
-        <v>1469.944844127002</v>
+        <v>1370.034224127002</v>
       </c>
       <c r="N94">
-        <v>-970.8938237188391</v>
+        <v>-870.983203718839</v>
       </c>
       <c r="O94">
-        <v>-242.7234559297098</v>
+        <v>-217.7458009297098</v>
       </c>
       <c r="P94">
-        <v>-728.1703677891294</v>
+        <v>-653.2374027891293</v>
       </c>
       <c r="Q94">
-        <v>-469.6703677891294</v>
+        <v>-394.7374027891293</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.5837746443334799</v>
+        <v>0.5801876049678205</v>
       </c>
       <c r="T94">
-        <v>10.7776545465106</v>
+        <v>10.71108345002266</v>
       </c>
       <c r="U94">
-        <v>0.2206889784279693</v>
+        <v>0.2056889784279693</v>
       </c>
       <c r="V94">
-        <v>0.08487580714372803</v>
+        <v>0.09106542953811297</v>
       </c>
       <c r="W94">
-        <v>0.2019578232561706</v>
+        <v>0.1869578232561706</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3395032285749121</v>
+        <v>0.3642617181524519</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9038,13 +9038,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.234252058726635</v>
+        <v>0.2200150955773823</v>
       </c>
       <c r="C95">
-        <v>-4522.322435701029</v>
+        <v>-4397.120987088227</v>
       </c>
       <c r="D95">
-        <v>1542.08456429897</v>
+        <v>1667.286012911773</v>
       </c>
       <c r="E95">
         <v>5030.407</v>
@@ -9071,37 +9071,37 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M95">
-        <v>1485.922505476209</v>
+        <v>1384.925900476209</v>
       </c>
       <c r="N95">
-        <v>-986.8714850680457</v>
+        <v>-885.8748800680456</v>
       </c>
       <c r="O95">
-        <v>-246.7178712670114</v>
+        <v>-221.4687200170114</v>
       </c>
       <c r="P95">
-        <v>-740.1536138010342</v>
+        <v>-664.4061600510342</v>
       </c>
       <c r="Q95">
-        <v>-481.6536138010342</v>
+        <v>-405.9061600510342</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.6606281649525486</v>
+        <v>0.656528691391795</v>
       </c>
       <c r="T95">
-        <v>12.3173194817264</v>
+        <v>12.24123822859733</v>
       </c>
       <c r="U95">
-        <v>0.2206889784279693</v>
+        <v>0.2056889784279693</v>
       </c>
       <c r="V95">
-        <v>0.08396316405616105</v>
+        <v>0.0900862313710365</v>
       </c>
       <c r="W95">
-        <v>0.2021592335268351</v>
+        <v>0.1871592335268351</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3358526562246442</v>
+        <v>0.360344925484146</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9120,13 +9120,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2360009485109147</v>
+        <v>0.2216139853616619</v>
       </c>
       <c r="C96">
-        <v>-4608.900838917009</v>
+        <v>-4484.682640776062</v>
       </c>
       <c r="D96">
-        <v>1527.905161082992</v>
+        <v>1652.123359223939</v>
       </c>
       <c r="E96">
         <v>5102.806</v>
@@ -9153,37 +9153,37 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M96">
-        <v>1501.900166825415</v>
+        <v>1399.817576825415</v>
       </c>
       <c r="N96">
-        <v>-1002.849146417252</v>
+        <v>-900.7665564172522</v>
       </c>
       <c r="O96">
-        <v>-250.7122866043131</v>
+        <v>-225.1916391043131</v>
       </c>
       <c r="P96">
-        <v>-752.1368598129392</v>
+        <v>-675.5749173129392</v>
       </c>
       <c r="Q96">
-        <v>-493.6368598129392</v>
+        <v>-417.0749173129392</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>0.7630995257779737</v>
+        <v>0.758316806623761</v>
       </c>
       <c r="T96">
-        <v>14.37020606201413</v>
+        <v>14.28144460003022</v>
       </c>
       <c r="U96">
-        <v>0.2206889784279693</v>
+        <v>0.2056889784279693</v>
       </c>
       <c r="V96">
-        <v>0.08306993890662744</v>
+        <v>0.08912786720751482</v>
       </c>
       <c r="W96">
-        <v>0.2023563584725919</v>
+        <v>0.1873563584725918</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3322797556265097</v>
+        <v>0.3565114688300594</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9202,13 +9202,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2377498382951944</v>
+        <v>0.2232128751459417</v>
       </c>
       <c r="C97">
-        <v>-4695.22085990509</v>
+        <v>-4571.970995109899</v>
       </c>
       <c r="D97">
-        <v>1513.98414009491</v>
+        <v>1637.2340048901</v>
       </c>
       <c r="E97">
         <v>5175.205</v>
@@ -9235,37 +9235,37 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M97">
-        <v>1517.877828174622</v>
+        <v>1414.709253174622</v>
       </c>
       <c r="N97">
-        <v>-1018.826807766459</v>
+        <v>-915.6582327664586</v>
       </c>
       <c r="O97">
-        <v>-254.7067019416147</v>
+        <v>-228.9145581916146</v>
       </c>
       <c r="P97">
-        <v>-764.120105824844</v>
+        <v>-686.7436745748439</v>
       </c>
       <c r="Q97">
-        <v>-505.620105824844</v>
+        <v>-428.2436745748439</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>0.9065594309335687</v>
+        <v>0.9008201679485137</v>
       </c>
       <c r="T97">
-        <v>17.24424727441697</v>
+        <v>17.13773352003628</v>
       </c>
       <c r="U97">
-        <v>0.2206889784279693</v>
+        <v>0.2056889784279693</v>
       </c>
       <c r="V97">
-        <v>0.08219551849708399</v>
+        <v>0.08818967913164626</v>
       </c>
       <c r="W97">
-        <v>0.2025493334194906</v>
+        <v>0.1875493334194906</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3287820739883359</v>
+        <v>0.3527587165265851</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9284,13 +9284,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.2394987280794741</v>
+        <v>0.2248117649302213</v>
       </c>
       <c r="C98">
-        <v>-4781.289497400525</v>
+        <v>-4658.993373220912</v>
       </c>
       <c r="D98">
-        <v>1500.314502599474</v>
+        <v>1622.610626779087</v>
       </c>
       <c r="E98">
         <v>5247.603999999999</v>
@@ -9317,37 +9317,37 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M98">
-        <v>1533.855489523829</v>
+        <v>1429.600929523828</v>
       </c>
       <c r="N98">
-        <v>-1034.804469115665</v>
+        <v>-930.5499091156652</v>
       </c>
       <c r="O98">
-        <v>-258.7011172789163</v>
+        <v>-232.6374772789163</v>
       </c>
       <c r="P98">
-        <v>-776.1033518367489</v>
+        <v>-697.9124318367489</v>
       </c>
       <c r="Q98">
-        <v>-517.6033518367489</v>
+        <v>-439.4124318367489</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>1.121749288666959</v>
+        <v>1.11457520993564</v>
       </c>
       <c r="T98">
-        <v>21.55530909302116</v>
+        <v>21.4221669000453</v>
       </c>
       <c r="U98">
-        <v>0.2206889784279693</v>
+        <v>0.2056889784279693</v>
       </c>
       <c r="V98">
-        <v>0.08133931517940603</v>
+        <v>0.08727103664069161</v>
       </c>
       <c r="W98">
-        <v>0.2027382880549956</v>
+        <v>0.1877382880549955</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3253572607176242</v>
+        <v>0.3490841465627664</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9366,13 +9366,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.2412476178637538</v>
+        <v>0.2264106547145011</v>
       </c>
       <c r="C99">
-        <v>-4867.113499636326</v>
+        <v>-4745.756838922682</v>
       </c>
       <c r="D99">
-        <v>1486.889500363674</v>
+        <v>1608.246161077318</v>
       </c>
       <c r="E99">
         <v>5320.003</v>
@@ -9399,37 +9399,37 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M99">
-        <v>1549.833150873035</v>
+        <v>1444.492605873035</v>
       </c>
       <c r="N99">
-        <v>-1050.782130464872</v>
+        <v>-945.4415854648718</v>
       </c>
       <c r="O99">
-        <v>-262.695532616218</v>
+        <v>-236.3603963662179</v>
       </c>
       <c r="P99">
-        <v>-788.0865978486539</v>
+        <v>-709.0811890986538</v>
       </c>
       <c r="Q99">
-        <v>-529.5865978486539</v>
+        <v>-450.5811890986538</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>1.480399051555945</v>
+        <v>1.47083361324752</v>
       </c>
       <c r="T99">
-        <v>28.74041212402822</v>
+        <v>28.5628892000604</v>
       </c>
       <c r="U99">
-        <v>0.2206889784279693</v>
+        <v>0.2056889784279693</v>
       </c>
       <c r="V99">
-        <v>0.08050076553838123</v>
+        <v>0.08637133523202468</v>
       </c>
       <c r="W99">
-        <v>0.2029233467186344</v>
+        <v>0.1879233467186344</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3220030621535248</v>
+        <v>0.3454853409280987</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9448,13 +9448,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.2429965076480335</v>
+        <v>0.2280095444987807</v>
       </c>
       <c r="C100">
-        <v>-4952.699375451492</v>
+        <v>-4832.268208088782</v>
       </c>
       <c r="D100">
-        <v>1473.702624548509</v>
+        <v>1594.133791911218</v>
       </c>
       <c r="E100">
         <v>5392.402</v>
@@ -9481,37 +9481,37 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M100">
-        <v>1565.810812222242</v>
+        <v>1459.384282222242</v>
       </c>
       <c r="N100">
-        <v>-1066.759791814078</v>
+        <v>-960.3332618140784</v>
       </c>
       <c r="O100">
-        <v>-266.6899479535195</v>
+        <v>-240.0833154535196</v>
       </c>
       <c r="P100">
-        <v>-800.0698438605586</v>
+        <v>-720.2499463605587</v>
       </c>
       <c r="Q100">
-        <v>-541.5698438605586</v>
+        <v>-461.7499463605587</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>2.197698577333917</v>
+        <v>2.183350419871279</v>
       </c>
       <c r="T100">
-        <v>43.11061818604232</v>
+        <v>42.8443338000906</v>
       </c>
       <c r="U100">
-        <v>0.2206889784279693</v>
+        <v>0.2056889784279693</v>
       </c>
       <c r="V100">
-        <v>0.07967932915533653</v>
+        <v>0.08548999507659585</v>
       </c>
       <c r="W100">
-        <v>0.2031046286748522</v>
+        <v>0.1881046286748521</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9519,7 +9519,7 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3187173166213462</v>
+        <v>0.3419599803063834</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9530,13 +9530,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.2447453974323132</v>
+        <v>0.2296084342830604</v>
       </c>
       <c r="C101">
-        <v>-5038.053404813332</v>
+        <v>-4918.534059436508</v>
       </c>
       <c r="D101">
-        <v>1460.747595186667</v>
+        <v>1580.266940563491</v>
       </c>
       <c r="E101">
         <v>5464.800999999999</v>
@@ -9563,37 +9563,37 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M101">
-        <v>1581.788473571448</v>
+        <v>1474.275958571448</v>
       </c>
       <c r="N101">
-        <v>-1082.737453163285</v>
+        <v>-975.2249381632847</v>
       </c>
       <c r="O101">
-        <v>-270.6843632908212</v>
+        <v>-243.8062345408212</v>
       </c>
       <c r="P101">
-        <v>-812.0530898724637</v>
+        <v>-731.4187036224636</v>
       </c>
       <c r="Q101">
-        <v>-553.5530898724637</v>
+        <v>-472.9187036224636</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>4.349597154667834</v>
+        <v>4.320900839742558</v>
       </c>
       <c r="T101">
-        <v>86.22123637208465</v>
+        <v>85.68866760018119</v>
       </c>
       <c r="U101">
-        <v>0.2206889784279693</v>
+        <v>0.2056889784279693</v>
       </c>
       <c r="V101">
-        <v>0.07887448744669676</v>
+        <v>0.08462645977279187</v>
       </c>
       <c r="W101">
-        <v>0.2032822483693281</v>
+        <v>0.1882822483693281</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
@@ -9601,7 +9601,7 @@
         </is>
       </c>
       <c r="Y101">
-        <v>0.315497949786787</v>
+        <v>0.3385058390911675</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/united_arab_emirates/united_arab_emirates_chemical_specialty.xlsx
+++ b/research/traditional_assets/database/data/united_arab_emirates/united_arab_emirates_chemical_specialty.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09246020988882045</v>
+        <v>0.09229947670230816</v>
       </c>
       <c r="C2">
-        <v>6893.84113816388</v>
+        <v>6842.96037541269</v>
       </c>
       <c r="D2">
-        <v>6225.14113816388</v>
+        <v>6246.659375412691</v>
       </c>
       <c r="E2">
-        <v>-1702.7</v>
+        <v>-1630.301</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>72.399</v>
       </c>
       <c r="G2">
         <v>668.7</v>
@@ -1445,28 +1445,28 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>3.995626849206546</v>
       </c>
       <c r="N2">
-        <v>499.0510204081633</v>
+        <v>495.0553935589567</v>
       </c>
       <c r="O2">
-        <v>124.7627551020408</v>
+        <v>123.7638483897392</v>
       </c>
       <c r="P2">
-        <v>374.2882653061224</v>
+        <v>371.2915451692176</v>
       </c>
       <c r="Q2">
-        <v>632.7882653061224</v>
+        <v>629.7915451692176</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09246020988882045</v>
+        <v>0.09281369632737212</v>
       </c>
       <c r="T2">
-        <v>0.9352413814778209</v>
+        <v>0.9423265434587135</v>
       </c>
       <c r="U2">
         <v>0.05518897842796926</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>124.8993059767994</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09229947670230816</v>
+        <v>0.09213874351579589</v>
       </c>
       <c r="C3">
-        <v>6842.96037541269</v>
+        <v>6792.228891410931</v>
       </c>
       <c r="D3">
-        <v>6246.659375412691</v>
+        <v>6268.326891410931</v>
       </c>
       <c r="E3">
-        <v>-1630.301</v>
+        <v>-1557.902</v>
       </c>
       <c r="F3">
-        <v>72.399</v>
+        <v>144.798</v>
       </c>
       <c r="G3">
         <v>668.7</v>
@@ -1527,28 +1527,28 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M3">
-        <v>3.995626849206546</v>
+        <v>7.991253698413092</v>
       </c>
       <c r="N3">
-        <v>495.0553935589567</v>
+        <v>491.0597667097501</v>
       </c>
       <c r="O3">
-        <v>123.7638483897392</v>
+        <v>122.7649416774375</v>
       </c>
       <c r="P3">
-        <v>371.2915451692176</v>
+        <v>368.2948250323126</v>
       </c>
       <c r="Q3">
-        <v>629.7915451692176</v>
+        <v>626.7948250323126</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09281369632737212</v>
+        <v>0.09317439677487382</v>
       </c>
       <c r="T3">
-        <v>0.9423265434587135</v>
+        <v>0.9495563005820733</v>
       </c>
       <c r="U3">
         <v>0.05518897842796926</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>124.8993059767994</v>
+        <v>62.44965298839969</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09213874351579589</v>
+        <v>0.0919780103292836</v>
       </c>
       <c r="C4">
-        <v>6792.228891410931</v>
+        <v>6741.648244955674</v>
       </c>
       <c r="D4">
-        <v>6268.326891410931</v>
+        <v>6290.145244955675</v>
       </c>
       <c r="E4">
-        <v>-1557.902</v>
+        <v>-1485.503</v>
       </c>
       <c r="F4">
-        <v>144.798</v>
+        <v>217.197</v>
       </c>
       <c r="G4">
         <v>668.7</v>
@@ -1609,28 +1609,28 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M4">
-        <v>7.991253698413092</v>
+        <v>11.98688054761964</v>
       </c>
       <c r="N4">
-        <v>491.0597667097501</v>
+        <v>487.0641398605436</v>
       </c>
       <c r="O4">
-        <v>122.7649416774375</v>
+        <v>121.7660349651359</v>
       </c>
       <c r="P4">
-        <v>368.2948250323126</v>
+        <v>365.2981048954077</v>
       </c>
       <c r="Q4">
-        <v>626.7948250323126</v>
+        <v>623.7981048954077</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09317439677487382</v>
+        <v>0.09354253434500442</v>
       </c>
       <c r="T4">
-        <v>0.9495563005820733</v>
+        <v>0.9569351248626156</v>
       </c>
       <c r="U4">
         <v>0.05518897842796926</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>62.44965298839969</v>
+        <v>41.63310199226646</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.0919780103292836</v>
+        <v>0.09181727714277131</v>
       </c>
       <c r="C5">
-        <v>6741.648244955674</v>
+        <v>6691.220016622803</v>
       </c>
       <c r="D5">
-        <v>6290.145244955675</v>
+        <v>6312.116016622804</v>
       </c>
       <c r="E5">
-        <v>-1485.503</v>
+        <v>-1413.104</v>
       </c>
       <c r="F5">
-        <v>217.197</v>
+        <v>289.596</v>
       </c>
       <c r="G5">
         <v>668.7</v>
@@ -1691,28 +1691,28 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M5">
-        <v>11.98688054761964</v>
+        <v>15.98250739682618</v>
       </c>
       <c r="N5">
-        <v>487.0641398605436</v>
+        <v>483.0685130113371</v>
       </c>
       <c r="O5">
-        <v>121.7660349651359</v>
+        <v>120.7671282528343</v>
       </c>
       <c r="P5">
-        <v>365.2981048954077</v>
+        <v>362.3013847585028</v>
       </c>
       <c r="Q5">
-        <v>623.7981048954077</v>
+        <v>620.8013847585028</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09354253434500442</v>
+        <v>0.09391834144784608</v>
       </c>
       <c r="T5">
-        <v>0.9569351248626156</v>
+        <v>0.9644676746490027</v>
       </c>
       <c r="U5">
         <v>0.05518897842796926</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>41.63310199226646</v>
+        <v>31.22482649419985</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09181727714277131</v>
+        <v>0.09165654395625904</v>
       </c>
       <c r="C6">
-        <v>6691.220016622803</v>
+        <v>6640.945809148702</v>
       </c>
       <c r="D6">
-        <v>6312.116016622804</v>
+        <v>6334.240809148702</v>
       </c>
       <c r="E6">
-        <v>-1413.104</v>
+        <v>-1340.705</v>
       </c>
       <c r="F6">
-        <v>289.596</v>
+        <v>361.995</v>
       </c>
       <c r="G6">
         <v>668.7</v>
@@ -1773,28 +1773,28 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M6">
-        <v>15.98250739682618</v>
+        <v>19.97813424603273</v>
       </c>
       <c r="N6">
-        <v>483.0685130113371</v>
+        <v>479.0728861621305</v>
       </c>
       <c r="O6">
-        <v>120.7671282528343</v>
+        <v>119.7682215405326</v>
       </c>
       <c r="P6">
-        <v>362.3013847585028</v>
+        <v>359.3046646215979</v>
       </c>
       <c r="Q6">
-        <v>620.8013847585028</v>
+        <v>617.8046646215979</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09391834144784608</v>
+        <v>0.09430206027916863</v>
       </c>
       <c r="T6">
-        <v>0.9644676746490027</v>
+        <v>0.9721588044308928</v>
       </c>
       <c r="U6">
         <v>0.05518897842796926</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>31.22482649419985</v>
+        <v>24.97986119535988</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09165654395625904</v>
+        <v>0.09149581076974676</v>
       </c>
       <c r="C7">
-        <v>6640.945809148702</v>
+        <v>6590.827247819999</v>
       </c>
       <c r="D7">
-        <v>6334.240809148702</v>
+        <v>6356.521247819999</v>
       </c>
       <c r="E7">
-        <v>-1340.705</v>
+        <v>-1268.306</v>
       </c>
       <c r="F7">
-        <v>361.995</v>
+        <v>434.394</v>
       </c>
       <c r="G7">
         <v>668.7</v>
@@ -1855,28 +1855,28 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M7">
-        <v>19.97813424603273</v>
+        <v>23.97376109523928</v>
       </c>
       <c r="N7">
-        <v>479.0728861621305</v>
+        <v>475.077259312924</v>
       </c>
       <c r="O7">
-        <v>119.7682215405326</v>
+        <v>118.769314828231</v>
       </c>
       <c r="P7">
-        <v>359.3046646215979</v>
+        <v>356.3079444846929</v>
       </c>
       <c r="Q7">
-        <v>617.8046646215979</v>
+        <v>614.8079444846929</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09430206027916863</v>
+        <v>0.09469394334094483</v>
       </c>
       <c r="T7">
-        <v>0.9721588044308928</v>
+        <v>0.9800135752719719</v>
       </c>
       <c r="U7">
         <v>0.05518897842796926</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>24.97986119535988</v>
+        <v>20.81655099613323</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09149581076974676</v>
+        <v>0.09133507758323448</v>
       </c>
       <c r="C8">
-        <v>6590.827247819999</v>
+        <v>6540.86598087157</v>
       </c>
       <c r="D8">
-        <v>6356.521247819999</v>
+        <v>6378.95898087157</v>
       </c>
       <c r="E8">
-        <v>-1268.306</v>
+        <v>-1195.907</v>
       </c>
       <c r="F8">
-        <v>434.3939999999999</v>
+        <v>506.7929999999999</v>
       </c>
       <c r="G8">
         <v>668.7</v>
@@ -1937,28 +1937,28 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M8">
-        <v>23.97376109523928</v>
+        <v>27.96938794444582</v>
       </c>
       <c r="N8">
-        <v>475.077259312924</v>
+        <v>471.0816324637174</v>
       </c>
       <c r="O8">
-        <v>118.769314828231</v>
+        <v>117.7704081159294</v>
       </c>
       <c r="P8">
-        <v>356.3079444846929</v>
+        <v>353.3112243477881</v>
       </c>
       <c r="Q8">
-        <v>614.8079444846929</v>
+        <v>611.8112243477881</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09469394334094483</v>
+        <v>0.09509425399544741</v>
       </c>
       <c r="T8">
-        <v>0.9800135752719719</v>
+        <v>0.9880372659160849</v>
       </c>
       <c r="U8">
         <v>0.05518897842796926</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>20.81655099613323</v>
+        <v>17.84275799668563</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09133507758323448</v>
+        <v>0.09117434439672219</v>
       </c>
       <c r="C9">
-        <v>6540.86598087157</v>
+        <v>6491.063679892983</v>
       </c>
       <c r="D9">
-        <v>6378.95898087157</v>
+        <v>6401.555679892983</v>
       </c>
       <c r="E9">
-        <v>-1195.907</v>
+        <v>-1123.508</v>
       </c>
       <c r="F9">
-        <v>506.793</v>
+        <v>579.192</v>
       </c>
       <c r="G9">
         <v>668.7</v>
@@ -2019,28 +2019,28 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M9">
-        <v>27.96938794444582</v>
+        <v>31.96501479365237</v>
       </c>
       <c r="N9">
-        <v>471.0816324637174</v>
+        <v>467.0860056145109</v>
       </c>
       <c r="O9">
-        <v>117.7704081159294</v>
+        <v>116.7715014036277</v>
       </c>
       <c r="P9">
-        <v>353.3112243477881</v>
+        <v>350.3145042108832</v>
       </c>
       <c r="Q9">
-        <v>611.8112243477881</v>
+        <v>608.8145042108831</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09509425399544741</v>
+        <v>0.09550326705548265</v>
       </c>
       <c r="T9">
-        <v>0.9880372659160849</v>
+        <v>0.9962353846176788</v>
       </c>
       <c r="U9">
         <v>0.05518897842796926</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>17.84275799668562</v>
+        <v>15.61241324709992</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09117434439672219</v>
+        <v>0.09101361121020993</v>
       </c>
       <c r="C10">
-        <v>6491.063679892983</v>
+        <v>6441.422040243631</v>
       </c>
       <c r="D10">
-        <v>6401.555679892983</v>
+        <v>6424.313040243631</v>
       </c>
       <c r="E10">
-        <v>-1123.508</v>
+        <v>-1051.109</v>
       </c>
       <c r="F10">
-        <v>579.192</v>
+        <v>651.5909999999999</v>
       </c>
       <c r="G10">
         <v>668.7</v>
@@ -2101,28 +2101,28 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M10">
-        <v>31.96501479365237</v>
+        <v>35.96064164285891</v>
       </c>
       <c r="N10">
-        <v>467.0860056145109</v>
+        <v>463.0903787653044</v>
       </c>
       <c r="O10">
-        <v>116.7715014036277</v>
+        <v>115.7725946913261</v>
       </c>
       <c r="P10">
-        <v>350.3145042108832</v>
+        <v>347.3177840739783</v>
       </c>
       <c r="Q10">
-        <v>608.8145042108831</v>
+        <v>605.8177840739783</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09550326705548265</v>
+        <v>0.09592126941354065</v>
       </c>
       <c r="T10">
-        <v>0.9962353846176788</v>
+        <v>1.004613681752275</v>
       </c>
       <c r="U10">
         <v>0.05518897842796926</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>15.61241324709992</v>
+        <v>13.87770066408882</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09101361121020993</v>
+        <v>0.09085287802369764</v>
       </c>
       <c r="C11">
-        <v>6441.422040243631</v>
+        <v>6391.942781476759</v>
       </c>
       <c r="D11">
-        <v>6424.313040243631</v>
+        <v>6447.232781476759</v>
       </c>
       <c r="E11">
-        <v>-1051.109</v>
+        <v>-978.7100000000002</v>
       </c>
       <c r="F11">
-        <v>651.5909999999999</v>
+        <v>723.9899999999999</v>
       </c>
       <c r="G11">
         <v>668.7</v>
@@ -2183,28 +2183,28 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M11">
-        <v>35.96064164285891</v>
+        <v>39.95626849206545</v>
       </c>
       <c r="N11">
-        <v>463.0903787653044</v>
+        <v>459.0947519160978</v>
       </c>
       <c r="O11">
-        <v>115.7725946913261</v>
+        <v>114.7736879790244</v>
       </c>
       <c r="P11">
-        <v>347.3177840739783</v>
+        <v>344.3210639370733</v>
       </c>
       <c r="Q11">
-        <v>605.8177840739783</v>
+        <v>602.8210639370734</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09592126941354065</v>
+        <v>0.09634856071288882</v>
       </c>
       <c r="T11">
-        <v>1.004613681752275</v>
+        <v>1.013178163267639</v>
       </c>
       <c r="U11">
         <v>0.05518897842796926</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>13.87770066408882</v>
+        <v>12.48993059767994</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09085287802369764</v>
+        <v>0.09069214483718535</v>
       </c>
       <c r="C12">
-        <v>6391.942781476759</v>
+        <v>6342.627647772558</v>
       </c>
       <c r="D12">
-        <v>6447.232781476759</v>
+        <v>6470.316647772558</v>
       </c>
       <c r="E12">
-        <v>-978.71</v>
+        <v>-906.311</v>
       </c>
       <c r="F12">
-        <v>723.99</v>
+        <v>796.389</v>
       </c>
       <c r="G12">
         <v>668.7</v>
@@ -2265,28 +2265,28 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M12">
-        <v>39.95626849206546</v>
+        <v>43.95189534127201</v>
       </c>
       <c r="N12">
-        <v>459.0947519160978</v>
+        <v>455.0991250668912</v>
       </c>
       <c r="O12">
-        <v>114.7736879790244</v>
+        <v>113.7747812667228</v>
       </c>
       <c r="P12">
-        <v>344.3210639370733</v>
+        <v>341.3243438001684</v>
       </c>
       <c r="Q12">
-        <v>602.8210639370734</v>
+        <v>599.8243438001684</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09634856071288882</v>
+        <v>0.09678545406390773</v>
       </c>
       <c r="T12">
-        <v>1.013178163267639</v>
+        <v>1.021935105041776</v>
       </c>
       <c r="U12">
         <v>0.05518897842796926</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>12.48993059767994</v>
+        <v>11.35448236152722</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09069214483718535</v>
+        <v>0.09053141165067306</v>
       </c>
       <c r="C13">
-        <v>6342.627647772558</v>
+        <v>6293.478408380646</v>
       </c>
       <c r="D13">
-        <v>6470.316647772558</v>
+        <v>6493.566408380646</v>
       </c>
       <c r="E13">
-        <v>-906.311</v>
+        <v>-833.9120000000001</v>
       </c>
       <c r="F13">
-        <v>796.389</v>
+        <v>868.7879999999999</v>
       </c>
       <c r="G13">
         <v>668.7</v>
@@ -2347,28 +2347,28 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M13">
-        <v>43.95189534127201</v>
+        <v>47.94752219047855</v>
       </c>
       <c r="N13">
-        <v>455.0991250668912</v>
+        <v>451.1034982176847</v>
       </c>
       <c r="O13">
-        <v>113.7747812667228</v>
+        <v>112.7758745544212</v>
       </c>
       <c r="P13">
-        <v>341.3243438001684</v>
+        <v>338.3276236632635</v>
       </c>
       <c r="Q13">
-        <v>599.8243438001684</v>
+        <v>596.8276236632635</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09678545406390773</v>
+        <v>0.09723227680926799</v>
       </c>
       <c r="T13">
-        <v>1.021935105041776</v>
+        <v>1.030891068219871</v>
       </c>
       <c r="U13">
         <v>0.05518897842796926</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>11.35448236152722</v>
+        <v>10.40827549806662</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09053141165067306</v>
+        <v>0.09037067846416079</v>
       </c>
       <c r="C14">
-        <v>6293.478408380646</v>
+        <v>6244.496858072092</v>
       </c>
       <c r="D14">
-        <v>6493.566408380646</v>
+        <v>6516.983858072092</v>
       </c>
       <c r="E14">
-        <v>-833.9120000000001</v>
+        <v>-761.513</v>
       </c>
       <c r="F14">
-        <v>868.7879999999999</v>
+        <v>941.187</v>
       </c>
       <c r="G14">
         <v>668.7</v>
@@ -2429,28 +2429,28 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M14">
-        <v>47.94752219047855</v>
+        <v>51.9431490396851</v>
       </c>
       <c r="N14">
-        <v>451.1034982176847</v>
+        <v>447.1078713684781</v>
       </c>
       <c r="O14">
-        <v>112.7758745544212</v>
+        <v>111.7769678421195</v>
       </c>
       <c r="P14">
-        <v>338.3276236632635</v>
+        <v>335.3309035263586</v>
       </c>
       <c r="Q14">
-        <v>596.8276236632635</v>
+        <v>593.8309035263586</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09723227680926799</v>
+        <v>0.09768937134187791</v>
       </c>
       <c r="T14">
-        <v>1.030891068219871</v>
+        <v>1.040052915608956</v>
       </c>
       <c r="U14">
         <v>0.05518897842796926</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>10.40827549806662</v>
+        <v>9.60763892129226</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09037067846416079</v>
+        <v>0.0902099452776485</v>
       </c>
       <c r="C15">
-        <v>6244.496858072092</v>
+        <v>6195.684817601273</v>
       </c>
       <c r="D15">
-        <v>6516.983858072092</v>
+        <v>6540.570817601273</v>
       </c>
       <c r="E15">
-        <v>-761.513</v>
+        <v>-689.114</v>
       </c>
       <c r="F15">
-        <v>941.187</v>
+        <v>1013.586</v>
       </c>
       <c r="G15">
         <v>668.7</v>
@@ -2511,28 +2511,28 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M15">
-        <v>51.9431490396851</v>
+        <v>55.93877588889165</v>
       </c>
       <c r="N15">
-        <v>447.1078713684781</v>
+        <v>443.1122445192716</v>
       </c>
       <c r="O15">
-        <v>111.7769678421195</v>
+        <v>110.7780611298179</v>
       </c>
       <c r="P15">
-        <v>335.3309035263586</v>
+        <v>332.3341833894537</v>
       </c>
       <c r="Q15">
-        <v>593.8309035263586</v>
+        <v>590.8341833894538</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09768937134187791</v>
+        <v>0.09815709597989736</v>
       </c>
       <c r="T15">
-        <v>1.040052915608956</v>
+        <v>1.049427829216392</v>
       </c>
       <c r="U15">
         <v>0.05518897842796926</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>9.60763892129226</v>
+        <v>8.921378998342814</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.0902099452776485</v>
+        <v>0.09021796209113622</v>
       </c>
       <c r="C16">
-        <v>6195.684817601273</v>
+        <v>6122.10533714068</v>
       </c>
       <c r="D16">
-        <v>6540.570817601273</v>
+        <v>6539.39033714068</v>
       </c>
       <c r="E16">
-        <v>-689.114</v>
+        <v>-616.7149999999999</v>
       </c>
       <c r="F16">
-        <v>1013.586</v>
+        <v>1085.985</v>
       </c>
       <c r="G16">
         <v>668.7</v>
@@ -2593,45 +2593,45 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M16">
-        <v>55.93877588889165</v>
+        <v>61.5633802380982</v>
       </c>
       <c r="N16">
-        <v>443.1122445192716</v>
+        <v>437.487640170065</v>
       </c>
       <c r="O16">
-        <v>110.7780611298179</v>
+        <v>109.3719100425163</v>
       </c>
       <c r="P16">
-        <v>332.3341833894537</v>
+        <v>328.1157301275488</v>
       </c>
       <c r="Q16">
-        <v>590.8341833894538</v>
+        <v>586.6157301275488</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09815709597989736</v>
+        <v>0.09863582590351727</v>
       </c>
       <c r="T16">
-        <v>1.049427829216392</v>
+        <v>1.059023329026356</v>
       </c>
       <c r="U16">
-        <v>0.05518897842796926</v>
+        <v>0.05668897842796925</v>
       </c>
       <c r="V16">
         <v>0.25</v>
       </c>
       <c r="W16">
-        <v>0.04139173382097694</v>
+        <v>0.04251673382097694</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y16">
-        <v>8.921378998342814</v>
+        <v>8.106296608114574</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09021796209113622</v>
+        <v>0.09006847890462394</v>
       </c>
       <c r="C17">
-        <v>6122.105337140681</v>
+        <v>6071.788164427981</v>
       </c>
       <c r="D17">
-        <v>6539.39033714068</v>
+        <v>6561.472164427982</v>
       </c>
       <c r="E17">
-        <v>-616.7150000000001</v>
+        <v>-544.316</v>
       </c>
       <c r="F17">
-        <v>1085.985</v>
+        <v>1158.384</v>
       </c>
       <c r="G17">
         <v>668.7</v>
@@ -2675,28 +2675,28 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M17">
-        <v>61.56338023809818</v>
+        <v>65.66760558730473</v>
       </c>
       <c r="N17">
-        <v>437.487640170065</v>
+        <v>433.3834148208585</v>
       </c>
       <c r="O17">
-        <v>109.3719100425163</v>
+        <v>108.3458537052146</v>
       </c>
       <c r="P17">
-        <v>328.1157301275488</v>
+        <v>325.0375611156439</v>
       </c>
       <c r="Q17">
-        <v>586.6157301275488</v>
+        <v>583.5375611156439</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09863582590351727</v>
+        <v>0.09912595415865194</v>
       </c>
       <c r="T17">
-        <v>1.059023329026356</v>
+        <v>1.068847293117509</v>
       </c>
       <c r="U17">
         <v>0.05668897842796925</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>8.106296608114576</v>
+        <v>7.599653070107415</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09006847890462394</v>
+        <v>0.08991899571811166</v>
       </c>
       <c r="C18">
-        <v>6071.788164427981</v>
+        <v>6021.620626214127</v>
       </c>
       <c r="D18">
-        <v>6561.472164427982</v>
+        <v>6583.703626214127</v>
       </c>
       <c r="E18">
-        <v>-544.316</v>
+        <v>-471.9169999999999</v>
       </c>
       <c r="F18">
-        <v>1158.384</v>
+        <v>1230.783</v>
       </c>
       <c r="G18">
         <v>668.7</v>
@@ -2757,28 +2757,28 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M18">
-        <v>65.66760558730473</v>
+        <v>69.77183093651129</v>
       </c>
       <c r="N18">
-        <v>433.3834148208585</v>
+        <v>429.279189471652</v>
       </c>
       <c r="O18">
-        <v>108.3458537052146</v>
+        <v>107.319797367913</v>
       </c>
       <c r="P18">
-        <v>325.0375611156439</v>
+        <v>321.959392103739</v>
       </c>
       <c r="Q18">
-        <v>583.5375611156439</v>
+        <v>580.459392103739</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09912595415865194</v>
+        <v>0.09962789273318745</v>
       </c>
       <c r="T18">
-        <v>1.068847293117509</v>
+        <v>1.078907979234956</v>
       </c>
       <c r="U18">
         <v>0.05668897842796925</v>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>7.599653070107415</v>
+        <v>7.152614654218742</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08991899571811166</v>
+        <v>0.08976951253159937</v>
       </c>
       <c r="C19">
-        <v>6021.620626214127</v>
+        <v>5971.604248636691</v>
       </c>
       <c r="D19">
-        <v>6583.703626214127</v>
+        <v>6606.086248636691</v>
       </c>
       <c r="E19">
-        <v>-471.9169999999999</v>
+        <v>-399.518</v>
       </c>
       <c r="F19">
-        <v>1230.783</v>
+        <v>1303.182</v>
       </c>
       <c r="G19">
         <v>668.7</v>
@@ -2839,28 +2839,28 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M19">
-        <v>69.77183093651129</v>
+        <v>73.87605628571782</v>
       </c>
       <c r="N19">
-        <v>429.279189471652</v>
+        <v>425.1749641224454</v>
       </c>
       <c r="O19">
-        <v>107.319797367913</v>
+        <v>106.2937410306114</v>
       </c>
       <c r="P19">
-        <v>321.959392103739</v>
+        <v>318.881223091834</v>
       </c>
       <c r="Q19">
-        <v>580.459392103739</v>
+        <v>577.381223091834</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09962789273318745</v>
+        <v>0.1001420737119799</v>
       </c>
       <c r="T19">
-        <v>1.078907979234956</v>
+        <v>1.089214047940633</v>
       </c>
       <c r="U19">
         <v>0.05668897842796925</v>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>7.152614654218742</v>
+        <v>6.755247173428813</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08976951253159937</v>
+        <v>0.08986227934508711</v>
       </c>
       <c r="C20">
-        <v>5971.604248636691</v>
+        <v>5885.297080924537</v>
       </c>
       <c r="D20">
-        <v>6606.086248636691</v>
+        <v>6592.178080924537</v>
       </c>
       <c r="E20">
-        <v>-399.5180000000003</v>
+        <v>-327.1190000000001</v>
       </c>
       <c r="F20">
-        <v>1303.182</v>
+        <v>1375.581</v>
       </c>
       <c r="G20">
         <v>668.7</v>
@@ -2921,45 +2921,45 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M20">
-        <v>73.87605628571781</v>
+        <v>80.31876933492437</v>
       </c>
       <c r="N20">
-        <v>425.1749641224454</v>
+        <v>418.7322510732389</v>
       </c>
       <c r="O20">
-        <v>106.2937410306114</v>
+        <v>104.6830627683097</v>
       </c>
       <c r="P20">
-        <v>318.881223091834</v>
+        <v>314.0491883049292</v>
       </c>
       <c r="Q20">
-        <v>577.381223091834</v>
+        <v>572.5491883049292</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1001420737119799</v>
+        <v>0.1006689505174092</v>
       </c>
       <c r="T20">
-        <v>1.089214047940633</v>
+        <v>1.099774587478549</v>
       </c>
       <c r="U20">
-        <v>0.05668897842796925</v>
+        <v>0.05838897842796925</v>
       </c>
       <c r="V20">
         <v>0.25</v>
       </c>
       <c r="W20">
-        <v>0.04251673382097694</v>
+        <v>0.04379173382097694</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y20">
-        <v>6.755247173428814</v>
+        <v>6.213379818198545</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08986227934508711</v>
+        <v>0.08972554615857481</v>
       </c>
       <c r="C21">
-        <v>5885.297080924537</v>
+        <v>5833.418474952363</v>
       </c>
       <c r="D21">
-        <v>6592.178080924537</v>
+        <v>6612.698474952363</v>
       </c>
       <c r="E21">
-        <v>-327.1190000000001</v>
+        <v>-254.72</v>
       </c>
       <c r="F21">
-        <v>1375.581</v>
+        <v>1447.98</v>
       </c>
       <c r="G21">
         <v>668.7</v>
@@ -3003,28 +3003,28 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M21">
-        <v>80.31876933492437</v>
+        <v>84.54607298413092</v>
       </c>
       <c r="N21">
-        <v>418.7322510732389</v>
+        <v>414.5049474240324</v>
       </c>
       <c r="O21">
-        <v>104.6830627683097</v>
+        <v>103.6262368560081</v>
       </c>
       <c r="P21">
-        <v>314.0491883049292</v>
+        <v>310.8787105680243</v>
       </c>
       <c r="Q21">
-        <v>572.5491883049292</v>
+        <v>569.3787105680243</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1006689505174092</v>
+        <v>0.1012089992429743</v>
       </c>
       <c r="T21">
-        <v>1.099774587478549</v>
+        <v>1.110599140504912</v>
       </c>
       <c r="U21">
         <v>0.05838897842796925</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>6.213379818198545</v>
+        <v>5.902710827288618</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08972554615857481</v>
+        <v>0.08958881297206253</v>
       </c>
       <c r="C22">
-        <v>5833.418474952363</v>
+        <v>5781.668021294599</v>
       </c>
       <c r="D22">
-        <v>6612.698474952363</v>
+        <v>6633.347021294599</v>
       </c>
       <c r="E22">
-        <v>-254.72</v>
+        <v>-182.3209999999999</v>
       </c>
       <c r="F22">
-        <v>1447.98</v>
+        <v>1520.379</v>
       </c>
       <c r="G22">
         <v>668.7</v>
@@ -3085,28 +3085,28 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M22">
-        <v>84.54607298413092</v>
+        <v>88.77337663333746</v>
       </c>
       <c r="N22">
-        <v>414.5049474240324</v>
+        <v>410.2776437748258</v>
       </c>
       <c r="O22">
-        <v>103.6262368560081</v>
+        <v>102.5694109437064</v>
       </c>
       <c r="P22">
-        <v>310.8787105680243</v>
+        <v>307.7082328311193</v>
       </c>
       <c r="Q22">
-        <v>569.3787105680243</v>
+        <v>566.2082328311194</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1012089992429743</v>
+        <v>0.1017627200881739</v>
       </c>
       <c r="T22">
-        <v>1.110599140504912</v>
+        <v>1.121697732848399</v>
       </c>
       <c r="U22">
         <v>0.05838897842796925</v>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>5.902710827288618</v>
+        <v>5.621629359322493</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08958881297206253</v>
+        <v>0.08958407978555026</v>
       </c>
       <c r="C23">
-        <v>5781.668021294599</v>
+        <v>5709.98610542212</v>
       </c>
       <c r="D23">
-        <v>6633.347021294599</v>
+        <v>6634.064105422121</v>
       </c>
       <c r="E23">
-        <v>-182.3210000000001</v>
+        <v>-109.922</v>
       </c>
       <c r="F23">
-        <v>1520.379</v>
+        <v>1592.778</v>
       </c>
       <c r="G23">
         <v>668.7</v>
@@ -3167,45 +3167,45 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M23">
-        <v>88.77337663333746</v>
+        <v>94.27490268254401</v>
       </c>
       <c r="N23">
-        <v>410.2776437748258</v>
+        <v>404.7761177256193</v>
       </c>
       <c r="O23">
-        <v>102.5694109437064</v>
+        <v>101.1940294314048</v>
       </c>
       <c r="P23">
-        <v>307.7082328311193</v>
+        <v>303.5820882942144</v>
       </c>
       <c r="Q23">
-        <v>566.2082328311194</v>
+        <v>562.0820882942144</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1017627200881739</v>
+        <v>0.1023306389037632</v>
       </c>
       <c r="T23">
-        <v>1.121697732848399</v>
+        <v>1.133080904482744</v>
       </c>
       <c r="U23">
-        <v>0.05838897842796925</v>
+        <v>0.05918897842796925</v>
       </c>
       <c r="V23">
         <v>0.25</v>
       </c>
       <c r="W23">
-        <v>0.04379173382097694</v>
+        <v>0.04439173382097694</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y23">
-        <v>5.621629359322493</v>
+        <v>5.29357237406693</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08958407978555026</v>
+        <v>0.08945334659903798</v>
       </c>
       <c r="C24">
-        <v>5709.98610542212</v>
+        <v>5657.454822506788</v>
       </c>
       <c r="D24">
-        <v>6634.064105422121</v>
+        <v>6653.931822506788</v>
       </c>
       <c r="E24">
-        <v>-109.922</v>
+        <v>-37.52300000000014</v>
       </c>
       <c r="F24">
-        <v>1592.778</v>
+        <v>1665.177</v>
       </c>
       <c r="G24">
         <v>668.7</v>
@@ -3249,28 +3249,28 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M24">
-        <v>94.27490268254401</v>
+        <v>98.56012553175056</v>
       </c>
       <c r="N24">
-        <v>404.7761177256193</v>
+        <v>400.4908948764127</v>
       </c>
       <c r="O24">
-        <v>101.1940294314048</v>
+        <v>100.1227237191032</v>
       </c>
       <c r="P24">
-        <v>303.5820882942144</v>
+        <v>300.3681711573095</v>
       </c>
       <c r="Q24">
-        <v>562.0820882942144</v>
+        <v>558.8681711573095</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1023306389037632</v>
+        <v>0.1029133088574198</v>
       </c>
       <c r="T24">
-        <v>1.133080904482744</v>
+        <v>1.144759742912787</v>
       </c>
       <c r="U24">
         <v>0.05918897842796925</v>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>5.29357237406693</v>
+        <v>5.063417053455324</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08945334659903798</v>
+        <v>0.08932261341252569</v>
       </c>
       <c r="C25">
-        <v>5657.454822506788</v>
+        <v>5605.042896852407</v>
       </c>
       <c r="D25">
-        <v>6653.931822506788</v>
+        <v>6673.918896852408</v>
       </c>
       <c r="E25">
-        <v>-37.52300000000014</v>
+        <v>34.87599999999998</v>
       </c>
       <c r="F25">
-        <v>1665.177</v>
+        <v>1737.576</v>
       </c>
       <c r="G25">
         <v>668.7</v>
@@ -3331,28 +3331,28 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M25">
-        <v>98.56012553175056</v>
+        <v>102.8453483809571</v>
       </c>
       <c r="N25">
-        <v>400.4908948764127</v>
+        <v>396.2056720272062</v>
       </c>
       <c r="O25">
-        <v>100.1227237191032</v>
+        <v>99.05141800680154</v>
       </c>
       <c r="P25">
-        <v>300.3681711573095</v>
+        <v>297.1542540204046</v>
       </c>
       <c r="Q25">
-        <v>558.8681711573095</v>
+        <v>555.6542540204046</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1029133088574198</v>
+        <v>0.1035113122309095</v>
       </c>
       <c r="T25">
-        <v>1.144759742912787</v>
+        <v>1.156745919196252</v>
       </c>
       <c r="U25">
         <v>0.05918897842796925</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.063417053455324</v>
+        <v>4.852441342894686</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08932261341252569</v>
+        <v>0.0891918802260134</v>
       </c>
       <c r="C26">
-        <v>5605.042896852407</v>
+        <v>5552.751407275222</v>
       </c>
       <c r="D26">
-        <v>6673.918896852408</v>
+        <v>6694.026407275222</v>
       </c>
       <c r="E26">
-        <v>34.87599999999975</v>
+        <v>107.2749999999999</v>
       </c>
       <c r="F26">
-        <v>1737.576</v>
+        <v>1809.975</v>
       </c>
       <c r="G26">
         <v>668.7</v>
@@ -3413,28 +3413,28 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M26">
-        <v>102.8453483809571</v>
+        <v>107.1305712301636</v>
       </c>
       <c r="N26">
-        <v>396.2056720272062</v>
+        <v>391.9204491779996</v>
       </c>
       <c r="O26">
-        <v>99.05141800680154</v>
+        <v>97.9801122944999</v>
       </c>
       <c r="P26">
-        <v>297.1542540204046</v>
+        <v>293.9403368834997</v>
       </c>
       <c r="Q26">
-        <v>555.6542540204046</v>
+        <v>552.4403368834996</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1035113122309095</v>
+        <v>0.1041252623610256</v>
       </c>
       <c r="T26">
-        <v>1.156745919196252</v>
+        <v>1.169051726847276</v>
       </c>
       <c r="U26">
         <v>0.05918897842796925</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>4.852441342894686</v>
+        <v>4.658343689178898</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.0891918802260134</v>
+        <v>0.08906114703950113</v>
       </c>
       <c r="C27">
-        <v>5552.751407275222</v>
+        <v>5500.581445632003</v>
       </c>
       <c r="D27">
-        <v>6694.026407275222</v>
+        <v>6714.255445632003</v>
       </c>
       <c r="E27">
-        <v>107.2749999999999</v>
+        <v>179.674</v>
       </c>
       <c r="F27">
-        <v>1809.975</v>
+        <v>1882.374</v>
       </c>
       <c r="G27">
         <v>668.7</v>
@@ -3495,28 +3495,28 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M27">
-        <v>107.1305712301636</v>
+        <v>111.4157940793702</v>
       </c>
       <c r="N27">
-        <v>391.9204491779996</v>
+        <v>387.6352263287931</v>
       </c>
       <c r="O27">
-        <v>97.9801122944999</v>
+        <v>96.90880658219827</v>
       </c>
       <c r="P27">
-        <v>293.9403368834997</v>
+        <v>290.7264197465948</v>
       </c>
       <c r="Q27">
-        <v>552.4403368834996</v>
+        <v>549.2264197465947</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1041252623610256</v>
+        <v>0.1047558057379015</v>
       </c>
       <c r="T27">
-        <v>1.169051726847276</v>
+        <v>1.181690123894274</v>
       </c>
       <c r="U27">
         <v>0.05918897842796925</v>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>4.658343689178898</v>
+        <v>4.479176624210479</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08906114703950113</v>
+        <v>0.08893041385298883</v>
       </c>
       <c r="C28">
-        <v>5500.581445632003</v>
+        <v>5448.534117017697</v>
       </c>
       <c r="D28">
-        <v>6714.255445632003</v>
+        <v>6734.607117017697</v>
       </c>
       <c r="E28">
-        <v>179.674</v>
+        <v>252.0730000000001</v>
       </c>
       <c r="F28">
-        <v>1882.374</v>
+        <v>1954.773</v>
       </c>
       <c r="G28">
         <v>668.7</v>
@@ -3577,28 +3577,28 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M28">
-        <v>111.4157940793702</v>
+        <v>115.7010169285767</v>
       </c>
       <c r="N28">
-        <v>387.6352263287931</v>
+        <v>383.3500034795865</v>
       </c>
       <c r="O28">
-        <v>96.90880658219827</v>
+        <v>95.83750086989663</v>
       </c>
       <c r="P28">
-        <v>290.7264197465948</v>
+        <v>287.5125026096899</v>
       </c>
       <c r="Q28">
-        <v>549.2264197465947</v>
+        <v>546.0125026096898</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1047558057379015</v>
+        <v>0.1054036242757878</v>
       </c>
       <c r="T28">
-        <v>1.181690123894274</v>
+        <v>1.194674778394614</v>
       </c>
       <c r="U28">
         <v>0.05918897842796925</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>4.479176624210479</v>
+        <v>4.313281193684165</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08893041385298883</v>
+        <v>0.08900968066647655</v>
       </c>
       <c r="C29">
-        <v>5448.534117017697</v>
+        <v>5363.780689999867</v>
       </c>
       <c r="D29">
-        <v>6734.607117017697</v>
+        <v>6722.252689999867</v>
       </c>
       <c r="E29">
-        <v>252.0730000000001</v>
+        <v>324.472</v>
       </c>
       <c r="F29">
-        <v>1954.773</v>
+        <v>2027.172</v>
       </c>
       <c r="G29">
         <v>668.7</v>
@@ -3659,45 +3659,45 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M29">
-        <v>115.7010169285767</v>
+        <v>122.0134117777833</v>
       </c>
       <c r="N29">
-        <v>383.3500034795865</v>
+        <v>377.03760863038</v>
       </c>
       <c r="O29">
-        <v>95.83750086989663</v>
+        <v>94.25940215759499</v>
       </c>
       <c r="P29">
-        <v>287.5125026096899</v>
+        <v>282.778206472785</v>
       </c>
       <c r="Q29">
-        <v>546.0125026096898</v>
+        <v>541.278206472785</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1054036242757878</v>
+        <v>0.1060694377730597</v>
       </c>
       <c r="T29">
-        <v>1.194674778394614</v>
+        <v>1.208020117742185</v>
       </c>
       <c r="U29">
-        <v>0.05918897842796925</v>
+        <v>0.06018897842796925</v>
       </c>
       <c r="V29">
         <v>0.25</v>
       </c>
       <c r="W29">
-        <v>0.04439173382097694</v>
+        <v>0.04514173382097694</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y29">
-        <v>4.313281193684165</v>
+        <v>4.090132495574004</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08900968066647655</v>
+        <v>0.08888644747996427</v>
       </c>
       <c r="C30">
-        <v>5363.780689999867</v>
+        <v>5310.608260487366</v>
       </c>
       <c r="D30">
-        <v>6722.252689999867</v>
+        <v>6741.479260487366</v>
       </c>
       <c r="E30">
-        <v>324.472</v>
+        <v>396.8710000000003</v>
       </c>
       <c r="F30">
-        <v>2027.172</v>
+        <v>2099.571</v>
       </c>
       <c r="G30">
         <v>668.7</v>
@@ -3741,28 +3741,28 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M30">
-        <v>122.0134117777833</v>
+        <v>126.3710336269899</v>
       </c>
       <c r="N30">
-        <v>377.03760863038</v>
+        <v>372.6799867811734</v>
       </c>
       <c r="O30">
-        <v>94.25940215759499</v>
+        <v>93.16999669529335</v>
       </c>
       <c r="P30">
-        <v>282.778206472785</v>
+        <v>279.5099900858801</v>
       </c>
       <c r="Q30">
-        <v>541.278206472785</v>
+        <v>538.0099900858801</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1060694377730597</v>
+        <v>0.106754006580114</v>
       </c>
       <c r="T30">
-        <v>1.208020117742185</v>
+        <v>1.221741382141801</v>
       </c>
       <c r="U30">
         <v>0.06018897842796925</v>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>4.090132495574004</v>
+        <v>3.949093444002485</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08888644747996427</v>
+        <v>0.08876321429345198</v>
       </c>
       <c r="C31">
-        <v>5310.608260487366</v>
+        <v>5257.546127729234</v>
       </c>
       <c r="D31">
-        <v>6741.479260487366</v>
+        <v>6760.816127729234</v>
       </c>
       <c r="E31">
-        <v>396.8709999999999</v>
+        <v>469.2699999999998</v>
       </c>
       <c r="F31">
-        <v>2099.571</v>
+        <v>2171.97</v>
       </c>
       <c r="G31">
         <v>668.7</v>
@@ -3823,28 +3823,28 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M31">
-        <v>126.3710336269898</v>
+        <v>130.7286554761964</v>
       </c>
       <c r="N31">
-        <v>372.6799867811734</v>
+        <v>368.3223649319669</v>
       </c>
       <c r="O31">
-        <v>93.16999669529335</v>
+        <v>92.08059123299172</v>
       </c>
       <c r="P31">
-        <v>279.5099900858801</v>
+        <v>276.2417736989752</v>
       </c>
       <c r="Q31">
-        <v>538.0099900858801</v>
+        <v>534.7417736989752</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.106754006580114</v>
+        <v>0.1074581344959413</v>
       </c>
       <c r="T31">
-        <v>1.221741382141801</v>
+        <v>1.23585468266712</v>
       </c>
       <c r="U31">
         <v>0.06018897842796925</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>3.949093444002486</v>
+        <v>3.81745699586907</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08876321429345198</v>
+        <v>0.0886399811069397</v>
       </c>
       <c r="C32">
-        <v>5257.546127729234</v>
+        <v>5204.595243562057</v>
       </c>
       <c r="D32">
-        <v>6760.816127729234</v>
+        <v>6780.264243562056</v>
       </c>
       <c r="E32">
-        <v>469.2699999999998</v>
+        <v>541.6689999999996</v>
       </c>
       <c r="F32">
-        <v>2171.97</v>
+        <v>2244.369</v>
       </c>
       <c r="G32">
         <v>668.7</v>
@@ -3905,28 +3905,28 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M32">
-        <v>130.7286554761964</v>
+        <v>135.0862773254029</v>
       </c>
       <c r="N32">
-        <v>368.3223649319669</v>
+        <v>363.9647430827604</v>
       </c>
       <c r="O32">
-        <v>92.08059123299172</v>
+        <v>90.99118577069009</v>
       </c>
       <c r="P32">
-        <v>276.2417736989752</v>
+        <v>272.9735573120703</v>
       </c>
       <c r="Q32">
-        <v>534.7417736989752</v>
+        <v>531.4735573120703</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1074581344959413</v>
+        <v>0.1081826719165752</v>
       </c>
       <c r="T32">
-        <v>1.23585468266712</v>
+        <v>1.250377064367087</v>
       </c>
       <c r="U32">
         <v>0.06018897842796925</v>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>3.81745699586907</v>
+        <v>3.694313221808778</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.0886399811069397</v>
+        <v>0.08851674792042744</v>
       </c>
       <c r="C33">
-        <v>5204.595243562057</v>
+        <v>5151.756570806203</v>
       </c>
       <c r="D33">
-        <v>6780.264243562056</v>
+        <v>6799.824570806203</v>
       </c>
       <c r="E33">
-        <v>541.6689999999996</v>
+        <v>614.068</v>
       </c>
       <c r="F33">
-        <v>2244.369</v>
+        <v>2316.768</v>
       </c>
       <c r="G33">
         <v>668.7</v>
@@ -3987,28 +3987,28 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M33">
-        <v>135.0862773254029</v>
+        <v>139.4438991746095</v>
       </c>
       <c r="N33">
-        <v>363.9647430827604</v>
+        <v>359.6071212335538</v>
       </c>
       <c r="O33">
-        <v>90.99118577069009</v>
+        <v>89.90178030838845</v>
       </c>
       <c r="P33">
-        <v>272.9735573120703</v>
+        <v>269.7053409251654</v>
       </c>
       <c r="Q33">
-        <v>531.4735573120703</v>
+        <v>528.2053409251654</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1081826719165752</v>
+        <v>0.1089285192613453</v>
       </c>
       <c r="T33">
-        <v>1.250377064367087</v>
+        <v>1.265326574940581</v>
       </c>
       <c r="U33">
         <v>0.06018897842796925</v>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>3.694313221808778</v>
+        <v>3.578865933627253</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08851674792042744</v>
+        <v>0.08839351473391513</v>
       </c>
       <c r="C34">
-        <v>5151.756570806203</v>
+        <v>5099.03108342473</v>
       </c>
       <c r="D34">
-        <v>6799.824570806203</v>
+        <v>6819.498083424731</v>
       </c>
       <c r="E34">
-        <v>614.068</v>
+        <v>686.4669999999999</v>
       </c>
       <c r="F34">
-        <v>2316.768</v>
+        <v>2389.167</v>
       </c>
       <c r="G34">
         <v>668.7</v>
@@ -4069,28 +4069,28 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M34">
-        <v>139.4438991746095</v>
+        <v>143.801521023816</v>
       </c>
       <c r="N34">
-        <v>359.6071212335538</v>
+        <v>355.2494993843472</v>
       </c>
       <c r="O34">
-        <v>89.90178030838845</v>
+        <v>88.81237484608681</v>
       </c>
       <c r="P34">
-        <v>269.7053409251654</v>
+        <v>266.4371245382604</v>
       </c>
       <c r="Q34">
-        <v>528.2053409251654</v>
+        <v>524.9371245382604</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1089285192613453</v>
+        <v>0.1096966307059593</v>
       </c>
       <c r="T34">
-        <v>1.265326574940581</v>
+        <v>1.280722339561046</v>
       </c>
       <c r="U34">
         <v>0.06018897842796925</v>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>3.578865933627253</v>
+        <v>3.470415450790064</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08839351473391513</v>
+        <v>0.08827028154740288</v>
       </c>
       <c r="C35">
-        <v>5099.03108342473</v>
+        <v>5046.419766685003</v>
       </c>
       <c r="D35">
-        <v>6819.498083424731</v>
+        <v>6839.285766685003</v>
       </c>
       <c r="E35">
-        <v>686.4669999999999</v>
+        <v>758.8660000000002</v>
       </c>
       <c r="F35">
-        <v>2389.167</v>
+        <v>2461.566</v>
       </c>
       <c r="G35">
         <v>668.7</v>
@@ -4151,28 +4151,28 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M35">
-        <v>143.801521023816</v>
+        <v>148.1591428730226</v>
       </c>
       <c r="N35">
-        <v>355.2494993843472</v>
+        <v>350.8918775351407</v>
       </c>
       <c r="O35">
-        <v>88.81237484608681</v>
+        <v>87.72296938378517</v>
       </c>
       <c r="P35">
-        <v>266.4371245382604</v>
+        <v>263.1689081513555</v>
       </c>
       <c r="Q35">
-        <v>524.9371245382604</v>
+        <v>521.6689081513555</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1096966307059593</v>
+        <v>0.1104880182549556</v>
       </c>
       <c r="T35">
-        <v>1.280722339561046</v>
+        <v>1.296584642503343</v>
       </c>
       <c r="U35">
         <v>0.06018897842796925</v>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.470415450790064</v>
+        <v>3.368344408119767</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08827028154740288</v>
+        <v>0.0881470483608906</v>
       </c>
       <c r="C36">
-        <v>5046.419766685003</v>
+        <v>4993.923617323233</v>
       </c>
       <c r="D36">
-        <v>6839.285766685003</v>
+        <v>6859.188617323233</v>
       </c>
       <c r="E36">
-        <v>758.8660000000002</v>
+        <v>831.2650000000001</v>
       </c>
       <c r="F36">
-        <v>2461.566</v>
+        <v>2533.965</v>
       </c>
       <c r="G36">
         <v>668.7</v>
@@ -4233,28 +4233,28 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M36">
-        <v>148.1591428730226</v>
+        <v>152.5167647222291</v>
       </c>
       <c r="N36">
-        <v>350.8918775351407</v>
+        <v>346.5342556859341</v>
       </c>
       <c r="O36">
-        <v>87.72296938378517</v>
+        <v>86.63356392148353</v>
       </c>
       <c r="P36">
-        <v>263.1689081513555</v>
+        <v>259.9006917644506</v>
       </c>
       <c r="Q36">
-        <v>521.6689081513555</v>
+        <v>518.4006917644506</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1104880182549556</v>
+        <v>0.1113037561900749</v>
       </c>
       <c r="T36">
-        <v>1.296584642503343</v>
+        <v>1.312935016305403</v>
       </c>
       <c r="U36">
         <v>0.06018897842796925</v>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.368344408119767</v>
+        <v>3.272105996459203</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.0881470483608906</v>
+        <v>0.08802381517437829</v>
       </c>
       <c r="C37">
-        <v>4993.923617323233</v>
+        <v>4941.543643711795</v>
       </c>
       <c r="D37">
-        <v>6859.188617323233</v>
+        <v>6879.207643711796</v>
       </c>
       <c r="E37">
-        <v>831.2650000000001</v>
+        <v>903.664</v>
       </c>
       <c r="F37">
-        <v>2533.965</v>
+        <v>2606.364</v>
       </c>
       <c r="G37">
         <v>668.7</v>
@@ -4315,28 +4315,28 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M37">
-        <v>152.5167647222291</v>
+        <v>156.8743865714357</v>
       </c>
       <c r="N37">
-        <v>346.5342556859341</v>
+        <v>342.1766338367276</v>
       </c>
       <c r="O37">
-        <v>86.63356392148353</v>
+        <v>85.5441584591819</v>
       </c>
       <c r="P37">
-        <v>259.9006917644506</v>
+        <v>256.6324753775457</v>
       </c>
       <c r="Q37">
-        <v>518.4006917644506</v>
+        <v>515.1324753775457</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1113037561900749</v>
+        <v>0.1121449859356666</v>
       </c>
       <c r="T37">
-        <v>1.312935016305403</v>
+        <v>1.329796339288777</v>
       </c>
       <c r="U37">
         <v>0.06018897842796925</v>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.272105996459203</v>
+        <v>3.181214163224225</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08802381517437831</v>
+        <v>0.08790058198786602</v>
       </c>
       <c r="C38">
-        <v>4941.543643711793</v>
+        <v>4889.280866029542</v>
       </c>
       <c r="D38">
-        <v>6879.207643711793</v>
+        <v>6899.343866029542</v>
       </c>
       <c r="E38">
-        <v>903.6639999999995</v>
+        <v>976.0629999999999</v>
       </c>
       <c r="F38">
-        <v>2606.364</v>
+        <v>2678.763</v>
       </c>
       <c r="G38">
         <v>668.7</v>
@@ -4397,28 +4397,28 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M38">
-        <v>156.8743865714356</v>
+        <v>161.2320084206422</v>
       </c>
       <c r="N38">
-        <v>342.1766338367277</v>
+        <v>337.8190119875211</v>
       </c>
       <c r="O38">
-        <v>85.54415845918192</v>
+        <v>84.45475299688027</v>
       </c>
       <c r="P38">
-        <v>256.6324753775457</v>
+        <v>253.3642589906408</v>
       </c>
       <c r="Q38">
-        <v>515.1324753775457</v>
+        <v>511.8642589906408</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1121449859356666</v>
+        <v>0.1130129213874675</v>
       </c>
       <c r="T38">
-        <v>1.329796339288777</v>
+        <v>1.347192942366861</v>
       </c>
       <c r="U38">
         <v>0.06018897842796925</v>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>3.181214163224226</v>
+        <v>3.095235402056003</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08790058198786602</v>
+        <v>0.08777734880135374</v>
       </c>
       <c r="C39">
-        <v>4889.280866029542</v>
+        <v>4837.136316435122</v>
       </c>
       <c r="D39">
-        <v>6899.343866029542</v>
+        <v>6919.598316435123</v>
       </c>
       <c r="E39">
-        <v>976.0629999999999</v>
+        <v>1048.462</v>
       </c>
       <c r="F39">
-        <v>2678.763</v>
+        <v>2751.162</v>
       </c>
       <c r="G39">
         <v>668.7</v>
@@ -4479,28 +4479,28 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M39">
-        <v>161.2320084206422</v>
+        <v>165.5896302698487</v>
       </c>
       <c r="N39">
-        <v>337.8190119875211</v>
+        <v>333.4613901383145</v>
       </c>
       <c r="O39">
-        <v>84.45475299688027</v>
+        <v>83.36534753457863</v>
       </c>
       <c r="P39">
-        <v>253.3642589906408</v>
+        <v>250.0960426037359</v>
       </c>
       <c r="Q39">
-        <v>511.8642589906408</v>
+        <v>508.5960426037359</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1130129213874675</v>
+        <v>0.1139088547570686</v>
       </c>
       <c r="T39">
-        <v>1.347192942366861</v>
+        <v>1.3651507261894</v>
       </c>
       <c r="U39">
         <v>0.06018897842796925</v>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.095235402056003</v>
+        <v>3.013781838844003</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08777734880135374</v>
+        <v>0.08838536561484145</v>
       </c>
       <c r="C40">
-        <v>4837.136316435122</v>
+        <v>4665.942059937253</v>
       </c>
       <c r="D40">
-        <v>6919.598316435123</v>
+        <v>6820.803059937253</v>
       </c>
       <c r="E40">
-        <v>1048.462</v>
+        <v>1120.861</v>
       </c>
       <c r="F40">
-        <v>2751.162</v>
+        <v>2823.561</v>
       </c>
       <c r="G40">
         <v>668.7</v>
@@ -4561,45 +4561,45 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M40">
-        <v>165.5896302698487</v>
+        <v>177.0061546190553</v>
       </c>
       <c r="N40">
-        <v>333.4613901383145</v>
+        <v>322.044865789108</v>
       </c>
       <c r="O40">
-        <v>83.36534753457863</v>
+        <v>80.51121644727699</v>
       </c>
       <c r="P40">
-        <v>250.0960426037359</v>
+        <v>241.533649341831</v>
       </c>
       <c r="Q40">
-        <v>508.5960426037359</v>
+        <v>500.033649341831</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1139088547570686</v>
+        <v>0.1148341629912466</v>
       </c>
       <c r="T40">
-        <v>1.3651507261894</v>
+        <v>1.383697289809399</v>
       </c>
       <c r="U40">
-        <v>0.06018897842796925</v>
+        <v>0.06268897842796925</v>
       </c>
       <c r="V40">
         <v>0.25</v>
       </c>
       <c r="W40">
-        <v>0.04514173382097694</v>
+        <v>0.04701673382097694</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y40">
-        <v>3.013781838844003</v>
+        <v>2.819399254688056</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08838536561484145</v>
+        <v>0.08828088242832918</v>
       </c>
       <c r="C41">
-        <v>4665.942059937253</v>
+        <v>4610.319058869884</v>
       </c>
       <c r="D41">
-        <v>6820.803059937253</v>
+        <v>6837.579058869884</v>
       </c>
       <c r="E41">
-        <v>1120.861</v>
+        <v>1193.26</v>
       </c>
       <c r="F41">
-        <v>2823.561</v>
+        <v>2895.96</v>
       </c>
       <c r="G41">
         <v>668.7</v>
@@ -4643,28 +4643,28 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M41">
-        <v>177.0061546190553</v>
+        <v>181.5447739682618</v>
       </c>
       <c r="N41">
-        <v>322.044865789108</v>
+        <v>317.5062464399014</v>
       </c>
       <c r="O41">
-        <v>80.51121644727699</v>
+        <v>79.37656160997535</v>
       </c>
       <c r="P41">
-        <v>241.533649341831</v>
+        <v>238.1296848299261</v>
       </c>
       <c r="Q41">
-        <v>500.033649341831</v>
+        <v>496.6296848299261</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1148341629912466</v>
+        <v>0.1157903148332307</v>
       </c>
       <c r="T41">
-        <v>1.383697289809399</v>
+        <v>1.402862072216731</v>
       </c>
       <c r="U41">
         <v>0.06268897842796925</v>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.819399254688056</v>
+        <v>2.748914273320854</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08828088242832918</v>
+        <v>0.0881763992418169</v>
       </c>
       <c r="C42">
-        <v>4610.319058869884</v>
+        <v>4554.778783558209</v>
       </c>
       <c r="D42">
-        <v>6837.579058869884</v>
+        <v>6854.43778355821</v>
       </c>
       <c r="E42">
-        <v>1193.26</v>
+        <v>1265.659</v>
       </c>
       <c r="F42">
-        <v>2895.96</v>
+        <v>2968.359</v>
       </c>
       <c r="G42">
         <v>668.7</v>
@@ -4725,28 +4725,28 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M42">
-        <v>181.5447739682618</v>
+        <v>186.0833933174684</v>
       </c>
       <c r="N42">
-        <v>317.5062464399014</v>
+        <v>312.9676270906949</v>
       </c>
       <c r="O42">
-        <v>79.37656160997535</v>
+        <v>78.24190677267373</v>
       </c>
       <c r="P42">
-        <v>238.1296848299261</v>
+        <v>234.7257203180212</v>
       </c>
       <c r="Q42">
-        <v>496.6296848299261</v>
+        <v>493.2257203180212</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1157903148332307</v>
+        <v>0.1167788786020616</v>
       </c>
       <c r="T42">
-        <v>1.402862072216731</v>
+        <v>1.42267650826499</v>
       </c>
       <c r="U42">
         <v>0.06268897842796925</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.748914273320854</v>
+        <v>2.681867583727663</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.0881763992418169</v>
+        <v>0.08807191605530462</v>
       </c>
       <c r="C43">
-        <v>4554.778783558209</v>
+        <v>4499.321847420169</v>
       </c>
       <c r="D43">
-        <v>6854.43778355821</v>
+        <v>6871.379847420169</v>
       </c>
       <c r="E43">
-        <v>1265.659</v>
+        <v>1338.058</v>
       </c>
       <c r="F43">
-        <v>2968.359</v>
+        <v>3040.758</v>
       </c>
       <c r="G43">
         <v>668.7</v>
@@ -4807,28 +4807,28 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M43">
-        <v>186.0833933174684</v>
+        <v>190.6220126666749</v>
       </c>
       <c r="N43">
-        <v>312.9676270906949</v>
+        <v>308.4290077414883</v>
       </c>
       <c r="O43">
-        <v>78.24190677267373</v>
+        <v>77.10725193537208</v>
       </c>
       <c r="P43">
-        <v>234.7257203180212</v>
+        <v>231.3217558061162</v>
       </c>
       <c r="Q43">
-        <v>493.2257203180212</v>
+        <v>489.8217558061162</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1167788786020616</v>
+        <v>0.1178015307767143</v>
       </c>
       <c r="T43">
-        <v>1.42267650826499</v>
+        <v>1.443174200728706</v>
       </c>
       <c r="U43">
         <v>0.06268897842796925</v>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.681867583727663</v>
+        <v>2.618013593638909</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08807191605530462</v>
+        <v>0.08796743286879233</v>
       </c>
       <c r="C44">
-        <v>4499.321847420169</v>
+        <v>4443.948869953454</v>
       </c>
       <c r="D44">
-        <v>6871.379847420169</v>
+        <v>6888.405869953453</v>
       </c>
       <c r="E44">
-        <v>1338.058</v>
+        <v>1410.457</v>
       </c>
       <c r="F44">
-        <v>3040.758</v>
+        <v>3113.157</v>
       </c>
       <c r="G44">
         <v>668.7</v>
@@ -4889,28 +4889,28 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M44">
-        <v>190.6220126666749</v>
+        <v>195.1606320158814</v>
       </c>
       <c r="N44">
-        <v>308.4290077414884</v>
+        <v>303.8903883922818</v>
       </c>
       <c r="O44">
-        <v>77.10725193537209</v>
+        <v>75.97259709807045</v>
       </c>
       <c r="P44">
-        <v>231.3217558061163</v>
+        <v>227.9177912942114</v>
       </c>
       <c r="Q44">
-        <v>489.8217558061162</v>
+        <v>486.4177912942114</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1178015307767143</v>
+        <v>0.118860065483811</v>
       </c>
       <c r="T44">
-        <v>1.443174200728706</v>
+        <v>1.464391110471851</v>
       </c>
       <c r="U44">
         <v>0.06268897842796925</v>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.618013593638909</v>
+        <v>2.557129556577539</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08796743286879233</v>
+        <v>0.08901794968228006</v>
       </c>
       <c r="C45">
-        <v>4443.948869953454</v>
+        <v>4204.110501873465</v>
       </c>
       <c r="D45">
-        <v>6888.405869953453</v>
+        <v>6720.966501873465</v>
       </c>
       <c r="E45">
-        <v>1410.457</v>
+        <v>1482.856</v>
       </c>
       <c r="F45">
-        <v>3113.157</v>
+        <v>3185.556</v>
       </c>
       <c r="G45">
         <v>668.7</v>
@@ -4971,45 +4971,45 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M45">
-        <v>195.1606320158814</v>
+        <v>210.848697365088</v>
       </c>
       <c r="N45">
-        <v>303.8903883922818</v>
+        <v>288.2023230430752</v>
       </c>
       <c r="O45">
-        <v>75.97259709807045</v>
+        <v>72.05058076076881</v>
       </c>
       <c r="P45">
-        <v>227.9177912942114</v>
+        <v>216.1517422823064</v>
       </c>
       <c r="Q45">
-        <v>486.4177912942114</v>
+        <v>474.6517422823064</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.118860065483811</v>
+        <v>0.1199564050018753</v>
       </c>
       <c r="T45">
-        <v>1.464391110471851</v>
+        <v>1.486365766991537</v>
       </c>
       <c r="U45">
-        <v>0.06268897842796925</v>
+        <v>0.06618897842796925</v>
       </c>
       <c r="V45">
         <v>0.25</v>
       </c>
       <c r="W45">
-        <v>0.04701673382097694</v>
+        <v>0.04964173382097694</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y45">
-        <v>2.557129556577539</v>
+        <v>2.366867932525322</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08901794968228006</v>
+        <v>0.08893971649576776</v>
       </c>
       <c r="C46">
-        <v>4204.110501873465</v>
+        <v>4143.899867226667</v>
       </c>
       <c r="D46">
-        <v>6720.966501873465</v>
+        <v>6733.154867226667</v>
       </c>
       <c r="E46">
-        <v>1482.856</v>
+        <v>1555.255</v>
       </c>
       <c r="F46">
-        <v>3185.556</v>
+        <v>3257.955</v>
       </c>
       <c r="G46">
         <v>668.7</v>
@@ -5053,28 +5053,28 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M46">
-        <v>210.848697365088</v>
+        <v>215.6407132142945</v>
       </c>
       <c r="N46">
-        <v>288.2023230430752</v>
+        <v>283.4103071938687</v>
       </c>
       <c r="O46">
-        <v>72.05058076076881</v>
+        <v>70.85257679846717</v>
       </c>
       <c r="P46">
-        <v>216.1517422823064</v>
+        <v>212.5577303954015</v>
       </c>
       <c r="Q46">
-        <v>474.6517422823064</v>
+        <v>471.0577303954015</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1199564050018753</v>
+        <v>0.1210926114115057</v>
       </c>
       <c r="T46">
-        <v>1.486365766991537</v>
+        <v>1.50913950193012</v>
       </c>
       <c r="U46">
         <v>0.06618897842796925</v>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.366867932525322</v>
+        <v>2.314270867358093</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08893971649576776</v>
+        <v>0.0888614833092555</v>
       </c>
       <c r="C47">
-        <v>4143.899867226667</v>
+        <v>4083.733519705466</v>
       </c>
       <c r="D47">
-        <v>6733.154867226667</v>
+        <v>6745.387519705466</v>
       </c>
       <c r="E47">
-        <v>1555.255</v>
+        <v>1627.654</v>
       </c>
       <c r="F47">
-        <v>3257.955</v>
+        <v>3330.354</v>
       </c>
       <c r="G47">
         <v>668.7</v>
@@ -5135,28 +5135,28 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M47">
-        <v>215.6407132142945</v>
+        <v>220.4327290635011</v>
       </c>
       <c r="N47">
-        <v>283.4103071938687</v>
+        <v>278.6182913446621</v>
       </c>
       <c r="O47">
-        <v>70.85257679846717</v>
+        <v>69.65457283616553</v>
       </c>
       <c r="P47">
-        <v>212.5577303954015</v>
+        <v>208.9637185084966</v>
       </c>
       <c r="Q47">
-        <v>471.0577303954015</v>
+        <v>467.4637185084966</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1210926114115057</v>
+        <v>0.1222708995400113</v>
       </c>
       <c r="T47">
-        <v>1.50913950193012</v>
+        <v>1.532756708533095</v>
       </c>
       <c r="U47">
         <v>0.06618897842796925</v>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.314270867358093</v>
+        <v>2.263960631111178</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.0888614833092555</v>
+        <v>0.08977025012274321</v>
       </c>
       <c r="C48">
-        <v>4083.733519705466</v>
+        <v>3871.922433012517</v>
       </c>
       <c r="D48">
-        <v>6745.387519705466</v>
+        <v>6605.975433012517</v>
       </c>
       <c r="E48">
-        <v>1627.654</v>
+        <v>1700.053</v>
       </c>
       <c r="F48">
-        <v>3330.354</v>
+        <v>3402.753</v>
       </c>
       <c r="G48">
         <v>668.7</v>
@@ -5217,45 +5217,45 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M48">
-        <v>220.4327290635011</v>
+        <v>234.7524533127077</v>
       </c>
       <c r="N48">
-        <v>278.6182913446621</v>
+        <v>264.2985670954556</v>
       </c>
       <c r="O48">
-        <v>69.65457283616553</v>
+        <v>66.0746417738639</v>
       </c>
       <c r="P48">
-        <v>208.9637185084966</v>
+        <v>198.2239253215917</v>
       </c>
       <c r="Q48">
-        <v>467.4637185084966</v>
+        <v>456.7239253215917</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1222708995400113</v>
+        <v>0.1234936513714793</v>
       </c>
       <c r="T48">
-        <v>1.532756708533095</v>
+        <v>1.557265130479579</v>
       </c>
       <c r="U48">
-        <v>0.06618897842796925</v>
+        <v>0.06898897842796925</v>
       </c>
       <c r="V48">
         <v>0.25</v>
       </c>
       <c r="W48">
-        <v>0.04964173382097694</v>
+        <v>0.05174173382097694</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y48">
-        <v>2.263960631111178</v>
+        <v>2.125860724204617</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08977025012274321</v>
+        <v>0.08971301693623093</v>
       </c>
       <c r="C49">
-        <v>3871.922433012517</v>
+        <v>3808.133204110735</v>
       </c>
       <c r="D49">
-        <v>6605.975433012517</v>
+        <v>6614.585204110736</v>
       </c>
       <c r="E49">
-        <v>1700.053</v>
+        <v>1772.452</v>
       </c>
       <c r="F49">
-        <v>3402.753</v>
+        <v>3475.152</v>
       </c>
       <c r="G49">
         <v>668.7</v>
@@ -5299,28 +5299,28 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M49">
-        <v>234.7524533127077</v>
+        <v>239.7471863619142</v>
       </c>
       <c r="N49">
-        <v>264.2985670954556</v>
+        <v>259.3038340462491</v>
       </c>
       <c r="O49">
-        <v>66.0746417738639</v>
+        <v>64.82595851156226</v>
       </c>
       <c r="P49">
-        <v>198.2239253215917</v>
+        <v>194.4778755346868</v>
       </c>
       <c r="Q49">
-        <v>456.7239253215917</v>
+        <v>452.9778755346868</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1234936513714793</v>
+        <v>0.1247634321195423</v>
       </c>
       <c r="T49">
-        <v>1.557265130479579</v>
+        <v>1.582716184039389</v>
       </c>
       <c r="U49">
         <v>0.06898897842796925</v>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.125860724204617</v>
+        <v>2.081571959117021</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08971301693623092</v>
+        <v>0.08965578374971864</v>
       </c>
       <c r="C50">
-        <v>3808.133204110738</v>
+        <v>3744.36644725679</v>
       </c>
       <c r="D50">
-        <v>6614.585204110738</v>
+        <v>6623.21744725679</v>
       </c>
       <c r="E50">
-        <v>1772.452</v>
+        <v>1844.851</v>
       </c>
       <c r="F50">
-        <v>3475.152</v>
+        <v>3547.551</v>
       </c>
       <c r="G50">
         <v>668.7</v>
@@ -5381,28 +5381,28 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M50">
-        <v>239.7471863619142</v>
+        <v>244.7419194111207</v>
       </c>
       <c r="N50">
-        <v>259.3038340462491</v>
+        <v>254.3091009970425</v>
       </c>
       <c r="O50">
-        <v>64.82595851156228</v>
+        <v>63.57727524926063</v>
       </c>
       <c r="P50">
-        <v>194.4778755346868</v>
+        <v>190.7318257477819</v>
       </c>
       <c r="Q50">
-        <v>452.9778755346869</v>
+        <v>449.2318257477819</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1247634321195423</v>
+        <v>0.1260830081910587</v>
       </c>
       <c r="T50">
-        <v>1.582716184039389</v>
+        <v>1.609165318130956</v>
       </c>
       <c r="U50">
         <v>0.06898897842796925</v>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.081571959117021</v>
+        <v>2.039090898726878</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08965578374971864</v>
+        <v>0.09252355056320635</v>
       </c>
       <c r="C51">
-        <v>3744.36644725679</v>
+        <v>3265.452039827264</v>
       </c>
       <c r="D51">
-        <v>6623.21744725679</v>
+        <v>6216.702039827264</v>
       </c>
       <c r="E51">
-        <v>1844.851</v>
+        <v>1917.25</v>
       </c>
       <c r="F51">
-        <v>3547.551</v>
+        <v>3619.95</v>
       </c>
       <c r="G51">
         <v>668.7</v>
@@ -5463,45 +5463,45 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M51">
-        <v>244.7419194111207</v>
+        <v>277.9722624603273</v>
       </c>
       <c r="N51">
-        <v>254.3091009970425</v>
+        <v>221.078757947836</v>
       </c>
       <c r="O51">
-        <v>63.57727524926063</v>
+        <v>55.269689486959</v>
       </c>
       <c r="P51">
-        <v>190.7318257477819</v>
+        <v>165.809068460877</v>
       </c>
       <c r="Q51">
-        <v>449.2318257477819</v>
+        <v>424.309068460877</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1260830081910587</v>
+        <v>0.1274553673054358</v>
       </c>
       <c r="T51">
-        <v>1.609165318130956</v>
+        <v>1.636672417586186</v>
       </c>
       <c r="U51">
-        <v>0.06898897842796925</v>
+        <v>0.07678897842796925</v>
       </c>
       <c r="V51">
         <v>0.25</v>
       </c>
       <c r="W51">
-        <v>0.05174173382097694</v>
+        <v>0.05759173382097694</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y51">
-        <v>2.039090898726878</v>
+        <v>1.795326684724123</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.09252355056320635</v>
+        <v>0.09252481737669409</v>
       </c>
       <c r="C52">
-        <v>3265.452039827264</v>
+        <v>3192.884491239267</v>
       </c>
       <c r="D52">
-        <v>6216.702039827264</v>
+        <v>6216.533491239267</v>
       </c>
       <c r="E52">
-        <v>1917.25</v>
+        <v>1989.649</v>
       </c>
       <c r="F52">
-        <v>3619.95</v>
+        <v>3692.349</v>
       </c>
       <c r="G52">
         <v>668.7</v>
@@ -5545,28 +5545,28 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M52">
-        <v>277.9722624603273</v>
+        <v>283.5317077095338</v>
       </c>
       <c r="N52">
-        <v>221.078757947836</v>
+        <v>215.5193126986294</v>
       </c>
       <c r="O52">
-        <v>55.269689486959</v>
+        <v>53.87982817465736</v>
       </c>
       <c r="P52">
-        <v>165.809068460877</v>
+        <v>161.6394845239721</v>
       </c>
       <c r="Q52">
-        <v>424.309068460877</v>
+        <v>420.1394845239721</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1274553673054358</v>
+        <v>0.1288837410775426</v>
       </c>
       <c r="T52">
-        <v>1.636672417586186</v>
+        <v>1.665302255794691</v>
       </c>
       <c r="U52">
         <v>0.07678897842796925</v>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>1.795326684724123</v>
+        <v>1.760124200709925</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.09252481737669409</v>
+        <v>0.0940470841901818</v>
       </c>
       <c r="C53">
-        <v>3192.884491239267</v>
+        <v>2924.34467179936</v>
       </c>
       <c r="D53">
-        <v>6216.533491239267</v>
+        <v>6020.39267179936</v>
       </c>
       <c r="E53">
-        <v>1989.649</v>
+        <v>2062.048</v>
       </c>
       <c r="F53">
-        <v>3692.349</v>
+        <v>3764.748</v>
       </c>
       <c r="G53">
         <v>668.7</v>
@@ -5627,45 +5627,45 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M53">
-        <v>283.5317077095338</v>
+        <v>303.7736701587404</v>
       </c>
       <c r="N53">
-        <v>215.5193126986294</v>
+        <v>195.2773502494229</v>
       </c>
       <c r="O53">
-        <v>53.87982817465736</v>
+        <v>48.81933756235571</v>
       </c>
       <c r="P53">
-        <v>161.6394845239721</v>
+        <v>146.4580126870671</v>
       </c>
       <c r="Q53">
-        <v>420.1394845239721</v>
+        <v>404.9580126870671</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1288837410775426</v>
+        <v>0.1303716304234871</v>
       </c>
       <c r="T53">
-        <v>1.665302255794691</v>
+        <v>1.69512500392855</v>
       </c>
       <c r="U53">
-        <v>0.07678897842796925</v>
+        <v>0.08068897842796925</v>
       </c>
       <c r="V53">
         <v>0.25</v>
       </c>
       <c r="W53">
-        <v>0.05759173382097694</v>
+        <v>0.06051673382097694</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y53">
-        <v>1.760124200709925</v>
+        <v>1.642838301777038</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.0940470841901818</v>
+        <v>0.09407760100366952</v>
       </c>
       <c r="C54">
-        <v>2924.34467179936</v>
+        <v>2848.140114015448</v>
       </c>
       <c r="D54">
-        <v>6020.39267179936</v>
+        <v>6016.587114015448</v>
       </c>
       <c r="E54">
-        <v>2062.048</v>
+        <v>2134.447</v>
       </c>
       <c r="F54">
-        <v>3764.748</v>
+        <v>3837.147</v>
       </c>
       <c r="G54">
         <v>668.7</v>
@@ -5709,28 +5709,28 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M54">
-        <v>303.7736701587404</v>
+        <v>309.6154715079469</v>
       </c>
       <c r="N54">
-        <v>195.2773502494229</v>
+        <v>189.4355489002163</v>
       </c>
       <c r="O54">
-        <v>48.81933756235571</v>
+        <v>47.35888722505408</v>
       </c>
       <c r="P54">
-        <v>146.4580126870671</v>
+        <v>142.0766616751622</v>
       </c>
       <c r="Q54">
-        <v>404.9580126870671</v>
+        <v>400.5766616751622</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1303716304234871</v>
+        <v>0.1319228342096846</v>
       </c>
       <c r="T54">
-        <v>1.69512500392855</v>
+        <v>1.726216805174489</v>
       </c>
       <c r="U54">
         <v>0.08068897842796925</v>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>1.642838301777038</v>
+        <v>1.611841352686906</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.09407760100366952</v>
+        <v>0.09410811781715724</v>
       </c>
       <c r="C55">
-        <v>2848.140114015448</v>
+        <v>2771.940364263905</v>
       </c>
       <c r="D55">
-        <v>6016.587114015448</v>
+        <v>6012.786364263906</v>
       </c>
       <c r="E55">
-        <v>2134.447</v>
+        <v>2206.846</v>
       </c>
       <c r="F55">
-        <v>3837.147</v>
+        <v>3909.546</v>
       </c>
       <c r="G55">
         <v>668.7</v>
@@ -5791,28 +5791,28 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M55">
-        <v>309.6154715079469</v>
+        <v>315.4572728571535</v>
       </c>
       <c r="N55">
-        <v>189.4355489002163</v>
+        <v>183.5937475510098</v>
       </c>
       <c r="O55">
-        <v>47.35888722505408</v>
+        <v>45.89843688775244</v>
       </c>
       <c r="P55">
-        <v>142.0766616751622</v>
+        <v>137.6953106632573</v>
       </c>
       <c r="Q55">
-        <v>400.5766616751622</v>
+        <v>396.1953106632573</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1319228342096846</v>
+        <v>0.1335414816387602</v>
       </c>
       <c r="T55">
-        <v>1.726216805174489</v>
+        <v>1.758660423865902</v>
       </c>
       <c r="U55">
         <v>0.08068897842796925</v>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>1.611841352686906</v>
+        <v>1.581992438748259</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.09410811781715724</v>
+        <v>0.09413863463064495</v>
       </c>
       <c r="C56">
-        <v>2771.940364263905</v>
+        <v>2695.745413438612</v>
       </c>
       <c r="D56">
-        <v>6012.786364263906</v>
+        <v>6008.990413438612</v>
       </c>
       <c r="E56">
-        <v>2206.846</v>
+        <v>2279.245</v>
       </c>
       <c r="F56">
-        <v>3909.546</v>
+        <v>3981.945</v>
       </c>
       <c r="G56">
         <v>668.7</v>
@@ -5873,28 +5873,28 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M56">
-        <v>315.4572728571535</v>
+        <v>321.29907420636</v>
       </c>
       <c r="N56">
-        <v>183.5937475510098</v>
+        <v>177.7519462018032</v>
       </c>
       <c r="O56">
-        <v>45.89843688775244</v>
+        <v>44.4379865504508</v>
       </c>
       <c r="P56">
-        <v>137.6953106632573</v>
+        <v>133.3139596513524</v>
       </c>
       <c r="Q56">
-        <v>396.1953106632573</v>
+        <v>391.8139596513524</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1335414816387602</v>
+        <v>0.1352320689535725</v>
       </c>
       <c r="T56">
-        <v>1.758660423865902</v>
+        <v>1.792545981165824</v>
       </c>
       <c r="U56">
         <v>0.08068897842796925</v>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>1.581992438748259</v>
+        <v>1.553228939861927</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.09413863463064495</v>
+        <v>0.09416915144413267</v>
       </c>
       <c r="C57">
-        <v>2695.745413438612</v>
+        <v>2619.555252456428</v>
       </c>
       <c r="D57">
-        <v>6008.990413438612</v>
+        <v>6005.199252456428</v>
       </c>
       <c r="E57">
-        <v>2279.245</v>
+        <v>2351.644</v>
       </c>
       <c r="F57">
-        <v>3981.945</v>
+        <v>4054.344</v>
       </c>
       <c r="G57">
         <v>668.7</v>
@@ -5955,28 +5955,28 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M57">
-        <v>321.29907420636</v>
+        <v>327.1408755555666</v>
       </c>
       <c r="N57">
-        <v>177.7519462018032</v>
+        <v>171.9101448525967</v>
       </c>
       <c r="O57">
-        <v>44.4379865504508</v>
+        <v>42.97753621314916</v>
       </c>
       <c r="P57">
-        <v>133.3139596513524</v>
+        <v>128.9326086394475</v>
       </c>
       <c r="Q57">
-        <v>391.8139596513524</v>
+        <v>387.4326086394475</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1352320689535725</v>
+        <v>0.1369995011463309</v>
       </c>
       <c r="T57">
-        <v>1.792545981165824</v>
+        <v>1.827971791070286</v>
       </c>
       <c r="U57">
         <v>0.08068897842796925</v>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>1.553228939861927</v>
+        <v>1.525492708792964</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.09416915144413267</v>
+        <v>0.1002701682576204</v>
       </c>
       <c r="C58">
-        <v>2619.555252456428</v>
+        <v>1874.534471038395</v>
       </c>
       <c r="D58">
-        <v>6005.199252456428</v>
+        <v>5332.577471038396</v>
       </c>
       <c r="E58">
-        <v>2351.644</v>
+        <v>2424.043000000001</v>
       </c>
       <c r="F58">
-        <v>4054.344</v>
+        <v>4126.743</v>
       </c>
       <c r="G58">
         <v>668.7</v>
@@ -6037,45 +6037,45 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M58">
-        <v>327.1408755555666</v>
+        <v>391.5824275047732</v>
       </c>
       <c r="N58">
-        <v>171.9101448525967</v>
+        <v>107.4685929033901</v>
       </c>
       <c r="O58">
-        <v>42.97753621314916</v>
+        <v>26.86714822584752</v>
       </c>
       <c r="P58">
-        <v>128.9326086394475</v>
+        <v>80.60144467754255</v>
       </c>
       <c r="Q58">
-        <v>387.4326086394475</v>
+        <v>339.1014446775425</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1369995011463309</v>
+        <v>0.1388491394875896</v>
       </c>
       <c r="T58">
-        <v>1.827971791070286</v>
+        <v>1.865045313063329</v>
       </c>
       <c r="U58">
-        <v>0.08068897842796925</v>
+        <v>0.09488897842796926</v>
       </c>
       <c r="V58">
         <v>0.25</v>
       </c>
       <c r="W58">
-        <v>0.06051673382097694</v>
+        <v>0.07116673382097694</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y58">
-        <v>1.525492708792964</v>
+        <v>1.274446924465424</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1002701682576204</v>
+        <v>0.1004071850711081</v>
       </c>
       <c r="C59">
-        <v>1874.534471038395</v>
+        <v>1788.755312881432</v>
       </c>
       <c r="D59">
-        <v>5332.577471038396</v>
+        <v>5319.197312881432</v>
       </c>
       <c r="E59">
-        <v>2424.043000000001</v>
+        <v>2496.442000000001</v>
       </c>
       <c r="F59">
-        <v>4126.743</v>
+        <v>4199.142000000001</v>
       </c>
       <c r="G59">
         <v>668.7</v>
@@ -6119,28 +6119,28 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M59">
-        <v>391.5824275047732</v>
+        <v>398.4522946539797</v>
       </c>
       <c r="N59">
-        <v>107.4685929033901</v>
+        <v>100.5987257541835</v>
       </c>
       <c r="O59">
-        <v>26.86714822584752</v>
+        <v>25.14968143854588</v>
       </c>
       <c r="P59">
-        <v>80.60144467754255</v>
+        <v>75.44904431563765</v>
       </c>
       <c r="Q59">
-        <v>339.1014446775425</v>
+        <v>333.9490443156377</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1388491394875896</v>
+        <v>0.1407868558450988</v>
       </c>
       <c r="T59">
-        <v>1.865045313063329</v>
+        <v>1.903884240865564</v>
       </c>
       <c r="U59">
         <v>0.09488897842796926</v>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>1.274446924465424</v>
+        <v>1.252473701629814</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1004071850711081</v>
+        <v>0.1145526968201056</v>
       </c>
       <c r="C60">
-        <v>1788.755312881432</v>
+        <v>621.9589791815479</v>
       </c>
       <c r="D60">
-        <v>5319.197312881432</v>
+        <v>4224.799979181547</v>
       </c>
       <c r="E60">
-        <v>2496.442</v>
+        <v>2568.840999999999</v>
       </c>
       <c r="F60">
-        <v>4199.142</v>
+        <v>4271.540999999999</v>
       </c>
       <c r="G60">
         <v>668.7</v>
@@ -6201,45 +6201,45 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M60">
-        <v>398.4522946539797</v>
+        <v>527.4882344031862</v>
       </c>
       <c r="N60">
-        <v>100.5987257541836</v>
+        <v>-28.43721399502294</v>
       </c>
       <c r="O60">
-        <v>25.1496814385459</v>
+        <v>-7.109303498755736</v>
       </c>
       <c r="P60">
-        <v>75.44904431563769</v>
+        <v>-21.32791049626721</v>
       </c>
       <c r="Q60">
-        <v>333.9490443156377</v>
+        <v>237.1720895037328</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1407868558450988</v>
+        <v>0.1437240544040451</v>
       </c>
       <c r="T60">
-        <v>1.903884240865564</v>
+        <v>1.962756450066702</v>
       </c>
       <c r="U60">
-        <v>0.09488897842796926</v>
+        <v>0.1234889784279693</v>
       </c>
       <c r="V60">
-        <v>0.25</v>
+        <v>0.2365223467840958</v>
       </c>
       <c r="W60">
-        <v>0.07116673382097694</v>
+        <v>0.0942810754482154</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y60">
-        <v>1.252473701629814</v>
+        <v>0.9460893871363831</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1145526968201056</v>
+        <v>0.1153295866043853</v>
       </c>
       <c r="C61">
-        <v>621.9589791815479</v>
+        <v>502.3541189895896</v>
       </c>
       <c r="D61">
-        <v>4224.799979181547</v>
+        <v>4177.594118989589</v>
       </c>
       <c r="E61">
-        <v>2568.840999999999</v>
+        <v>2641.24</v>
       </c>
       <c r="F61">
-        <v>4271.540999999999</v>
+        <v>4343.94</v>
       </c>
       <c r="G61">
         <v>668.7</v>
@@ -6283,37 +6283,37 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M61">
-        <v>527.4882344031862</v>
+        <v>536.4287129523927</v>
       </c>
       <c r="N61">
-        <v>-28.43721399502294</v>
+        <v>-37.37769254422949</v>
       </c>
       <c r="O61">
-        <v>-7.109303498755736</v>
+        <v>-9.344423136057372</v>
       </c>
       <c r="P61">
-        <v>-21.32791049626721</v>
+        <v>-28.03326940817212</v>
       </c>
       <c r="Q61">
-        <v>237.1720895037328</v>
+        <v>230.4667305918279</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1437240544040451</v>
+        <v>0.1461721557641463</v>
       </c>
       <c r="T61">
-        <v>1.962756450066702</v>
+        <v>2.01182536131837</v>
       </c>
       <c r="U61">
         <v>0.1234889784279693</v>
       </c>
       <c r="V61">
-        <v>0.2365223467840958</v>
+        <v>0.2325803076710275</v>
       </c>
       <c r="W61">
-        <v>0.0942810754482154</v>
+        <v>0.0947678738312113</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.9460893871363831</v>
+        <v>0.9303212306841101</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1153295866043853</v>
+        <v>0.116106476388665</v>
       </c>
       <c r="C62">
-        <v>502.3541189895896</v>
+        <v>383.7925126321297</v>
       </c>
       <c r="D62">
-        <v>4177.594118989589</v>
+        <v>4131.43151263213</v>
       </c>
       <c r="E62">
-        <v>2641.24</v>
+        <v>2713.639</v>
       </c>
       <c r="F62">
-        <v>4343.94</v>
+        <v>4416.339</v>
       </c>
       <c r="G62">
         <v>668.7</v>
@@ -6365,37 +6365,37 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M62">
-        <v>536.4287129523927</v>
+        <v>545.3691915015994</v>
       </c>
       <c r="N62">
-        <v>-37.37769254422949</v>
+        <v>-46.31817109343615</v>
       </c>
       <c r="O62">
-        <v>-9.344423136057372</v>
+        <v>-11.57954277335904</v>
       </c>
       <c r="P62">
-        <v>-28.03326940817212</v>
+        <v>-34.73862832007711</v>
       </c>
       <c r="Q62">
-        <v>230.4667305918279</v>
+        <v>223.7613716799229</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1461721557641463</v>
+        <v>0.1487458007837398</v>
       </c>
       <c r="T62">
-        <v>2.01182536131837</v>
+        <v>2.0634106269932</v>
       </c>
       <c r="U62">
         <v>0.1234889784279693</v>
       </c>
       <c r="V62">
-        <v>0.2325803076710275</v>
+        <v>0.2287675157419942</v>
       </c>
       <c r="W62">
-        <v>0.0947678738312113</v>
+        <v>0.09523871161148602</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.9303212306841101</v>
+        <v>0.915070062967977</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.116106476388665</v>
+        <v>0.1168833661729447</v>
       </c>
       <c r="C63">
-        <v>383.7925126321297</v>
+        <v>266.2399540794031</v>
       </c>
       <c r="D63">
-        <v>4131.43151263213</v>
+        <v>4086.277954079402</v>
       </c>
       <c r="E63">
-        <v>2713.639</v>
+        <v>2786.038</v>
       </c>
       <c r="F63">
-        <v>4416.339</v>
+        <v>4488.737999999999</v>
       </c>
       <c r="G63">
         <v>668.7</v>
@@ -6447,37 +6447,37 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M63">
-        <v>545.3691915015994</v>
+        <v>554.3096700508058</v>
       </c>
       <c r="N63">
-        <v>-46.31817109343615</v>
+        <v>-55.25864964264258</v>
       </c>
       <c r="O63">
-        <v>-11.57954277335904</v>
+        <v>-13.81466241066065</v>
       </c>
       <c r="P63">
-        <v>-34.73862832007711</v>
+        <v>-41.44398723198194</v>
       </c>
       <c r="Q63">
-        <v>223.7613716799229</v>
+        <v>217.0560127680181</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1487458007837398</v>
+        <v>0.1514549008043645</v>
       </c>
       <c r="T63">
-        <v>2.0634106269932</v>
+        <v>2.117710906650915</v>
       </c>
       <c r="U63">
         <v>0.1234889784279693</v>
       </c>
       <c r="V63">
-        <v>0.2287675157419942</v>
+        <v>0.2250777171009944</v>
       </c>
       <c r="W63">
-        <v>0.09523871161148602</v>
+        <v>0.09569436107626801</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.915070062967977</v>
+        <v>0.9003108684039776</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1168833661729447</v>
+        <v>0.1176602559572243</v>
       </c>
       <c r="C64">
-        <v>266.2399540794031</v>
+        <v>149.6637165234806</v>
       </c>
       <c r="D64">
-        <v>4086.277954079402</v>
+        <v>4042.100716523481</v>
       </c>
       <c r="E64">
-        <v>2786.038</v>
+        <v>2858.437</v>
       </c>
       <c r="F64">
-        <v>4488.737999999999</v>
+        <v>4561.137</v>
       </c>
       <c r="G64">
         <v>668.7</v>
@@ -6529,37 +6529,37 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M64">
-        <v>554.3096700508058</v>
+        <v>563.2501486000125</v>
       </c>
       <c r="N64">
-        <v>-55.25864964264258</v>
+        <v>-64.19912819184924</v>
       </c>
       <c r="O64">
-        <v>-13.81466241066065</v>
+        <v>-16.04978204796231</v>
       </c>
       <c r="P64">
-        <v>-41.44398723198194</v>
+        <v>-48.14934614388693</v>
       </c>
       <c r="Q64">
-        <v>217.0560127680181</v>
+        <v>210.3506538561131</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1514549008043645</v>
+        <v>0.1543104386639419</v>
       </c>
       <c r="T64">
-        <v>2.117710906650915</v>
+        <v>2.174946336560399</v>
       </c>
       <c r="U64">
         <v>0.1234889784279693</v>
       </c>
       <c r="V64">
-        <v>0.2250777171009944</v>
+        <v>0.2215050549247881</v>
       </c>
       <c r="W64">
-        <v>0.09569436107626801</v>
+        <v>0.09613554547867596</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.9003108684039776</v>
+        <v>0.8860202196991523</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1176602559572243</v>
+        <v>0.118437145741504</v>
       </c>
       <c r="C65">
-        <v>149.6637165234806</v>
+        <v>34.03247327328336</v>
       </c>
       <c r="D65">
-        <v>4042.100716523481</v>
+        <v>3998.868473273283</v>
       </c>
       <c r="E65">
-        <v>2858.437</v>
+        <v>2930.836</v>
       </c>
       <c r="F65">
-        <v>4561.137</v>
+        <v>4633.536</v>
       </c>
       <c r="G65">
         <v>668.7</v>
@@ -6611,37 +6611,37 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M65">
-        <v>563.2501486000125</v>
+        <v>572.190627149219</v>
       </c>
       <c r="N65">
-        <v>-64.19912819184924</v>
+        <v>-73.13960674105579</v>
       </c>
       <c r="O65">
-        <v>-16.04978204796231</v>
+        <v>-18.28490168526395</v>
       </c>
       <c r="P65">
-        <v>-48.14934614388693</v>
+        <v>-54.85470505579184</v>
       </c>
       <c r="Q65">
-        <v>210.3506538561131</v>
+        <v>203.6452949442082</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1543104386639419</v>
+        <v>0.1573246175157181</v>
       </c>
       <c r="T65">
-        <v>2.174946336560399</v>
+        <v>2.235361512575966</v>
       </c>
       <c r="U65">
         <v>0.1234889784279693</v>
       </c>
       <c r="V65">
-        <v>0.2215050549247881</v>
+        <v>0.2180440384415883</v>
       </c>
       <c r="W65">
-        <v>0.09613554547867596</v>
+        <v>0.09656294286850868</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.8860202196991523</v>
+        <v>0.872176153766353</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.118437145741504</v>
+        <v>0.1192140355257837</v>
       </c>
       <c r="C66">
-        <v>34.03247327328336</v>
+        <v>-80.68377632775537</v>
       </c>
       <c r="D66">
-        <v>3998.868473273283</v>
+        <v>3956.551223672244</v>
       </c>
       <c r="E66">
-        <v>2930.836</v>
+        <v>3003.235</v>
       </c>
       <c r="F66">
-        <v>4633.536</v>
+        <v>4705.934999999999</v>
       </c>
       <c r="G66">
         <v>668.7</v>
@@ -6693,37 +6693,37 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M66">
-        <v>572.190627149219</v>
+        <v>581.1311056984255</v>
       </c>
       <c r="N66">
-        <v>-73.13960674105579</v>
+        <v>-82.08008529026222</v>
       </c>
       <c r="O66">
-        <v>-18.28490168526395</v>
+        <v>-20.52002132256555</v>
       </c>
       <c r="P66">
-        <v>-54.85470505579184</v>
+        <v>-61.56006396769666</v>
       </c>
       <c r="Q66">
-        <v>203.6452949442082</v>
+        <v>196.9399360323033</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1573246175157181</v>
+        <v>0.1605110351590243</v>
       </c>
       <c r="T66">
-        <v>2.235361512575966</v>
+        <v>2.299228984363851</v>
       </c>
       <c r="U66">
         <v>0.1234889784279693</v>
       </c>
       <c r="V66">
-        <v>0.2180440384415883</v>
+        <v>0.2146895147732562</v>
       </c>
       <c r="W66">
-        <v>0.09656294286850868</v>
+        <v>0.09697718956942346</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.872176153766353</v>
+        <v>0.8587580590930247</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1192140355257837</v>
+        <v>0.1199909253100634</v>
       </c>
       <c r="C67">
-        <v>-80.68377632775537</v>
+        <v>-194.5137763294952</v>
       </c>
       <c r="D67">
-        <v>3956.551223672244</v>
+        <v>3915.120223670504</v>
       </c>
       <c r="E67">
-        <v>3003.235</v>
+        <v>3075.634</v>
       </c>
       <c r="F67">
-        <v>4705.934999999999</v>
+        <v>4778.334</v>
       </c>
       <c r="G67">
         <v>668.7</v>
@@ -6775,37 +6775,37 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M67">
-        <v>581.1311056984255</v>
+        <v>590.0715842476321</v>
       </c>
       <c r="N67">
-        <v>-82.08008529026222</v>
+        <v>-91.02056383946888</v>
       </c>
       <c r="O67">
-        <v>-20.52002132256555</v>
+        <v>-22.75514095986722</v>
       </c>
       <c r="P67">
-        <v>-61.56006396769666</v>
+        <v>-68.26542287960166</v>
       </c>
       <c r="Q67">
-        <v>196.9399360323033</v>
+        <v>190.2345771203983</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1605110351590243</v>
+        <v>0.1638848891342897</v>
       </c>
       <c r="T67">
-        <v>2.299228984363851</v>
+        <v>2.366853366256906</v>
       </c>
       <c r="U67">
         <v>0.1234889784279693</v>
       </c>
       <c r="V67">
-        <v>0.2146895147732562</v>
+        <v>0.2114366433372977</v>
       </c>
       <c r="W67">
-        <v>0.09697718956942346</v>
+        <v>0.09737888334000748</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.8587580590930247</v>
+        <v>0.8457465733491909</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1199909253100634</v>
+        <v>0.1207678150943431</v>
       </c>
       <c r="C68">
-        <v>-194.5137763294952</v>
+        <v>-307.4850792860216</v>
       </c>
       <c r="D68">
-        <v>3915.120223670504</v>
+        <v>3874.547920713979</v>
       </c>
       <c r="E68">
-        <v>3075.634</v>
+        <v>3148.033</v>
       </c>
       <c r="F68">
-        <v>4778.334</v>
+        <v>4850.733</v>
       </c>
       <c r="G68">
         <v>668.7</v>
@@ -6857,37 +6857,37 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M68">
-        <v>590.0715842476321</v>
+        <v>599.0120627968387</v>
       </c>
       <c r="N68">
-        <v>-91.02056383946888</v>
+        <v>-99.96104238867542</v>
       </c>
       <c r="O68">
-        <v>-22.75514095986722</v>
+        <v>-24.99026059716886</v>
       </c>
       <c r="P68">
-        <v>-68.26542287960166</v>
+        <v>-74.97078179150657</v>
       </c>
       <c r="Q68">
-        <v>190.2345771203983</v>
+        <v>183.5292182084934</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1638848891342897</v>
+        <v>0.1674632191080561</v>
       </c>
       <c r="T68">
-        <v>2.366853366256906</v>
+        <v>2.438576195537418</v>
       </c>
       <c r="U68">
         <v>0.1234889784279693</v>
       </c>
       <c r="V68">
-        <v>0.2114366433372977</v>
+        <v>0.2082808725412186</v>
       </c>
       <c r="W68">
-        <v>0.09737888334000748</v>
+        <v>0.09776858625176811</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.8457465733491909</v>
+        <v>0.8331234901648745</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1207678150943431</v>
+        <v>0.1215447048786228</v>
       </c>
       <c r="C69">
-        <v>-307.4850792860216</v>
+        <v>-419.6241073596457</v>
       </c>
       <c r="D69">
-        <v>3874.547920713979</v>
+        <v>3834.807892640355</v>
       </c>
       <c r="E69">
-        <v>3148.033</v>
+        <v>3220.432000000001</v>
       </c>
       <c r="F69">
-        <v>4850.733</v>
+        <v>4923.132000000001</v>
       </c>
       <c r="G69">
         <v>668.7</v>
@@ -6939,37 +6939,37 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M69">
-        <v>599.0120627968387</v>
+        <v>607.9525413460452</v>
       </c>
       <c r="N69">
-        <v>-99.96104238867542</v>
+        <v>-108.901520937882</v>
       </c>
       <c r="O69">
-        <v>-24.99026059716886</v>
+        <v>-27.22538023447049</v>
       </c>
       <c r="P69">
-        <v>-74.97078179150657</v>
+        <v>-81.67614070341148</v>
       </c>
       <c r="Q69">
-        <v>183.5292182084934</v>
+        <v>176.8238592965885</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1674632191080561</v>
+        <v>0.1712651947051828</v>
       </c>
       <c r="T69">
-        <v>2.438576195537418</v>
+        <v>2.514781701647963</v>
       </c>
       <c r="U69">
         <v>0.1234889784279693</v>
       </c>
       <c r="V69">
-        <v>0.2082808725412186</v>
+        <v>0.2052179185332595</v>
       </c>
       <c r="W69">
-        <v>0.09776858625176811</v>
+        <v>0.09814682731318283</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.8331234901648745</v>
+        <v>0.8208716741330382</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1215447048786228</v>
+        <v>0.1223215946629025</v>
       </c>
       <c r="C70">
-        <v>-419.6241073596457</v>
+        <v>-530.9562097027374</v>
       </c>
       <c r="D70">
-        <v>3834.807892640355</v>
+        <v>3795.874790297262</v>
       </c>
       <c r="E70">
-        <v>3220.432000000001</v>
+        <v>3292.831</v>
       </c>
       <c r="F70">
-        <v>4923.132000000001</v>
+        <v>4995.531</v>
       </c>
       <c r="G70">
         <v>668.7</v>
@@ -7021,37 +7021,37 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M70">
-        <v>607.9525413460452</v>
+        <v>616.8930198952518</v>
       </c>
       <c r="N70">
-        <v>-108.901520937882</v>
+        <v>-117.8419994870885</v>
       </c>
       <c r="O70">
-        <v>-27.22538023447049</v>
+        <v>-29.46049987177213</v>
       </c>
       <c r="P70">
-        <v>-81.67614070341148</v>
+        <v>-88.38149961531639</v>
       </c>
       <c r="Q70">
-        <v>176.8238592965885</v>
+        <v>170.1185003846836</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1712651947051828</v>
+        <v>0.1753124590505113</v>
       </c>
       <c r="T70">
-        <v>2.514781701647963</v>
+        <v>2.595903692023704</v>
       </c>
       <c r="U70">
         <v>0.1234889784279693</v>
       </c>
       <c r="V70">
-        <v>0.2052179185332595</v>
+        <v>0.2022437458008935</v>
       </c>
       <c r="W70">
-        <v>0.09814682731318283</v>
+        <v>0.09851410486557104</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.8208716741330382</v>
+        <v>0.8089749832035739</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1223215946629025</v>
+        <v>0.1832406305389493</v>
       </c>
       <c r="C71">
-        <v>-530.9562097027374</v>
+        <v>-2285.834630994167</v>
       </c>
       <c r="D71">
-        <v>3795.874790297262</v>
+        <v>2113.395369005833</v>
       </c>
       <c r="E71">
-        <v>3292.831</v>
+        <v>3365.23</v>
       </c>
       <c r="F71">
-        <v>4995.531</v>
+        <v>5067.93</v>
       </c>
       <c r="G71">
         <v>668.7</v>
@@ -7103,45 +7103,45 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M71">
-        <v>616.8930198952518</v>
+        <v>1042.417344444458</v>
       </c>
       <c r="N71">
-        <v>-117.8419994870885</v>
+        <v>-543.3663240362952</v>
       </c>
       <c r="O71">
-        <v>-29.46049987177213</v>
+        <v>-135.8415810090738</v>
       </c>
       <c r="P71">
-        <v>-88.38149961531639</v>
+        <v>-407.5247430272213</v>
       </c>
       <c r="Q71">
-        <v>170.1185003846836</v>
+        <v>-149.0247430272213</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1753124590505113</v>
+        <v>0.1883033613247521</v>
       </c>
       <c r="T71">
-        <v>2.595903692023704</v>
+        <v>2.856288920006043</v>
       </c>
       <c r="U71">
-        <v>0.1234889784279693</v>
+        <v>0.2056889784279693</v>
       </c>
       <c r="V71">
-        <v>0.2022437458008935</v>
+        <v>0.1196859931072342</v>
       </c>
       <c r="W71">
-        <v>0.09851410486557104</v>
+        <v>0.1810708887736053</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y71">
-        <v>0.8089749832035739</v>
+        <v>0.4787439724289367</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1832406305389493</v>
+        <v>0.184839520323229</v>
       </c>
       <c r="C72">
-        <v>-2285.834630994167</v>
+        <v>-2382.53669430877</v>
       </c>
       <c r="D72">
-        <v>2113.395369005833</v>
+        <v>2089.092305691231</v>
       </c>
       <c r="E72">
-        <v>3365.23</v>
+        <v>3437.629000000001</v>
       </c>
       <c r="F72">
-        <v>5067.93</v>
+        <v>5140.329000000001</v>
       </c>
       <c r="G72">
         <v>668.7</v>
@@ -7185,37 +7185,37 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M72">
-        <v>1042.417344444458</v>
+        <v>1057.309020793665</v>
       </c>
       <c r="N72">
-        <v>-543.3663240362952</v>
+        <v>-558.2580003855018</v>
       </c>
       <c r="O72">
-        <v>-135.8415810090738</v>
+        <v>-139.5645000963754</v>
       </c>
       <c r="P72">
-        <v>-407.5247430272213</v>
+        <v>-418.6935002891263</v>
       </c>
       <c r="Q72">
-        <v>-149.0247430272213</v>
+        <v>-160.1935002891263</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1883033613247521</v>
+        <v>0.1932172703359505</v>
       </c>
       <c r="T72">
-        <v>2.856288920006043</v>
+        <v>2.954781641385562</v>
       </c>
       <c r="U72">
         <v>0.2056889784279693</v>
       </c>
       <c r="V72">
-        <v>0.1196859931072342</v>
+        <v>0.1180002748944562</v>
       </c>
       <c r="W72">
-        <v>0.1810708887736053</v>
+        <v>0.181417622430709</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.4787439724289367</v>
+        <v>0.472001099577825</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.184839520323229</v>
+        <v>0.1864384101075087</v>
       </c>
       <c r="C73">
-        <v>-2382.536694308769</v>
+        <v>-2478.686164350584</v>
       </c>
       <c r="D73">
-        <v>2089.092305691231</v>
+        <v>2065.341835649415</v>
       </c>
       <c r="E73">
-        <v>3437.629</v>
+        <v>3510.027999999999</v>
       </c>
       <c r="F73">
-        <v>5140.329</v>
+        <v>5212.727999999999</v>
       </c>
       <c r="G73">
         <v>668.7</v>
@@ -7267,37 +7267,37 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M73">
-        <v>1057.309020793665</v>
+        <v>1072.200697142871</v>
       </c>
       <c r="N73">
-        <v>-558.2580003855015</v>
+        <v>-573.1496767347079</v>
       </c>
       <c r="O73">
-        <v>-139.5645000963754</v>
+        <v>-143.287419183677</v>
       </c>
       <c r="P73">
-        <v>-418.6935002891262</v>
+        <v>-429.8622575510309</v>
       </c>
       <c r="Q73">
-        <v>-160.1935002891262</v>
+        <v>-171.3622575510309</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1932172703359504</v>
+        <v>0.1984821728479486</v>
       </c>
       <c r="T73">
-        <v>2.95478164138556</v>
+        <v>3.06030955714933</v>
       </c>
       <c r="U73">
         <v>0.2056889784279693</v>
       </c>
       <c r="V73">
-        <v>0.1180002748944563</v>
+        <v>0.1163613821875888</v>
       </c>
       <c r="W73">
-        <v>0.181417622430709</v>
+        <v>0.1817547245973376</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.472001099577825</v>
+        <v>0.4654455287503553</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1864384101075087</v>
+        <v>0.1880372998917884</v>
       </c>
       <c r="C74">
-        <v>-2478.686164350584</v>
+        <v>-2574.301676226004</v>
       </c>
       <c r="D74">
-        <v>2065.341835649415</v>
+        <v>2042.125323773995</v>
       </c>
       <c r="E74">
-        <v>3510.027999999999</v>
+        <v>3582.427</v>
       </c>
       <c r="F74">
-        <v>5212.727999999999</v>
+        <v>5285.126999999999</v>
       </c>
       <c r="G74">
         <v>668.7</v>
@@ -7349,37 +7349,37 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M74">
-        <v>1072.200697142871</v>
+        <v>1087.092373492078</v>
       </c>
       <c r="N74">
-        <v>-573.1496767347079</v>
+        <v>-588.0413530839145</v>
       </c>
       <c r="O74">
-        <v>-143.287419183677</v>
+        <v>-147.0103382709786</v>
       </c>
       <c r="P74">
-        <v>-429.8622575510309</v>
+        <v>-441.0310148129358</v>
       </c>
       <c r="Q74">
-        <v>-171.3622575510309</v>
+        <v>-182.5310148129358</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1984821728479486</v>
+        <v>0.2041370681386134</v>
       </c>
       <c r="T74">
-        <v>3.06030955714933</v>
+        <v>3.173654355562268</v>
       </c>
       <c r="U74">
         <v>0.2056889784279693</v>
       </c>
       <c r="V74">
-        <v>0.1163613821875888</v>
+        <v>0.1147673906507725</v>
       </c>
       <c r="W74">
-        <v>0.1817547245973376</v>
+        <v>0.1820825910881682</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.4654455287503553</v>
+        <v>0.4590695626030902</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1880372998917884</v>
+        <v>0.1896361896760681</v>
       </c>
       <c r="C75">
-        <v>-2574.301676226004</v>
+        <v>-2669.401036446576</v>
       </c>
       <c r="D75">
-        <v>2042.125323773995</v>
+        <v>2019.424963553424</v>
       </c>
       <c r="E75">
-        <v>3582.427</v>
+        <v>3654.826</v>
       </c>
       <c r="F75">
-        <v>5285.126999999999</v>
+        <v>5357.526</v>
       </c>
       <c r="G75">
         <v>668.7</v>
@@ -7431,37 +7431,37 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M75">
-        <v>1087.092373492078</v>
+        <v>1101.984049841284</v>
       </c>
       <c r="N75">
-        <v>-588.0413530839145</v>
+        <v>-602.9330294331211</v>
       </c>
       <c r="O75">
-        <v>-147.0103382709786</v>
+        <v>-150.7332573582803</v>
       </c>
       <c r="P75">
-        <v>-441.0310148129358</v>
+        <v>-452.1997720748408</v>
       </c>
       <c r="Q75">
-        <v>-182.5310148129358</v>
+        <v>-193.6997720748408</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2041370681386134</v>
+        <v>0.2102269553747139</v>
       </c>
       <c r="T75">
-        <v>3.173654355562268</v>
+        <v>3.295717984622356</v>
       </c>
       <c r="U75">
         <v>0.2056889784279693</v>
       </c>
       <c r="V75">
-        <v>0.1147673906507725</v>
+        <v>0.1132164799663026</v>
       </c>
       <c r="W75">
-        <v>0.1820825910881682</v>
+        <v>0.1824015963224898</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.4590695626030902</v>
+        <v>0.4528659198652105</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1896361896760681</v>
+        <v>0.1912350794603478</v>
       </c>
       <c r="C76">
-        <v>-2669.401036446576</v>
+        <v>-2764.001268476192</v>
       </c>
       <c r="D76">
-        <v>2019.424963553424</v>
+        <v>1997.223731523807</v>
       </c>
       <c r="E76">
-        <v>3654.826</v>
+        <v>3727.224999999999</v>
       </c>
       <c r="F76">
-        <v>5357.526</v>
+        <v>5429.924999999999</v>
       </c>
       <c r="G76">
         <v>668.7</v>
@@ -7513,37 +7513,37 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M76">
-        <v>1101.984049841284</v>
+        <v>1116.875726190491</v>
       </c>
       <c r="N76">
-        <v>-602.9330294331211</v>
+        <v>-617.8247057823277</v>
       </c>
       <c r="O76">
-        <v>-150.7332573582803</v>
+        <v>-154.4561764455819</v>
       </c>
       <c r="P76">
-        <v>-452.1997720748408</v>
+        <v>-463.3685293367457</v>
       </c>
       <c r="Q76">
-        <v>-193.6997720748408</v>
+        <v>-204.8685293367457</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2102269553747139</v>
+        <v>0.2168040335897025</v>
       </c>
       <c r="T76">
-        <v>3.295717984622356</v>
+        <v>3.427546704007251</v>
       </c>
       <c r="U76">
         <v>0.2056889784279693</v>
       </c>
       <c r="V76">
-        <v>0.1132164799663026</v>
+        <v>0.1117069269000853</v>
       </c>
       <c r="W76">
-        <v>0.1824015963224898</v>
+        <v>0.1827120947505629</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.4528659198652105</v>
+        <v>0.4468277076003411</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1912350794603478</v>
+        <v>0.1928339692446275</v>
       </c>
       <c r="C77">
-        <v>-2764.001268476192</v>
+        <v>-2858.118655306527</v>
       </c>
       <c r="D77">
-        <v>1997.223731523807</v>
+        <v>1975.505344693472</v>
       </c>
       <c r="E77">
-        <v>3727.224999999999</v>
+        <v>3799.624</v>
       </c>
       <c r="F77">
-        <v>5429.924999999999</v>
+        <v>5502.324</v>
       </c>
       <c r="G77">
         <v>668.7</v>
@@ -7595,37 +7595,37 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M77">
-        <v>1116.875726190491</v>
+        <v>1131.767402539698</v>
       </c>
       <c r="N77">
-        <v>-617.8247057823277</v>
+        <v>-632.7163821315343</v>
       </c>
       <c r="O77">
-        <v>-154.4561764455819</v>
+        <v>-158.1790955328836</v>
       </c>
       <c r="P77">
-        <v>-463.3685293367457</v>
+        <v>-474.5372865986507</v>
       </c>
       <c r="Q77">
-        <v>-204.8685293367457</v>
+        <v>-216.0372865986507</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2168040335897025</v>
+        <v>0.2239292016559401</v>
       </c>
       <c r="T77">
-        <v>3.427546704007251</v>
+        <v>3.570361150007553</v>
       </c>
       <c r="U77">
         <v>0.2056889784279693</v>
       </c>
       <c r="V77">
-        <v>0.1117069269000853</v>
+        <v>0.1102370989145578</v>
       </c>
       <c r="W77">
-        <v>0.1827120947505629</v>
+        <v>0.1830144221673709</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.4468277076003411</v>
+        <v>0.4409483956582313</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1928339692446275</v>
+        <v>0.1944328590289072</v>
       </c>
       <c r="C78">
-        <v>-2858.118655306527</v>
+        <v>-2951.768779284476</v>
       </c>
       <c r="D78">
-        <v>1975.505344693472</v>
+        <v>1954.254220715523</v>
       </c>
       <c r="E78">
-        <v>3799.624</v>
+        <v>3872.023</v>
       </c>
       <c r="F78">
-        <v>5502.324</v>
+        <v>5574.723</v>
       </c>
       <c r="G78">
         <v>668.7</v>
@@ -7677,37 +7677,37 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M78">
-        <v>1131.767402539698</v>
+        <v>1146.659078888904</v>
       </c>
       <c r="N78">
-        <v>-632.7163821315343</v>
+        <v>-647.6080584807409</v>
       </c>
       <c r="O78">
-        <v>-158.1790955328836</v>
+        <v>-161.9020146201852</v>
       </c>
       <c r="P78">
-        <v>-474.5372865986507</v>
+        <v>-485.7060438605556</v>
       </c>
       <c r="Q78">
-        <v>-216.0372865986507</v>
+        <v>-227.2060438605556</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2239292016559401</v>
+        <v>0.2316739495540245</v>
       </c>
       <c r="T78">
-        <v>3.570361150007553</v>
+        <v>3.725594243486142</v>
       </c>
       <c r="U78">
         <v>0.2056889784279693</v>
       </c>
       <c r="V78">
-        <v>0.1102370989145578</v>
+        <v>0.1088054482793038</v>
       </c>
       <c r="W78">
-        <v>0.1830144221673709</v>
+        <v>0.183308896924002</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.4409483956582313</v>
+        <v>0.4352217931172153</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1944328590289072</v>
+        <v>0.1960317488131869</v>
       </c>
       <c r="C79">
-        <v>-2951.768779284476</v>
+        <v>-3044.96655939635</v>
       </c>
       <c r="D79">
-        <v>1954.254220715523</v>
+        <v>1933.45544060365</v>
       </c>
       <c r="E79">
-        <v>3872.023</v>
+        <v>3944.422</v>
       </c>
       <c r="F79">
-        <v>5574.723</v>
+        <v>5647.122</v>
       </c>
       <c r="G79">
         <v>668.7</v>
@@ -7759,37 +7759,37 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M79">
-        <v>1146.659078888904</v>
+        <v>1161.550755238111</v>
       </c>
       <c r="N79">
-        <v>-647.6080584807409</v>
+        <v>-662.4997348299474</v>
       </c>
       <c r="O79">
-        <v>-161.9020146201852</v>
+        <v>-165.6249337074869</v>
       </c>
       <c r="P79">
-        <v>-485.7060438605556</v>
+        <v>-496.8748011224606</v>
       </c>
       <c r="Q79">
-        <v>-227.2060438605556</v>
+        <v>-238.3748011224606</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2316739495540245</v>
+        <v>0.2401227654428438</v>
       </c>
       <c r="T79">
-        <v>3.725594243486142</v>
+        <v>3.894939436371876</v>
       </c>
       <c r="U79">
         <v>0.2056889784279693</v>
       </c>
       <c r="V79">
-        <v>0.1088054482793038</v>
+        <v>0.1074105066346974</v>
       </c>
       <c r="W79">
-        <v>0.183308896924002</v>
+        <v>0.1835958210458478</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.4352217931172153</v>
+        <v>0.4296420265387895</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1960317488131869</v>
+        <v>0.1976306385974665</v>
       </c>
       <c r="C80">
-        <v>-3044.96655939635</v>
+        <v>-3137.726286196274</v>
       </c>
       <c r="D80">
-        <v>1933.45544060365</v>
+        <v>1913.094713803726</v>
       </c>
       <c r="E80">
-        <v>3944.422</v>
+        <v>4016.821</v>
       </c>
       <c r="F80">
-        <v>5647.122</v>
+        <v>5719.521</v>
       </c>
       <c r="G80">
         <v>668.7</v>
@@ -7841,37 +7841,37 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M80">
-        <v>1161.550755238111</v>
+        <v>1176.442431587317</v>
       </c>
       <c r="N80">
-        <v>-662.4997348299474</v>
+        <v>-677.3914111791538</v>
       </c>
       <c r="O80">
-        <v>-165.6249337074869</v>
+        <v>-169.3478527947885</v>
       </c>
       <c r="P80">
-        <v>-496.8748011224606</v>
+        <v>-508.0435583843654</v>
       </c>
       <c r="Q80">
-        <v>-238.3748011224606</v>
+        <v>-249.5435583843654</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2401227654428438</v>
+        <v>0.2493762304639316</v>
       </c>
       <c r="T80">
-        <v>3.894939436371876</v>
+        <v>4.080412742865775</v>
       </c>
       <c r="U80">
         <v>0.2056889784279693</v>
       </c>
       <c r="V80">
-        <v>0.1074105066346974</v>
+        <v>0.1060508799684354</v>
       </c>
       <c r="W80">
-        <v>0.1835958210458478</v>
+        <v>0.1838754812658746</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.4296420265387895</v>
+        <v>0.4242035198737415</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1976306385974665</v>
+        <v>0.1992295283817462</v>
       </c>
       <c r="C81">
-        <v>-3137.726286196274</v>
+        <v>-3230.061654550673</v>
       </c>
       <c r="D81">
-        <v>1913.094713803726</v>
+        <v>1893.158345449327</v>
       </c>
       <c r="E81">
-        <v>4016.821</v>
+        <v>4089.22</v>
       </c>
       <c r="F81">
-        <v>5719.521</v>
+        <v>5791.92</v>
       </c>
       <c r="G81">
         <v>668.7</v>
@@ -7923,37 +7923,37 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M81">
-        <v>1176.442431587317</v>
+        <v>1191.334107936524</v>
       </c>
       <c r="N81">
-        <v>-677.3914111791538</v>
+        <v>-692.2830875283604</v>
       </c>
       <c r="O81">
-        <v>-169.3478527947885</v>
+        <v>-173.0707718820901</v>
       </c>
       <c r="P81">
-        <v>-508.0435583843654</v>
+        <v>-519.2123156462703</v>
       </c>
       <c r="Q81">
-        <v>-249.5435583843654</v>
+        <v>-260.7123156462703</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2493762304639316</v>
+        <v>0.2595550419871281</v>
       </c>
       <c r="T81">
-        <v>4.080412742865775</v>
+        <v>4.284433380009063</v>
       </c>
       <c r="U81">
         <v>0.2056889784279693</v>
       </c>
       <c r="V81">
-        <v>0.1060508799684354</v>
+        <v>0.1047252439688299</v>
       </c>
       <c r="W81">
-        <v>0.1838754812658746</v>
+        <v>0.1841481499804008</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.4242035198737415</v>
+        <v>0.4189009758753197</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1992295283817462</v>
+        <v>0.200828418166026</v>
       </c>
       <c r="C82">
-        <v>-3230.061654550673</v>
+        <v>-3321.985794356468</v>
       </c>
       <c r="D82">
-        <v>1893.158345449327</v>
+        <v>1873.633205643533</v>
       </c>
       <c r="E82">
-        <v>4089.22</v>
+        <v>4161.619000000001</v>
       </c>
       <c r="F82">
-        <v>5791.92</v>
+        <v>5864.319</v>
       </c>
       <c r="G82">
         <v>668.7</v>
@@ -8005,37 +8005,37 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M82">
-        <v>1191.334107936524</v>
+        <v>1206.22578428573</v>
       </c>
       <c r="N82">
-        <v>-692.2830875283604</v>
+        <v>-707.1747638775672</v>
       </c>
       <c r="O82">
-        <v>-173.0707718820901</v>
+        <v>-176.7936909693918</v>
       </c>
       <c r="P82">
-        <v>-519.2123156462703</v>
+        <v>-530.3810729081754</v>
       </c>
       <c r="Q82">
-        <v>-260.7123156462703</v>
+        <v>-271.8810729081754</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2595550419871281</v>
+        <v>0.2708053073548717</v>
       </c>
       <c r="T82">
-        <v>4.284433380009063</v>
+        <v>4.509929873693752</v>
       </c>
       <c r="U82">
         <v>0.2056889784279693</v>
       </c>
       <c r="V82">
-        <v>0.1047252439688299</v>
+        <v>0.1034323397223011</v>
       </c>
       <c r="W82">
-        <v>0.1841481499804008</v>
+        <v>0.1844140861340745</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.4189009758753197</v>
+        <v>0.4137293588892046</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.200828418166026</v>
+        <v>0.2024273079503057</v>
       </c>
       <c r="C83">
-        <v>-3321.985794356468</v>
+        <v>-3413.511299377809</v>
       </c>
       <c r="D83">
-        <v>1873.633205643533</v>
+        <v>1854.506700622191</v>
       </c>
       <c r="E83">
-        <v>4161.619000000001</v>
+        <v>4234.018</v>
       </c>
       <c r="F83">
-        <v>5864.319</v>
+        <v>5936.718</v>
       </c>
       <c r="G83">
         <v>668.7</v>
@@ -8087,37 +8087,37 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M83">
-        <v>1206.22578428573</v>
+        <v>1221.117460634937</v>
       </c>
       <c r="N83">
-        <v>-707.1747638775672</v>
+        <v>-722.0664402267736</v>
       </c>
       <c r="O83">
-        <v>-176.7936909693918</v>
+        <v>-180.5166100566934</v>
       </c>
       <c r="P83">
-        <v>-530.3810729081754</v>
+        <v>-541.5498301700802</v>
       </c>
       <c r="Q83">
-        <v>-271.8810729081754</v>
+        <v>-283.0498301700802</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2708053073548717</v>
+        <v>0.2833056022079202</v>
       </c>
       <c r="T83">
-        <v>4.509929873693752</v>
+        <v>4.760481533343405</v>
       </c>
       <c r="U83">
         <v>0.2056889784279693</v>
       </c>
       <c r="V83">
-        <v>0.1034323397223011</v>
+        <v>0.1021709697256877</v>
       </c>
       <c r="W83">
-        <v>0.1844140861340745</v>
+        <v>0.1846735360400976</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.4137293588892046</v>
+        <v>0.4086838789027509</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2024273079503057</v>
+        <v>0.2040261977345854</v>
       </c>
       <c r="C84">
-        <v>-3413.511299377809</v>
+        <v>-3504.650254334427</v>
       </c>
       <c r="D84">
-        <v>1854.506700622191</v>
+        <v>1835.766745665573</v>
       </c>
       <c r="E84">
-        <v>4234.018</v>
+        <v>4306.417</v>
       </c>
       <c r="F84">
-        <v>5936.718</v>
+        <v>6009.117</v>
       </c>
       <c r="G84">
         <v>668.7</v>
@@ -8169,37 +8169,37 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M84">
-        <v>1221.117460634937</v>
+        <v>1236.009136984143</v>
       </c>
       <c r="N84">
-        <v>-722.0664402267736</v>
+        <v>-736.9581165759802</v>
       </c>
       <c r="O84">
-        <v>-180.5166100566934</v>
+        <v>-184.239529143995</v>
       </c>
       <c r="P84">
-        <v>-541.5498301700802</v>
+        <v>-552.7185874319852</v>
       </c>
       <c r="Q84">
-        <v>-283.0498301700802</v>
+        <v>-294.2185874319852</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2833056022079202</v>
+        <v>0.2972765199848567</v>
       </c>
       <c r="T84">
-        <v>4.760481533343405</v>
+        <v>5.040509858834193</v>
       </c>
       <c r="U84">
         <v>0.2056889784279693</v>
       </c>
       <c r="V84">
-        <v>0.1021709697256877</v>
+        <v>0.100939994186824</v>
       </c>
       <c r="W84">
-        <v>0.1846735360400976</v>
+        <v>0.1849267341411563</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.4086838789027509</v>
+        <v>0.4037599767472961</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2040261977345854</v>
+        <v>0.205625087518865</v>
       </c>
       <c r="C85">
-        <v>-3504.650254334427</v>
+        <v>-3595.414260364026</v>
       </c>
       <c r="D85">
-        <v>1835.766745665573</v>
+        <v>1817.401739635974</v>
       </c>
       <c r="E85">
-        <v>4306.417</v>
+        <v>4378.816000000001</v>
       </c>
       <c r="F85">
-        <v>6009.117</v>
+        <v>6081.516000000001</v>
       </c>
       <c r="G85">
         <v>668.7</v>
@@ -8251,37 +8251,37 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M85">
-        <v>1236.009136984143</v>
+        <v>1250.90081333335</v>
       </c>
       <c r="N85">
-        <v>-736.9581165759802</v>
+        <v>-751.8497929251868</v>
       </c>
       <c r="O85">
-        <v>-184.239529143995</v>
+        <v>-187.9624482312967</v>
       </c>
       <c r="P85">
-        <v>-552.7185874319852</v>
+        <v>-563.8873446938901</v>
       </c>
       <c r="Q85">
-        <v>-294.2185874319852</v>
+        <v>-305.3873446938901</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2972765199848567</v>
+        <v>0.3129938024839103</v>
       </c>
       <c r="T85">
-        <v>5.040509858834193</v>
+        <v>5.355541725011332</v>
       </c>
       <c r="U85">
         <v>0.2056889784279693</v>
       </c>
       <c r="V85">
-        <v>0.100939994186824</v>
+        <v>0.09973832758936182</v>
       </c>
       <c r="W85">
-        <v>0.1849267341411563</v>
+        <v>0.1851739037159993</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.4037599767472961</v>
+        <v>0.3989533103574473</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.205625087518865</v>
+        <v>0.2072239773031447</v>
       </c>
       <c r="C86">
-        <v>-3595.414260364025</v>
+        <v>-3685.81445897146</v>
       </c>
       <c r="D86">
-        <v>1817.401739635975</v>
+        <v>1799.40054102854</v>
       </c>
       <c r="E86">
-        <v>4378.816</v>
+        <v>4451.215</v>
       </c>
       <c r="F86">
-        <v>6081.516</v>
+        <v>6153.915</v>
       </c>
       <c r="G86">
         <v>668.7</v>
@@ -8333,37 +8333,37 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M86">
-        <v>1250.90081333335</v>
+        <v>1265.792489682556</v>
       </c>
       <c r="N86">
-        <v>-751.8497929251865</v>
+        <v>-766.7414692743931</v>
       </c>
       <c r="O86">
-        <v>-187.9624482312966</v>
+        <v>-191.6853673185983</v>
       </c>
       <c r="P86">
-        <v>-563.8873446938899</v>
+        <v>-575.0561019557948</v>
       </c>
       <c r="Q86">
-        <v>-305.3873446938899</v>
+        <v>-316.5561019557948</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3129938024839101</v>
+        <v>0.3308067226495041</v>
       </c>
       <c r="T86">
-        <v>5.355541725011328</v>
+        <v>5.712577840012083</v>
       </c>
       <c r="U86">
         <v>0.2056889784279693</v>
       </c>
       <c r="V86">
-        <v>0.09973832758936185</v>
+        <v>0.09856493550007524</v>
       </c>
       <c r="W86">
-        <v>0.1851739037159993</v>
+        <v>0.1854152575361401</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3989533103574474</v>
+        <v>0.3942597420003009</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2072239773031447</v>
+        <v>0.2088228670874244</v>
       </c>
       <c r="C87">
-        <v>-3685.81445897146</v>
+        <v>-3775.861554568595</v>
       </c>
       <c r="D87">
-        <v>1799.40054102854</v>
+        <v>1781.752445431404</v>
       </c>
       <c r="E87">
-        <v>4451.215</v>
+        <v>4523.614</v>
       </c>
       <c r="F87">
-        <v>6153.915</v>
+        <v>6226.313999999999</v>
       </c>
       <c r="G87">
         <v>668.7</v>
@@ -8415,37 +8415,37 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M87">
-        <v>1265.792489682556</v>
+        <v>1280.684166031763</v>
       </c>
       <c r="N87">
-        <v>-766.7414692743931</v>
+        <v>-781.6331456235997</v>
       </c>
       <c r="O87">
-        <v>-191.6853673185983</v>
+        <v>-195.4082864058999</v>
       </c>
       <c r="P87">
-        <v>-575.0561019557948</v>
+        <v>-586.2248592176998</v>
       </c>
       <c r="Q87">
-        <v>-316.5561019557948</v>
+        <v>-327.7248592176998</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3308067226495041</v>
+        <v>0.3511643456958973</v>
       </c>
       <c r="T87">
-        <v>5.712577840012083</v>
+        <v>6.120619114298662</v>
       </c>
       <c r="U87">
         <v>0.2056889784279693</v>
       </c>
       <c r="V87">
-        <v>0.09856493550007524</v>
+        <v>0.09741883159891156</v>
       </c>
       <c r="W87">
-        <v>0.1854152575361401</v>
+        <v>0.1856509984767428</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3942597420003009</v>
+        <v>0.3896753263956463</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2088228670874244</v>
+        <v>0.2104217568717041</v>
       </c>
       <c r="C88">
-        <v>-3775.861554568595</v>
+        <v>-3865.565835700638</v>
       </c>
       <c r="D88">
-        <v>1781.752445431404</v>
+        <v>1764.447164299362</v>
       </c>
       <c r="E88">
-        <v>4523.614</v>
+        <v>4596.013</v>
       </c>
       <c r="F88">
-        <v>6226.313999999999</v>
+        <v>6298.713</v>
       </c>
       <c r="G88">
         <v>668.7</v>
@@ -8497,37 +8497,37 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M88">
-        <v>1280.684166031763</v>
+        <v>1295.57584238097</v>
       </c>
       <c r="N88">
-        <v>-781.6331456235997</v>
+        <v>-796.5248219728063</v>
       </c>
       <c r="O88">
-        <v>-195.4082864058999</v>
+        <v>-199.1312054932016</v>
       </c>
       <c r="P88">
-        <v>-586.2248592176998</v>
+        <v>-597.3936164796047</v>
       </c>
       <c r="Q88">
-        <v>-327.7248592176998</v>
+        <v>-338.8936164796047</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3511643456958973</v>
+        <v>0.3746539107494278</v>
       </c>
       <c r="T88">
-        <v>6.120619114298662</v>
+        <v>6.591435969244712</v>
       </c>
       <c r="U88">
         <v>0.2056889784279693</v>
       </c>
       <c r="V88">
-        <v>0.09741883159891156</v>
+        <v>0.09629907491386661</v>
       </c>
       <c r="W88">
-        <v>0.1856509984767428</v>
+        <v>0.1858813200853776</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3896753263956463</v>
+        <v>0.3851962996554664</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2104217568717041</v>
+        <v>0.2120206466559838</v>
       </c>
       <c r="C89">
-        <v>-3865.565835700638</v>
+        <v>-3954.937195047419</v>
       </c>
       <c r="D89">
-        <v>1764.447164299362</v>
+        <v>1747.474804952581</v>
       </c>
       <c r="E89">
-        <v>4596.013</v>
+        <v>4668.412</v>
       </c>
       <c r="F89">
-        <v>6298.713</v>
+        <v>6371.112</v>
       </c>
       <c r="G89">
         <v>668.7</v>
@@ -8579,37 +8579,37 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M89">
-        <v>1295.57584238097</v>
+        <v>1310.467518730176</v>
       </c>
       <c r="N89">
-        <v>-796.5248219728063</v>
+        <v>-811.4164983220129</v>
       </c>
       <c r="O89">
-        <v>-199.1312054932016</v>
+        <v>-202.8541245805032</v>
       </c>
       <c r="P89">
-        <v>-597.3936164796047</v>
+        <v>-608.5623737415096</v>
       </c>
       <c r="Q89">
-        <v>-338.8936164796047</v>
+        <v>-350.0623737415096</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3746539107494278</v>
+        <v>0.4020584033118802</v>
       </c>
       <c r="T89">
-        <v>6.591435969244712</v>
+        <v>7.140722300015105</v>
       </c>
       <c r="U89">
         <v>0.2056889784279693</v>
       </c>
       <c r="V89">
-        <v>0.09629907491386661</v>
+        <v>0.09520476724439084</v>
       </c>
       <c r="W89">
-        <v>0.1858813200853776</v>
+        <v>0.1861064071119979</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3851962996554664</v>
+        <v>0.3808190689775633</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2120206466559838</v>
+        <v>0.2136195364402635</v>
       </c>
       <c r="C90">
-        <v>-3954.937195047419</v>
+        <v>-4043.985148281295</v>
       </c>
       <c r="D90">
-        <v>1747.474804952581</v>
+        <v>1730.825851718705</v>
       </c>
       <c r="E90">
-        <v>4668.412</v>
+        <v>4740.811</v>
       </c>
       <c r="F90">
-        <v>6371.112</v>
+        <v>6443.511</v>
       </c>
       <c r="G90">
         <v>668.7</v>
@@ -8661,37 +8661,37 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M90">
-        <v>1310.467518730176</v>
+        <v>1325.359195079383</v>
       </c>
       <c r="N90">
-        <v>-811.4164983220129</v>
+        <v>-826.3081746712193</v>
       </c>
       <c r="O90">
-        <v>-202.8541245805032</v>
+        <v>-206.5770436678048</v>
       </c>
       <c r="P90">
-        <v>-608.5623737415096</v>
+        <v>-619.7311310034145</v>
       </c>
       <c r="Q90">
-        <v>-350.0623737415096</v>
+        <v>-361.2311310034145</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4020584033118802</v>
+        <v>0.4344455308856875</v>
       </c>
       <c r="T90">
-        <v>7.140722300015105</v>
+        <v>7.789878872743753</v>
       </c>
       <c r="U90">
         <v>0.2056889784279693</v>
       </c>
       <c r="V90">
-        <v>0.09520476724439084</v>
+        <v>0.09413505075849882</v>
       </c>
       <c r="W90">
-        <v>0.1861064071119979</v>
+        <v>0.1863264360031886</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3808190689775633</v>
+        <v>0.3765402030339953</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2136195364402635</v>
+        <v>0.2152184262245432</v>
       </c>
       <c r="C91">
-        <v>-4043.985148281295</v>
+        <v>-4132.718851857235</v>
       </c>
       <c r="D91">
-        <v>1730.825851718705</v>
+        <v>1714.491148142765</v>
       </c>
       <c r="E91">
-        <v>4740.811</v>
+        <v>4813.21</v>
       </c>
       <c r="F91">
-        <v>6443.511</v>
+        <v>6515.91</v>
       </c>
       <c r="G91">
         <v>668.7</v>
@@ -8743,37 +8743,37 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M91">
-        <v>1325.359195079383</v>
+        <v>1340.250871428589</v>
       </c>
       <c r="N91">
-        <v>-826.3081746712193</v>
+        <v>-841.1998510204259</v>
       </c>
       <c r="O91">
-        <v>-206.5770436678048</v>
+        <v>-210.2999627551065</v>
       </c>
       <c r="P91">
-        <v>-619.7311310034145</v>
+        <v>-630.8998882653194</v>
       </c>
       <c r="Q91">
-        <v>-361.2311310034145</v>
+        <v>-372.3998882653194</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4344455308856875</v>
+        <v>0.4733100839742562</v>
       </c>
       <c r="T91">
-        <v>7.789878872743753</v>
+        <v>8.568866760018127</v>
       </c>
       <c r="U91">
         <v>0.2056889784279693</v>
       </c>
       <c r="V91">
-        <v>0.09413505075849882</v>
+        <v>0.09308910575007105</v>
       </c>
       <c r="W91">
-        <v>0.1863264360031886</v>
+        <v>0.186541575363464</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3765402030339953</v>
+        <v>0.3723564230002843</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2152184262245432</v>
+        <v>0.2168173160088229</v>
       </c>
       <c r="C92">
-        <v>-4132.718851857235</v>
+        <v>-4221.147119804946</v>
       </c>
       <c r="D92">
-        <v>1714.491148142765</v>
+        <v>1698.461880195054</v>
       </c>
       <c r="E92">
-        <v>4813.21</v>
+        <v>4885.609</v>
       </c>
       <c r="F92">
-        <v>6515.91</v>
+        <v>6588.309</v>
       </c>
       <c r="G92">
         <v>668.7</v>
@@ -8825,37 +8825,37 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M92">
-        <v>1340.250871428589</v>
+        <v>1355.142547777796</v>
       </c>
       <c r="N92">
-        <v>-841.1998510204259</v>
+        <v>-856.0915273696324</v>
       </c>
       <c r="O92">
-        <v>-210.2999627551065</v>
+        <v>-214.0228818424081</v>
       </c>
       <c r="P92">
-        <v>-630.8998882653194</v>
+        <v>-642.0686455272244</v>
       </c>
       <c r="Q92">
-        <v>-372.3998882653194</v>
+        <v>-383.5686455272244</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4733100839742562</v>
+        <v>0.5208112044158403</v>
       </c>
       <c r="T92">
-        <v>8.568866760018127</v>
+        <v>9.520963066686809</v>
       </c>
       <c r="U92">
         <v>0.2056889784279693</v>
       </c>
       <c r="V92">
-        <v>0.09308910575007105</v>
+        <v>0.09206614854402631</v>
       </c>
       <c r="W92">
-        <v>0.186541575363464</v>
+        <v>0.1867519863861508</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3723564230002843</v>
+        <v>0.3682645941761052</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2168173160088229</v>
+        <v>0.2184162057931026</v>
       </c>
       <c r="C93">
-        <v>-4221.147119804946</v>
+        <v>-4309.278439587753</v>
       </c>
       <c r="D93">
-        <v>1698.461880195054</v>
+        <v>1682.729560412246</v>
       </c>
       <c r="E93">
-        <v>4885.609</v>
+        <v>4958.008</v>
       </c>
       <c r="F93">
-        <v>6588.309</v>
+        <v>6660.708</v>
       </c>
       <c r="G93">
         <v>668.7</v>
@@ -8907,37 +8907,37 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M93">
-        <v>1355.142547777796</v>
+        <v>1370.034224127002</v>
       </c>
       <c r="N93">
-        <v>-856.0915273696324</v>
+        <v>-870.983203718839</v>
       </c>
       <c r="O93">
-        <v>-214.0228818424081</v>
+        <v>-217.7458009297098</v>
       </c>
       <c r="P93">
-        <v>-642.0686455272244</v>
+        <v>-653.2374027891293</v>
       </c>
       <c r="Q93">
-        <v>-383.5686455272244</v>
+        <v>-394.7374027891293</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5208112044158403</v>
+        <v>0.5801876049678205</v>
       </c>
       <c r="T93">
-        <v>9.520963066686809</v>
+        <v>10.71108345002266</v>
       </c>
       <c r="U93">
         <v>0.2056889784279693</v>
       </c>
       <c r="V93">
-        <v>0.09206614854402631</v>
+        <v>0.09106542953811297</v>
       </c>
       <c r="W93">
-        <v>0.1867519863861508</v>
+        <v>0.1869578232561706</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3682645941761052</v>
+        <v>0.3642617181524519</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2184162057931026</v>
+        <v>0.2200150955773823</v>
       </c>
       <c r="C94">
-        <v>-4309.278439587753</v>
+        <v>-4397.120987088227</v>
       </c>
       <c r="D94">
-        <v>1682.729560412246</v>
+        <v>1667.286012911773</v>
       </c>
       <c r="E94">
-        <v>4958.008</v>
+        <v>5030.407</v>
       </c>
       <c r="F94">
-        <v>6660.708</v>
+        <v>6733.107</v>
       </c>
       <c r="G94">
         <v>668.7</v>
@@ -8989,37 +8989,37 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M94">
-        <v>1370.034224127002</v>
+        <v>1384.925900476209</v>
       </c>
       <c r="N94">
-        <v>-870.983203718839</v>
+        <v>-885.8748800680456</v>
       </c>
       <c r="O94">
-        <v>-217.7458009297098</v>
+        <v>-221.4687200170114</v>
       </c>
       <c r="P94">
-        <v>-653.2374027891293</v>
+        <v>-664.4061600510342</v>
       </c>
       <c r="Q94">
-        <v>-394.7374027891293</v>
+        <v>-405.9061600510342</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5801876049678205</v>
+        <v>0.656528691391795</v>
       </c>
       <c r="T94">
-        <v>10.71108345002266</v>
+        <v>12.24123822859733</v>
       </c>
       <c r="U94">
         <v>0.2056889784279693</v>
       </c>
       <c r="V94">
-        <v>0.09106542953811297</v>
+        <v>0.0900862313710365</v>
       </c>
       <c r="W94">
-        <v>0.1869578232561706</v>
+        <v>0.1871592335268351</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3642617181524519</v>
+        <v>0.360344925484146</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2200150955773823</v>
+        <v>0.2216139853616619</v>
       </c>
       <c r="C95">
-        <v>-4397.120987088227</v>
+        <v>-4484.682640776062</v>
       </c>
       <c r="D95">
-        <v>1667.286012911773</v>
+        <v>1652.123359223939</v>
       </c>
       <c r="E95">
-        <v>5030.407</v>
+        <v>5102.806</v>
       </c>
       <c r="F95">
-        <v>6733.107</v>
+        <v>6805.506</v>
       </c>
       <c r="G95">
         <v>668.7</v>
@@ -9071,37 +9071,37 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M95">
-        <v>1384.925900476209</v>
+        <v>1399.817576825415</v>
       </c>
       <c r="N95">
-        <v>-885.8748800680456</v>
+        <v>-900.7665564172522</v>
       </c>
       <c r="O95">
-        <v>-221.4687200170114</v>
+        <v>-225.1916391043131</v>
       </c>
       <c r="P95">
-        <v>-664.4061600510342</v>
+        <v>-675.5749173129392</v>
       </c>
       <c r="Q95">
-        <v>-405.9061600510342</v>
+        <v>-417.0749173129392</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.656528691391795</v>
+        <v>0.758316806623761</v>
       </c>
       <c r="T95">
-        <v>12.24123822859733</v>
+        <v>14.28144460003022</v>
       </c>
       <c r="U95">
         <v>0.2056889784279693</v>
       </c>
       <c r="V95">
-        <v>0.0900862313710365</v>
+        <v>0.08912786720751482</v>
       </c>
       <c r="W95">
-        <v>0.1871592335268351</v>
+        <v>0.1873563584725918</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.360344925484146</v>
+        <v>0.3565114688300594</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2216139853616619</v>
+        <v>0.2232128751459417</v>
       </c>
       <c r="C96">
-        <v>-4484.682640776062</v>
+        <v>-4571.970995109899</v>
       </c>
       <c r="D96">
-        <v>1652.123359223939</v>
+        <v>1637.2340048901</v>
       </c>
       <c r="E96">
-        <v>5102.806</v>
+        <v>5175.205</v>
       </c>
       <c r="F96">
-        <v>6805.506</v>
+        <v>6877.905</v>
       </c>
       <c r="G96">
         <v>668.7</v>
@@ -9153,37 +9153,37 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M96">
-        <v>1399.817576825415</v>
+        <v>1414.709253174622</v>
       </c>
       <c r="N96">
-        <v>-900.7665564172522</v>
+        <v>-915.6582327664586</v>
       </c>
       <c r="O96">
-        <v>-225.1916391043131</v>
+        <v>-228.9145581916146</v>
       </c>
       <c r="P96">
-        <v>-675.5749173129392</v>
+        <v>-686.7436745748439</v>
       </c>
       <c r="Q96">
-        <v>-417.0749173129392</v>
+        <v>-428.2436745748439</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.758316806623761</v>
+        <v>0.9008201679485137</v>
       </c>
       <c r="T96">
-        <v>14.28144460003022</v>
+        <v>17.13773352003628</v>
       </c>
       <c r="U96">
         <v>0.2056889784279693</v>
       </c>
       <c r="V96">
-        <v>0.08912786720751482</v>
+        <v>0.08818967913164626</v>
       </c>
       <c r="W96">
-        <v>0.1873563584725918</v>
+        <v>0.1875493334194906</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3565114688300594</v>
+        <v>0.3527587165265851</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2232128751459417</v>
+        <v>0.2248117649302214</v>
       </c>
       <c r="C97">
-        <v>-4571.970995109899</v>
+        <v>-4658.993373220911</v>
       </c>
       <c r="D97">
-        <v>1637.2340048901</v>
+        <v>1622.610626779089</v>
       </c>
       <c r="E97">
-        <v>5175.205</v>
+        <v>5247.604</v>
       </c>
       <c r="F97">
-        <v>6877.905</v>
+        <v>6950.304</v>
       </c>
       <c r="G97">
         <v>668.7</v>
@@ -9235,37 +9235,37 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M97">
-        <v>1414.709253174622</v>
+        <v>1429.600929523828</v>
       </c>
       <c r="N97">
-        <v>-915.6582327664586</v>
+        <v>-930.5499091156652</v>
       </c>
       <c r="O97">
-        <v>-228.9145581916146</v>
+        <v>-232.6374772789163</v>
       </c>
       <c r="P97">
-        <v>-686.7436745748439</v>
+        <v>-697.9124318367489</v>
       </c>
       <c r="Q97">
-        <v>-428.2436745748439</v>
+        <v>-439.4124318367489</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.9008201679485137</v>
+        <v>1.114575209935643</v>
       </c>
       <c r="T97">
-        <v>17.13773352003628</v>
+        <v>21.42216690004536</v>
       </c>
       <c r="U97">
         <v>0.2056889784279693</v>
       </c>
       <c r="V97">
-        <v>0.08818967913164626</v>
+        <v>0.08727103664069161</v>
       </c>
       <c r="W97">
-        <v>0.1875493334194906</v>
+        <v>0.1877382880549955</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3527587165265851</v>
+        <v>0.3490841465627664</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2248117649302213</v>
+        <v>0.2264106547145011</v>
       </c>
       <c r="C98">
-        <v>-4658.993373220912</v>
+        <v>-4745.756838922682</v>
       </c>
       <c r="D98">
-        <v>1622.610626779087</v>
+        <v>1608.246161077318</v>
       </c>
       <c r="E98">
-        <v>5247.603999999999</v>
+        <v>5320.003</v>
       </c>
       <c r="F98">
-        <v>6950.303999999999</v>
+        <v>7022.703</v>
       </c>
       <c r="G98">
         <v>668.7</v>
@@ -9317,37 +9317,37 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M98">
-        <v>1429.600929523828</v>
+        <v>1444.492605873035</v>
       </c>
       <c r="N98">
-        <v>-930.5499091156652</v>
+        <v>-945.4415854648718</v>
       </c>
       <c r="O98">
-        <v>-232.6374772789163</v>
+        <v>-236.3603963662179</v>
       </c>
       <c r="P98">
-        <v>-697.9124318367489</v>
+        <v>-709.0811890986538</v>
       </c>
       <c r="Q98">
-        <v>-439.4124318367489</v>
+        <v>-450.5811890986538</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.11457520993564</v>
+        <v>1.47083361324752</v>
       </c>
       <c r="T98">
-        <v>21.4221669000453</v>
+        <v>28.5628892000604</v>
       </c>
       <c r="U98">
         <v>0.2056889784279693</v>
       </c>
       <c r="V98">
-        <v>0.08727103664069161</v>
+        <v>0.08637133523202468</v>
       </c>
       <c r="W98">
-        <v>0.1877382880549955</v>
+        <v>0.1879233467186344</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3490841465627664</v>
+        <v>0.3454853409280987</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2264106547145011</v>
+        <v>0.2280095444987807</v>
       </c>
       <c r="C99">
-        <v>-4745.756838922682</v>
+        <v>-4832.268208088782</v>
       </c>
       <c r="D99">
-        <v>1608.246161077318</v>
+        <v>1594.133791911218</v>
       </c>
       <c r="E99">
-        <v>5320.003</v>
+        <v>5392.402</v>
       </c>
       <c r="F99">
-        <v>7022.703</v>
+        <v>7095.102</v>
       </c>
       <c r="G99">
         <v>668.7</v>
@@ -9399,37 +9399,37 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M99">
-        <v>1444.492605873035</v>
+        <v>1459.384282222242</v>
       </c>
       <c r="N99">
-        <v>-945.4415854648718</v>
+        <v>-960.3332618140784</v>
       </c>
       <c r="O99">
-        <v>-236.3603963662179</v>
+        <v>-240.0833154535196</v>
       </c>
       <c r="P99">
-        <v>-709.0811890986538</v>
+        <v>-720.2499463605587</v>
       </c>
       <c r="Q99">
-        <v>-450.5811890986538</v>
+        <v>-461.7499463605587</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.47083361324752</v>
+        <v>2.183350419871279</v>
       </c>
       <c r="T99">
-        <v>28.5628892000604</v>
+        <v>42.8443338000906</v>
       </c>
       <c r="U99">
         <v>0.2056889784279693</v>
       </c>
       <c r="V99">
-        <v>0.08637133523202468</v>
+        <v>0.08548999507659585</v>
       </c>
       <c r="W99">
-        <v>0.1879233467186344</v>
+        <v>0.1881046286748521</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3454853409280987</v>
+        <v>0.3419599803063834</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2280095444987807</v>
+        <v>0.2296084342830604</v>
       </c>
       <c r="C100">
-        <v>-4832.268208088782</v>
+        <v>-4918.534059436508</v>
       </c>
       <c r="D100">
-        <v>1594.133791911218</v>
+        <v>1580.266940563491</v>
       </c>
       <c r="E100">
-        <v>5392.402</v>
+        <v>5464.800999999999</v>
       </c>
       <c r="F100">
-        <v>7095.102</v>
+        <v>7167.500999999999</v>
       </c>
       <c r="G100">
         <v>668.7</v>
@@ -9481,37 +9481,37 @@
         <v>499.0510204081633</v>
       </c>
       <c r="M100">
-        <v>1459.384282222242</v>
+        <v>1474.275958571448</v>
       </c>
       <c r="N100">
-        <v>-960.3332618140784</v>
+        <v>-975.2249381632847</v>
       </c>
       <c r="O100">
-        <v>-240.0833154535196</v>
+        <v>-243.8062345408212</v>
       </c>
       <c r="P100">
-        <v>-720.2499463605587</v>
+        <v>-731.4187036224636</v>
       </c>
       <c r="Q100">
-        <v>-461.7499463605587</v>
+        <v>-472.9187036224636</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.183350419871279</v>
+        <v>4.320900839742558</v>
       </c>
       <c r="T100">
-        <v>42.8443338000906</v>
+        <v>85.68866760018119</v>
       </c>
       <c r="U100">
         <v>0.2056889784279693</v>
       </c>
       <c r="V100">
-        <v>0.08548999507659585</v>
+        <v>0.08462645977279187</v>
       </c>
       <c r="W100">
-        <v>0.1881046286748521</v>
+        <v>0.1882822483693281</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3419599803063834</v>
+        <v>0.3385058390911675</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2296084342830604</v>
-      </c>
-      <c r="C101">
-        <v>-4918.534059436508</v>
-      </c>
-      <c r="D101">
-        <v>1580.266940563491</v>
-      </c>
-      <c r="E101">
-        <v>5464.800999999999</v>
-      </c>
-      <c r="F101">
-        <v>7167.500999999999</v>
-      </c>
-      <c r="G101">
-        <v>668.7</v>
-      </c>
-      <c r="H101">
-        <v>5537.2</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>757.5510204081633</v>
-      </c>
-      <c r="K101">
-        <v>258.5</v>
-      </c>
-      <c r="L101">
-        <v>499.0510204081633</v>
-      </c>
-      <c r="M101">
-        <v>1474.275958571448</v>
-      </c>
-      <c r="N101">
-        <v>-975.2249381632847</v>
-      </c>
-      <c r="O101">
-        <v>-243.8062345408212</v>
-      </c>
-      <c r="P101">
-        <v>-731.4187036224636</v>
-      </c>
-      <c r="Q101">
-        <v>-472.9187036224636</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.320900839742558</v>
-      </c>
-      <c r="T101">
-        <v>85.68866760018119</v>
-      </c>
-      <c r="U101">
-        <v>0.2056889784279693</v>
-      </c>
-      <c r="V101">
-        <v>0.08462645977279187</v>
-      </c>
-      <c r="W101">
-        <v>0.1882822483693281</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3385058390911675</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
